--- a/artfynd/A 45800-2025 artfynd.xlsx
+++ b/artfynd/A 45800-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AY50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2039,6 +2039,3939 @@
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>128903544</v>
+      </c>
+      <c r="B15" t="n">
+        <v>79739</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Draggöl, Stora Ramm, Sm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>584191</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6374331</v>
+      </c>
+      <c r="S15" t="n">
+        <v>25</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Oskarshamn</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Misterhult</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-10-04</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-10-04</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>128903951</v>
+      </c>
+      <c r="B16" t="n">
+        <v>92832</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Draggöl, Stora Ramm, Sm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>584183</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6374596</v>
+      </c>
+      <c r="S16" t="n">
+        <v>25</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Oskarshamn</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Misterhult</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-10-04</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-10-04</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>128897118</v>
+      </c>
+      <c r="B17" t="n">
+        <v>96228</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>2180</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Blåmossa</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Leucobryum glaucum</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Draggöl, Draggöl, Sm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>584190</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6374486</v>
+      </c>
+      <c r="S17" t="n">
+        <v>2</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Oskarshamn</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Misterhult</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-10-04</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-10-04</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Kristian  Norrby</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Kristian  Norrby</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>128903715</v>
+      </c>
+      <c r="B18" t="n">
+        <v>96228</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>2180</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Blåmossa</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Leucobryum glaucum</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Draggöl, Stora Ramm, Sm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>584142</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6374419</v>
+      </c>
+      <c r="S18" t="n">
+        <v>25</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Oskarshamn</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Misterhult</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-10-04</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-10-04</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>128904192</v>
+      </c>
+      <c r="B19" t="n">
+        <v>79739</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Ekelund, Sm</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>584149</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6374399</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Oskarshamn</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Misterhult</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-10-04</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-10-04</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Lars Engström</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Lars Engström</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>128904395</v>
+      </c>
+      <c r="B20" t="n">
+        <v>92832</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Ekelund, Sm</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>584177</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6374515</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Oskarshamn</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Misterhult</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-10-04</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-10-04</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="inlineStr"/>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Lars Engström</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Lars Engström</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>128904088</v>
+      </c>
+      <c r="B21" t="n">
+        <v>79739</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Ekelund, Sm</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>584195</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6374314</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Oskarshamn</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Misterhult</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-10-04</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-10-04</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="inlineStr"/>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Lars Engström</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Lars Engström</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>128904450</v>
+      </c>
+      <c r="B22" t="n">
+        <v>79739</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Ekelund, Sm</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>584145</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6374604</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Oskarshamn</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Misterhult</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-10-04</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-10-04</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="inlineStr"/>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Lars Engström</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Lars Engström</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>128904443</v>
+      </c>
+      <c r="B23" t="n">
+        <v>57713</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Ekelund, Sm</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>584113</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6374565</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Oskarshamn</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Misterhult</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-10-04</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-10-04</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Lars Engström</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Lars Engström</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>128903851</v>
+      </c>
+      <c r="B24" t="n">
+        <v>91524</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Draggöl, Stora Ramm, Sm</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>584167</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6374518</v>
+      </c>
+      <c r="S24" t="n">
+        <v>25</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Oskarshamn</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Misterhult</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-10-04</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-10-04</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF24" t="inlineStr"/>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>128903521</v>
+      </c>
+      <c r="B25" t="n">
+        <v>58086</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Draggöl, Stora Ramm, Sm</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>584198</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6374339</v>
+      </c>
+      <c r="S25" t="n">
+        <v>25</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Oskarshamn</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Misterhult</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-10-04</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-10-04</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>128895716</v>
+      </c>
+      <c r="B26" t="n">
+        <v>96228</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>2180</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Blåmossa</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Leucobryum glaucum</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Draggöl, Draggöl, Sm</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>584171</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6374322</v>
+      </c>
+      <c r="S26" t="n">
+        <v>1</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Oskarshamn</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Misterhult</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-10-04</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>11:27</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-10-04</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>11:27</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Louise Lundberg</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Louise Lundberg</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>128903578</v>
+      </c>
+      <c r="B27" t="n">
+        <v>92832</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Draggöl, Stora Ramm, Sm</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>584236</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6374327</v>
+      </c>
+      <c r="S27" t="n">
+        <v>25</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Oskarshamn</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Misterhult</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-10-04</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-10-04</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF27" t="inlineStr"/>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>128903661</v>
+      </c>
+      <c r="B28" t="n">
+        <v>92832</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Draggöl, Stora Ramm, Sm</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>584164</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6374343</v>
+      </c>
+      <c r="S28" t="n">
+        <v>25</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Oskarshamn</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Misterhult</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-10-04</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-10-04</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF28" t="inlineStr"/>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>128904408</v>
+      </c>
+      <c r="B29" t="n">
+        <v>91524</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Ekelund, Sm</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>584143</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6374517</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Oskarshamn</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Misterhult</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-10-04</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-10-04</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF29" t="inlineStr"/>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Lars Engström</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Lars Engström</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>128904429</v>
+      </c>
+      <c r="B30" t="n">
+        <v>91524</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Ekelund, Sm</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>584130</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6374515</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Oskarshamn</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Misterhult</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-10-04</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-10-04</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF30" t="inlineStr"/>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Lars Engström</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Lars Engström</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>128904268</v>
+      </c>
+      <c r="B31" t="n">
+        <v>79739</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Ekelund, Sm</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>584121</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6374409</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Oskarshamn</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Misterhult</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-10-04</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-10-04</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF31" t="inlineStr"/>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Lars Engström</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Lars Engström</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>128904111</v>
+      </c>
+      <c r="B32" t="n">
+        <v>57713</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>E, Sm</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>584212</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6374329</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Oskarshamn</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Misterhult</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-10-04</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-10-04</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Lars Engström</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Lars Engström</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>128903926</v>
+      </c>
+      <c r="B33" t="n">
+        <v>92832</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Draggöl, Stora Ramm, Sm</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>584170</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6374460</v>
+      </c>
+      <c r="S33" t="n">
+        <v>25</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Oskarshamn</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Misterhult</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-10-04</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-10-04</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF33" t="inlineStr"/>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>128903960</v>
+      </c>
+      <c r="B34" t="n">
+        <v>92794</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Draggöl, Stora Ramm, Sm</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>584184</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6374584</v>
+      </c>
+      <c r="S34" t="n">
+        <v>25</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Oskarshamn</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Misterhult</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-10-04</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-10-04</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF34" t="inlineStr"/>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>128904329</v>
+      </c>
+      <c r="B35" t="n">
+        <v>79739</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Ekelund, Sm</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>584199</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6374485</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Oskarshamn</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Misterhult</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-10-04</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-10-04</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF35" t="inlineStr"/>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Lars Engström</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Lars Engström</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>128903654</v>
+      </c>
+      <c r="B36" t="n">
+        <v>92832</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Draggöl, Stora Ramm, Sm</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>584199</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6374343</v>
+      </c>
+      <c r="S36" t="n">
+        <v>25</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Oskarshamn</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Misterhult</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-10-04</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-10-04</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF36" t="inlineStr"/>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>128904124</v>
+      </c>
+      <c r="B37" t="n">
+        <v>92823</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>5449</v>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Phellodon niger s.lat</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Draggöl, Stora Ramm, Sm</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>584176</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6374554</v>
+      </c>
+      <c r="S37" t="n">
+        <v>25</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Oskarshamn</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Misterhult</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-10-04</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-10-04</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF37" t="inlineStr"/>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>128903739</v>
+      </c>
+      <c r="B38" t="n">
+        <v>79739</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Draggöl, Stora Ramm, Sm</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>584164</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6374477</v>
+      </c>
+      <c r="S38" t="n">
+        <v>25</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Oskarshamn</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Misterhult</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-10-04</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-10-04</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF38" t="inlineStr"/>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>128903593</v>
+      </c>
+      <c r="B39" t="n">
+        <v>92832</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Draggöl, Stora Ramm, Sm</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>584200</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6374370</v>
+      </c>
+      <c r="S39" t="n">
+        <v>25</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Oskarshamn</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Misterhult</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-10-04</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-10-04</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF39" t="inlineStr"/>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>128904385</v>
+      </c>
+      <c r="B40" t="n">
+        <v>92832</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Ekelund, Sm</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>584207</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6374488</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Oskarshamn</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Misterhult</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2025-10-04</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2025-10-04</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF40" t="inlineStr"/>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Lars Engström</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Lars Engström</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>128904323</v>
+      </c>
+      <c r="B41" t="n">
+        <v>92832</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Ekelund, Sm</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>584175</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6374451</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Oskarshamn</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Misterhult</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2025-10-04</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2025-10-04</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF41" t="inlineStr"/>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Lars Engström</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Lars Engström</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>128897896</v>
+      </c>
+      <c r="B42" t="n">
+        <v>96228</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>2180</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Blåmossa</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Leucobryum glaucum</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Draggöl, Draggöl, Sm</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>584067</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6374669</v>
+      </c>
+      <c r="S42" t="n">
+        <v>2</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Oskarshamn</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Misterhult</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2025-10-04</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>13:31</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2025-10-04</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>13:31</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Kristian  Norrby</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Kristian  Norrby</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>128897155</v>
+      </c>
+      <c r="B43" t="n">
+        <v>96228</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>2180</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Blåmossa</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Leucobryum glaucum</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Draggöl, Draggöl, Sm</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>584173</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6374485</v>
+      </c>
+      <c r="S43" t="n">
+        <v>2</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Oskarshamn</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Misterhult</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2025-10-04</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>13:07</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2025-10-04</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>13:07</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Kristian  Norrby</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Kristian  Norrby</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>128897364</v>
+      </c>
+      <c r="B44" t="n">
+        <v>92832</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Draggöl, Draggöl, Sm</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>584139</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6374551</v>
+      </c>
+      <c r="S44" t="n">
+        <v>2</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Oskarshamn</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Misterhult</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2025-10-04</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2025-10-04</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Kristian  Norrby</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Kristian  Norrby</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>128897073</v>
+      </c>
+      <c r="B45" t="n">
+        <v>79739</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Draggöl, Draggöl, Sm</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>584164</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6374466</v>
+      </c>
+      <c r="S45" t="n">
+        <v>2</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Oskarshamn</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Misterhult</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2025-10-04</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>12:56</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2025-10-04</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>12:56</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Kristian  Norrby</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Kristian  Norrby</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>128903690</v>
+      </c>
+      <c r="B46" t="n">
+        <v>79739</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Draggöl, Stora Ramm, Sm</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>584120</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6374392</v>
+      </c>
+      <c r="S46" t="n">
+        <v>25</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Oskarshamn</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Misterhult</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2025-10-04</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2025-10-04</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF46" t="inlineStr"/>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>128903940</v>
+      </c>
+      <c r="B47" t="n">
+        <v>92832</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Draggöl, Stora Ramm, Sm</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>584166</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6374449</v>
+      </c>
+      <c r="S47" t="n">
+        <v>25</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Oskarshamn</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Misterhult</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2025-10-04</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2025-10-04</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF47" t="inlineStr"/>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>128903857</v>
+      </c>
+      <c r="B48" t="n">
+        <v>79739</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Draggöl, Stora Ramm, Sm</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>584169</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6374498</v>
+      </c>
+      <c r="S48" t="n">
+        <v>25</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Oskarshamn</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Misterhult</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2025-10-04</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2025-10-04</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF48" t="inlineStr"/>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>128904459</v>
+      </c>
+      <c r="B49" t="n">
+        <v>79739</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Ekelund, Sm</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>584182</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6374604</v>
+      </c>
+      <c r="S49" t="n">
+        <v>10</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Oskarshamn</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Misterhult</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2025-10-04</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2025-10-04</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF49" t="inlineStr"/>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Lars Engström</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Lars Engström</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>128903869</v>
+      </c>
+      <c r="B50" t="n">
+        <v>79739</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Draggöl, Stora Ramm, Sm</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>584166</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6374521</v>
+      </c>
+      <c r="S50" t="n">
+        <v>25</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Oskarshamn</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Misterhult</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2025-10-04</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2025-10-04</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Brandljud</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF50" t="inlineStr"/>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 45800-2025 artfynd.xlsx
+++ b/artfynd/A 45800-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY50"/>
+  <dimension ref="A1:AY53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2374,52 +2374,59 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128903715</v>
+        <v>128904395</v>
       </c>
       <c r="B18" t="n">
-        <v>96228</v>
+        <v>92832</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2180</v>
+        <v>5966</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Draggöl, Stora Ramm, Sm</t>
+          <t>Ekelund, Sm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>584142</v>
+        <v>584177</v>
       </c>
       <c r="R18" t="n">
-        <v>6374419</v>
+        <v>6374515</v>
       </c>
       <c r="S18" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2446,19 +2453,9 @@
           <t>2025-10-04</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>10:30</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-10-04</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>15:00</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2474,63 +2471,64 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128904192</v>
+        <v>128903715</v>
       </c>
       <c r="B19" t="n">
-        <v>79739</v>
+        <v>96228</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6453</v>
+        <v>2180</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Ekelund, Sm</t>
+          <t>Draggöl, Stora Ramm, Sm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>584149</v>
+        <v>584142</v>
       </c>
       <c r="R19" t="n">
-        <v>6374399</v>
+        <v>6374419</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2557,9 +2555,19 @@
           <t>2025-10-04</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-10-04</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2575,22 +2583,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128904395</v>
+        <v>128904192</v>
       </c>
       <c r="B20" t="n">
-        <v>92832</v>
+        <v>79739</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2598,33 +2606,25 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
@@ -2633,10 +2633,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>584177</v>
+        <v>584149</v>
       </c>
       <c r="R20" t="n">
-        <v>6374515</v>
+        <v>6374399</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3463,10 +3463,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128903661</v>
+        <v>128904408</v>
       </c>
       <c r="B28" t="n">
-        <v>92832</v>
+        <v>91524</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3474,44 +3474,48 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5966</v>
+        <v>5442</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Draggöl, Stora Ramm, Sm</t>
+          <t>Ekelund, Sm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>584164</v>
+        <v>584143</v>
       </c>
       <c r="R28" t="n">
-        <v>6374343</v>
+        <v>6374517</v>
       </c>
       <c r="S28" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3538,19 +3542,9 @@
           <t>2025-10-04</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>10:30</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-10-04</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>15:00</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3566,22 +3560,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128904408</v>
+        <v>128903661</v>
       </c>
       <c r="B29" t="n">
-        <v>91524</v>
+        <v>92832</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3589,48 +3583,44 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5442</v>
+        <v>5966</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Ekelund, Sm</t>
+          <t>Draggöl, Stora Ramm, Sm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>584143</v>
+        <v>584164</v>
       </c>
       <c r="R29" t="n">
-        <v>6374517</v>
+        <v>6374343</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3657,9 +3647,19 @@
           <t>2025-10-04</t>
         </is>
       </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-10-04</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3675,12 +3675,12 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
@@ -5206,10 +5206,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128897364</v>
+        <v>128897073</v>
       </c>
       <c r="B44" t="n">
-        <v>92832</v>
+        <v>79739</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5217,21 +5217,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5241,10 +5241,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>584139</v>
+        <v>584164</v>
       </c>
       <c r="R44" t="n">
-        <v>6374551</v>
+        <v>6374466</v>
       </c>
       <c r="S44" t="n">
         <v>2</v>
@@ -5276,7 +5276,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5286,7 +5286,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5313,10 +5313,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128897073</v>
+        <v>128897364</v>
       </c>
       <c r="B45" t="n">
-        <v>79739</v>
+        <v>92832</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5324,21 +5324,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5348,10 +5348,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>584164</v>
+        <v>584139</v>
       </c>
       <c r="R45" t="n">
-        <v>6374466</v>
+        <v>6374551</v>
       </c>
       <c r="S45" t="n">
         <v>2</v>
@@ -5383,7 +5383,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5393,7 +5393,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5420,10 +5420,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128903690</v>
+        <v>128903940</v>
       </c>
       <c r="B46" t="n">
-        <v>79739</v>
+        <v>92832</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5431,24 +5431,28 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
       <c r="N46" t="inlineStr"/>
@@ -5458,10 +5462,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>584120</v>
+        <v>584166</v>
       </c>
       <c r="R46" t="n">
-        <v>6374392</v>
+        <v>6374449</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -5531,10 +5535,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128903940</v>
+        <v>128903690</v>
       </c>
       <c r="B47" t="n">
-        <v>92832</v>
+        <v>79739</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5542,28 +5546,24 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr"/>
       <c r="N47" t="inlineStr"/>
@@ -5573,10 +5573,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>584166</v>
+        <v>584120</v>
       </c>
       <c r="R47" t="n">
-        <v>6374449</v>
+        <v>6374392</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -5972,6 +5972,344 @@
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>128909203</v>
+      </c>
+      <c r="B51" t="n">
+        <v>79710</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Draggöl, Stora Ramm, Sm</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>584172</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6374454</v>
+      </c>
+      <c r="S51" t="n">
+        <v>25</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Oskarshamn</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Misterhult</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2025-10-04</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2025-10-04</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF51" t="inlineStr"/>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>128908556</v>
+      </c>
+      <c r="B52" t="n">
+        <v>78877</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Draggöl, Stora Ramm, Sm</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>584169</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6374498</v>
+      </c>
+      <c r="S52" t="n">
+        <v>25</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Oskarshamn</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Misterhult</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2025-10-04</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2025-10-04</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Flera stubbar som hade brandljud men även stående tallar var skadade.</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF52" t="inlineStr"/>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>128908500</v>
+      </c>
+      <c r="B53" t="n">
+        <v>92786</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>4361</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Orange taggsvamp</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Hydnellum aurantiacum</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Draggöl, Stora Ramm, Sm</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>584161</v>
+      </c>
+      <c r="R53" t="n">
+        <v>6374352</v>
+      </c>
+      <c r="S53" t="n">
+        <v>25</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Oskarshamn</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Misterhult</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2025-10-04</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2025-10-04</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF53" t="inlineStr"/>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 45800-2025 artfynd.xlsx
+++ b/artfynd/A 45800-2025 artfynd.xlsx
@@ -2041,10 +2041,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128903544</v>
+        <v>128903951</v>
       </c>
       <c r="B15" t="n">
-        <v>79739</v>
+        <v>92832</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2052,24 +2052,28 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
@@ -2079,10 +2083,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>584191</v>
+        <v>584183</v>
       </c>
       <c r="R15" t="n">
-        <v>6374331</v>
+        <v>6374596</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2152,10 +2156,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128903951</v>
+        <v>128903544</v>
       </c>
       <c r="B16" t="n">
-        <v>92832</v>
+        <v>79739</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2163,28 +2167,24 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
@@ -2194,10 +2194,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>584183</v>
+        <v>584191</v>
       </c>
       <c r="R16" t="n">
-        <v>6374596</v>
+        <v>6374331</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2267,48 +2267,59 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128897118</v>
+        <v>128904395</v>
       </c>
       <c r="B17" t="n">
-        <v>96228</v>
+        <v>92832</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2180</v>
+        <v>5966</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Draggöl, Draggöl, Sm</t>
+          <t>Ekelund, Sm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>584190</v>
+        <v>584177</v>
       </c>
       <c r="R17" t="n">
-        <v>6374486</v>
+        <v>6374515</v>
       </c>
       <c r="S17" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2335,49 +2346,40 @@
           <t>2025-10-04</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>13:05</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-10-04</t>
         </is>
       </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>13:05</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kristian  Norrby</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kristian  Norrby</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128904395</v>
+        <v>128904192</v>
       </c>
       <c r="B18" t="n">
-        <v>92832</v>
+        <v>79739</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2385,33 +2387,25 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
@@ -2420,10 +2414,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>584177</v>
+        <v>584149</v>
       </c>
       <c r="R18" t="n">
-        <v>6374515</v>
+        <v>6374399</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2595,51 +2589,48 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128904192</v>
+        <v>128897118</v>
       </c>
       <c r="B20" t="n">
-        <v>79739</v>
+        <v>96228</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6453</v>
+        <v>2180</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Ekelund, Sm</t>
+          <t>Draggöl, Draggöl, Sm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>584149</v>
+        <v>584190</v>
       </c>
       <c r="R20" t="n">
-        <v>6374399</v>
+        <v>6374486</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2666,40 +2657,49 @@
           <t>2025-10-04</t>
         </is>
       </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-10-04</t>
         </is>
       </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Kristian  Norrby</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Kristian  Norrby</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128904088</v>
+        <v>128904443</v>
       </c>
       <c r="B21" t="n">
-        <v>79739</v>
+        <v>57713</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2707,26 +2707,35 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2734,10 +2743,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>584195</v>
+        <v>584113</v>
       </c>
       <c r="R21" t="n">
-        <v>6374314</v>
+        <v>6374565</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2778,7 +2787,6 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2898,10 +2906,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128904443</v>
+        <v>128904088</v>
       </c>
       <c r="B23" t="n">
-        <v>57713</v>
+        <v>79739</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2909,35 +2917,26 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -2945,10 +2944,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>584113</v>
+        <v>584195</v>
       </c>
       <c r="R23" t="n">
-        <v>6374565</v>
+        <v>6374314</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2989,6 +2988,7 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3796,10 +3796,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128904268</v>
+        <v>128904111</v>
       </c>
       <c r="B31" t="n">
-        <v>79739</v>
+        <v>57713</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3807,37 +3807,46 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Ekelund, Sm</t>
+          <t>E, Sm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>584121</v>
+        <v>584212</v>
       </c>
       <c r="R31" t="n">
-        <v>6374409</v>
+        <v>6374329</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3878,7 +3887,6 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -3897,10 +3905,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128904111</v>
+        <v>128904268</v>
       </c>
       <c r="B32" t="n">
-        <v>57713</v>
+        <v>79739</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3908,46 +3916,37 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>E, Sm</t>
+          <t>Ekelund, Sm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>584212</v>
+        <v>584121</v>
       </c>
       <c r="R32" t="n">
-        <v>6374329</v>
+        <v>6374409</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3988,6 +3987,7 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -4452,10 +4452,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128904124</v>
+        <v>128903739</v>
       </c>
       <c r="B37" t="n">
-        <v>92823</v>
+        <v>79739</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4463,19 +4463,24 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5449</v>
+        <v>6453</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Phellodon niger s.lat</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr"/>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
@@ -4485,10 +4490,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>584176</v>
+        <v>584164</v>
       </c>
       <c r="R37" t="n">
-        <v>6374554</v>
+        <v>6374477</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4518,9 +4523,19 @@
           <t>2025-10-04</t>
         </is>
       </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-10-04</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4548,10 +4563,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128903739</v>
+        <v>128903593</v>
       </c>
       <c r="B38" t="n">
-        <v>79739</v>
+        <v>92832</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4559,24 +4574,28 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
@@ -4586,10 +4605,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>584164</v>
+        <v>584200</v>
       </c>
       <c r="R38" t="n">
-        <v>6374477</v>
+        <v>6374370</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4659,7 +4678,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128903593</v>
+        <v>128904385</v>
       </c>
       <c r="B39" t="n">
         <v>92832</v>
@@ -4689,25 +4708,29 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr"/>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K39" t="inlineStr"/>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Draggöl, Stora Ramm, Sm</t>
+          <t>Ekelund, Sm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>584200</v>
+        <v>584207</v>
       </c>
       <c r="R39" t="n">
-        <v>6374370</v>
+        <v>6374488</v>
       </c>
       <c r="S39" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4734,19 +4757,9 @@
           <t>2025-10-04</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>10:30</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-10-04</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>15:00</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4762,19 +4775,19 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128904385</v>
+        <v>128904323</v>
       </c>
       <c r="B40" t="n">
         <v>92832</v>
@@ -4804,7 +4817,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -4820,10 +4833,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>584207</v>
+        <v>584175</v>
       </c>
       <c r="R40" t="n">
-        <v>6374488</v>
+        <v>6374451</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4883,59 +4896,48 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128904323</v>
+        <v>128897896</v>
       </c>
       <c r="B41" t="n">
-        <v>92832</v>
+        <v>96228</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5966</v>
+        <v>2180</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Ekelund, Sm</t>
+          <t>Draggöl, Draggöl, Sm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>584175</v>
+        <v>584067</v>
       </c>
       <c r="R41" t="n">
-        <v>6374451</v>
+        <v>6374669</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4962,37 +4964,46 @@
           <t>2025-10-04</t>
         </is>
       </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>13:31</t>
+        </is>
+      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-10-04</t>
         </is>
       </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>13:31</t>
+        </is>
+      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Kristian  Norrby</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Kristian  Norrby</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128897896</v>
+        <v>128897155</v>
       </c>
       <c r="B42" t="n">
         <v>96228</v>
@@ -5027,10 +5038,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>584067</v>
+        <v>584173</v>
       </c>
       <c r="R42" t="n">
-        <v>6374669</v>
+        <v>6374485</v>
       </c>
       <c r="S42" t="n">
         <v>2</v>
@@ -5062,7 +5073,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5072,7 +5083,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5099,32 +5110,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128897155</v>
+        <v>128897364</v>
       </c>
       <c r="B43" t="n">
-        <v>96228</v>
+        <v>92832</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>2180</v>
+        <v>5966</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5134,10 +5145,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>584173</v>
+        <v>584139</v>
       </c>
       <c r="R43" t="n">
-        <v>6374485</v>
+        <v>6374551</v>
       </c>
       <c r="S43" t="n">
         <v>2</v>
@@ -5169,7 +5180,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5179,7 +5190,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5313,7 +5324,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128897364</v>
+        <v>128903940</v>
       </c>
       <c r="B45" t="n">
         <v>92832</v>
@@ -5341,20 +5352,27 @@
           <t>(Schaeff.) Quél.</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr"/>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Draggöl, Draggöl, Sm</t>
+          <t>Draggöl, Stora Ramm, Sm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>584139</v>
+        <v>584166</v>
       </c>
       <c r="R45" t="n">
-        <v>6374551</v>
+        <v>6374449</v>
       </c>
       <c r="S45" t="n">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5383,7 +5401,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5393,7 +5411,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5402,28 +5420,29 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Kristian  Norrby</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Kristian  Norrby</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128903940</v>
+        <v>128903690</v>
       </c>
       <c r="B46" t="n">
-        <v>92832</v>
+        <v>79739</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5431,28 +5450,24 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
       <c r="N46" t="inlineStr"/>
@@ -5462,10 +5477,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>584166</v>
+        <v>584120</v>
       </c>
       <c r="R46" t="n">
-        <v>6374449</v>
+        <v>6374392</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -5535,7 +5550,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128903690</v>
+        <v>128903857</v>
       </c>
       <c r="B47" t="n">
         <v>79739</v>
@@ -5573,10 +5588,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>584120</v>
+        <v>584169</v>
       </c>
       <c r="R47" t="n">
-        <v>6374392</v>
+        <v>6374498</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -5646,7 +5661,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128903857</v>
+        <v>128904459</v>
       </c>
       <c r="B48" t="n">
         <v>79739</v>
@@ -5680,17 +5695,17 @@
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Draggöl, Stora Ramm, Sm</t>
+          <t>Ekelund, Sm</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>584169</v>
+        <v>584182</v>
       </c>
       <c r="R48" t="n">
-        <v>6374498</v>
+        <v>6374604</v>
       </c>
       <c r="S48" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5717,19 +5732,9 @@
           <t>2025-10-04</t>
         </is>
       </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>10:30</t>
-        </is>
-      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-10-04</t>
-        </is>
-      </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>15:00</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5745,19 +5750,19 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128904459</v>
+        <v>128903869</v>
       </c>
       <c r="B49" t="n">
         <v>79739</v>
@@ -5791,17 +5796,17 @@
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Ekelund, Sm</t>
+          <t>Draggöl, Stora Ramm, Sm</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>584182</v>
+        <v>584166</v>
       </c>
       <c r="R49" t="n">
-        <v>6374604</v>
+        <v>6374521</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5828,9 +5833,24 @@
           <t>2025-10-04</t>
         </is>
       </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-10-04</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Brandljud</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5846,22 +5866,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128903869</v>
+        <v>128909203</v>
       </c>
       <c r="B50" t="n">
-        <v>79739</v>
+        <v>79710</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5869,21 +5889,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5896,10 +5916,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>584166</v>
+        <v>584172</v>
       </c>
       <c r="R50" t="n">
-        <v>6374521</v>
+        <v>6374454</v>
       </c>
       <c r="S50" t="n">
         <v>25</v>
@@ -5931,7 +5951,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5942,11 +5962,6 @@
       <c r="AB50" t="inlineStr">
         <is>
           <t>15:00</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Brandljud</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5974,10 +5989,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128909203</v>
+        <v>128908556</v>
       </c>
       <c r="B51" t="n">
-        <v>79710</v>
+        <v>78877</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5985,21 +6000,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6012,10 +6027,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>584172</v>
+        <v>584169</v>
       </c>
       <c r="R51" t="n">
-        <v>6374454</v>
+        <v>6374498</v>
       </c>
       <c r="S51" t="n">
         <v>25</v>
@@ -6058,6 +6073,11 @@
       <c r="AB51" t="inlineStr">
         <is>
           <t>15:00</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Flera stubbar som hade brandljud men även stående tallar var skadade.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6085,10 +6105,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128908556</v>
+        <v>128908500</v>
       </c>
       <c r="B52" t="n">
-        <v>78877</v>
+        <v>92786</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6096,21 +6116,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6446</v>
+        <v>4361</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6123,10 +6143,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>584169</v>
+        <v>584161</v>
       </c>
       <c r="R52" t="n">
-        <v>6374498</v>
+        <v>6374352</v>
       </c>
       <c r="S52" t="n">
         <v>25</v>
@@ -6169,11 +6189,6 @@
       <c r="AB52" t="inlineStr">
         <is>
           <t>15:00</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Flera stubbar som hade brandljud men även stående tallar var skadade.</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6201,10 +6216,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128908500</v>
+        <v>128904124</v>
       </c>
       <c r="B53" t="n">
-        <v>92786</v>
+        <v>92820</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6212,24 +6227,28 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>4361</v>
+        <v>5448</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
+          <t>(Sw. ex Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr"/>
       <c r="N53" t="inlineStr"/>
@@ -6239,10 +6258,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>584161</v>
+        <v>584176</v>
       </c>
       <c r="R53" t="n">
-        <v>6374352</v>
+        <v>6374554</v>
       </c>
       <c r="S53" t="n">
         <v>25</v>
@@ -6272,19 +6291,9 @@
           <t>2025-10-04</t>
         </is>
       </c>
-      <c r="Z53" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-10-04</t>
-        </is>
-      </c>
-      <c r="AB53" t="inlineStr">
-        <is>
-          <t>15:00</t>
         </is>
       </c>
       <c r="AD53" t="b">

--- a/artfynd/A 45800-2025 artfynd.xlsx
+++ b/artfynd/A 45800-2025 artfynd.xlsx
@@ -2041,10 +2041,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128903951</v>
+        <v>128903544</v>
       </c>
       <c r="B15" t="n">
-        <v>92832</v>
+        <v>79743</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2052,28 +2052,24 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
@@ -2083,10 +2079,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>584183</v>
+        <v>584191</v>
       </c>
       <c r="R15" t="n">
-        <v>6374596</v>
+        <v>6374331</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2156,10 +2152,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128903544</v>
+        <v>128903951</v>
       </c>
       <c r="B16" t="n">
-        <v>79739</v>
+        <v>92836</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2167,24 +2163,28 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
@@ -2194,10 +2194,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>584191</v>
+        <v>584183</v>
       </c>
       <c r="R16" t="n">
-        <v>6374331</v>
+        <v>6374596</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2267,10 +2267,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128904395</v>
+        <v>128904192</v>
       </c>
       <c r="B17" t="n">
-        <v>92832</v>
+        <v>79743</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2278,33 +2278,25 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
@@ -2313,10 +2305,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>584177</v>
+        <v>584149</v>
       </c>
       <c r="R17" t="n">
-        <v>6374515</v>
+        <v>6374399</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2376,51 +2368,52 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128904192</v>
+        <v>128903715</v>
       </c>
       <c r="B18" t="n">
-        <v>79739</v>
+        <v>96232</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6453</v>
+        <v>2180</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Ekelund, Sm</t>
+          <t>Draggöl, Stora Ramm, Sm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>584149</v>
+        <v>584142</v>
       </c>
       <c r="R18" t="n">
-        <v>6374399</v>
+        <v>6374419</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2447,9 +2440,19 @@
           <t>2025-10-04</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-10-04</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2465,64 +2468,71 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128903715</v>
+        <v>128904395</v>
       </c>
       <c r="B19" t="n">
-        <v>96228</v>
+        <v>92836</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2180</v>
+        <v>5966</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Draggöl, Stora Ramm, Sm</t>
+          <t>Ekelund, Sm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>584142</v>
+        <v>584177</v>
       </c>
       <c r="R19" t="n">
-        <v>6374419</v>
+        <v>6374515</v>
       </c>
       <c r="S19" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2549,19 +2559,9 @@
           <t>2025-10-04</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>10:30</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-10-04</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>15:00</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2577,12 +2577,12 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
@@ -2592,7 +2592,7 @@
         <v>128897118</v>
       </c>
       <c r="B20" t="n">
-        <v>96228</v>
+        <v>96232</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2699,7 +2699,7 @@
         <v>128904443</v>
       </c>
       <c r="B21" t="n">
-        <v>57713</v>
+        <v>57717</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2808,7 +2808,7 @@
         <v>128904450</v>
       </c>
       <c r="B22" t="n">
-        <v>79739</v>
+        <v>79743</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2909,7 +2909,7 @@
         <v>128904088</v>
       </c>
       <c r="B23" t="n">
-        <v>79739</v>
+        <v>79743</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3010,7 +3010,7 @@
         <v>128903851</v>
       </c>
       <c r="B24" t="n">
-        <v>91524</v>
+        <v>91528</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3125,7 +3125,7 @@
         <v>128903521</v>
       </c>
       <c r="B25" t="n">
-        <v>58086</v>
+        <v>58090</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3244,7 +3244,7 @@
         <v>128895716</v>
       </c>
       <c r="B26" t="n">
-        <v>96228</v>
+        <v>96232</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3348,10 +3348,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128903578</v>
+        <v>128904268</v>
       </c>
       <c r="B27" t="n">
-        <v>92832</v>
+        <v>79743</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3359,44 +3359,40 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Draggöl, Stora Ramm, Sm</t>
+          <t>Ekelund, Sm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>584236</v>
+        <v>584121</v>
       </c>
       <c r="R27" t="n">
-        <v>6374327</v>
+        <v>6374409</v>
       </c>
       <c r="S27" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3423,19 +3419,9 @@
           <t>2025-10-04</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>10:30</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-10-04</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>15:00</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3451,22 +3437,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128904408</v>
+        <v>128903578</v>
       </c>
       <c r="B28" t="n">
-        <v>91524</v>
+        <v>92836</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3474,48 +3460,44 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5442</v>
+        <v>5966</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Ekelund, Sm</t>
+          <t>Draggöl, Stora Ramm, Sm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>584143</v>
+        <v>584236</v>
       </c>
       <c r="R28" t="n">
-        <v>6374517</v>
+        <v>6374327</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3542,9 +3524,19 @@
           <t>2025-10-04</t>
         </is>
       </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-10-04</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3560,12 +3552,12 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
@@ -3575,7 +3567,7 @@
         <v>128903661</v>
       </c>
       <c r="B29" t="n">
-        <v>92832</v>
+        <v>92836</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3687,10 +3679,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128904429</v>
+        <v>128904111</v>
       </c>
       <c r="B30" t="n">
-        <v>91524</v>
+        <v>57717</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3698,21 +3690,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -3720,23 +3712,24 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Ekelund, Sm</t>
+          <t>E, Sm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>584130</v>
+        <v>584212</v>
       </c>
       <c r="R30" t="n">
-        <v>6374515</v>
+        <v>6374329</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3777,7 +3770,6 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3796,10 +3788,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128904111</v>
+        <v>128904408</v>
       </c>
       <c r="B31" t="n">
-        <v>57713</v>
+        <v>91528</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3807,46 +3799,45 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>E, Sm</t>
+          <t>Ekelund, Sm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>584212</v>
+        <v>584143</v>
       </c>
       <c r="R31" t="n">
-        <v>6374329</v>
+        <v>6374517</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3887,6 +3878,7 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -3905,10 +3897,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128904268</v>
+        <v>128904429</v>
       </c>
       <c r="B32" t="n">
-        <v>79739</v>
+        <v>91528</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3916,25 +3908,33 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6453</v>
+        <v>5442</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
@@ -3943,10 +3943,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>584121</v>
+        <v>584130</v>
       </c>
       <c r="R32" t="n">
-        <v>6374409</v>
+        <v>6374515</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4009,7 +4009,7 @@
         <v>128903926</v>
       </c>
       <c r="B33" t="n">
-        <v>92832</v>
+        <v>92836</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4124,7 +4124,7 @@
         <v>128903960</v>
       </c>
       <c r="B34" t="n">
-        <v>92794</v>
+        <v>92798</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4239,7 +4239,7 @@
         <v>128904329</v>
       </c>
       <c r="B35" t="n">
-        <v>79739</v>
+        <v>79743</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4340,7 +4340,7 @@
         <v>128903654</v>
       </c>
       <c r="B36" t="n">
-        <v>92832</v>
+        <v>92836</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4455,7 +4455,7 @@
         <v>128903739</v>
       </c>
       <c r="B37" t="n">
-        <v>79739</v>
+        <v>79743</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4566,7 +4566,7 @@
         <v>128903593</v>
       </c>
       <c r="B38" t="n">
-        <v>92832</v>
+        <v>92836</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4681,7 +4681,7 @@
         <v>128904385</v>
       </c>
       <c r="B39" t="n">
-        <v>92832</v>
+        <v>92836</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4790,7 +4790,7 @@
         <v>128904323</v>
       </c>
       <c r="B40" t="n">
-        <v>92832</v>
+        <v>92836</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4899,7 +4899,7 @@
         <v>128897896</v>
       </c>
       <c r="B41" t="n">
-        <v>96228</v>
+        <v>96232</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5006,7 +5006,7 @@
         <v>128897155</v>
       </c>
       <c r="B42" t="n">
-        <v>96228</v>
+        <v>96232</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5113,7 +5113,7 @@
         <v>128897364</v>
       </c>
       <c r="B43" t="n">
-        <v>92832</v>
+        <v>92836</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5220,7 +5220,7 @@
         <v>128897073</v>
       </c>
       <c r="B44" t="n">
-        <v>79739</v>
+        <v>79743</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5324,10 +5324,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128903940</v>
+        <v>128903690</v>
       </c>
       <c r="B45" t="n">
-        <v>92832</v>
+        <v>79743</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5335,28 +5335,24 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
       <c r="N45" t="inlineStr"/>
@@ -5366,10 +5362,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>584166</v>
+        <v>584120</v>
       </c>
       <c r="R45" t="n">
-        <v>6374449</v>
+        <v>6374392</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -5439,10 +5435,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128903690</v>
+        <v>128903940</v>
       </c>
       <c r="B46" t="n">
-        <v>79739</v>
+        <v>92836</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5450,24 +5446,28 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
       <c r="N46" t="inlineStr"/>
@@ -5477,10 +5477,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>584120</v>
+        <v>584166</v>
       </c>
       <c r="R46" t="n">
-        <v>6374392</v>
+        <v>6374449</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -5553,7 +5553,7 @@
         <v>128903857</v>
       </c>
       <c r="B47" t="n">
-        <v>79739</v>
+        <v>79743</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5664,7 +5664,7 @@
         <v>128904459</v>
       </c>
       <c r="B48" t="n">
-        <v>79739</v>
+        <v>79743</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5765,7 +5765,7 @@
         <v>128903869</v>
       </c>
       <c r="B49" t="n">
-        <v>79739</v>
+        <v>79743</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5881,7 +5881,7 @@
         <v>128909203</v>
       </c>
       <c r="B50" t="n">
-        <v>79710</v>
+        <v>79714</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5992,7 +5992,7 @@
         <v>128908556</v>
       </c>
       <c r="B51" t="n">
-        <v>78877</v>
+        <v>78881</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6108,7 +6108,7 @@
         <v>128908500</v>
       </c>
       <c r="B52" t="n">
-        <v>92786</v>
+        <v>92790</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6219,7 +6219,7 @@
         <v>128904124</v>
       </c>
       <c r="B53" t="n">
-        <v>92820</v>
+        <v>92824</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>

--- a/artfynd/A 45800-2025 artfynd.xlsx
+++ b/artfynd/A 45800-2025 artfynd.xlsx
@@ -2696,10 +2696,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128904443</v>
+        <v>128904088</v>
       </c>
       <c r="B21" t="n">
-        <v>57717</v>
+        <v>79743</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2707,35 +2707,26 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2743,10 +2734,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>584113</v>
+        <v>584195</v>
       </c>
       <c r="R21" t="n">
-        <v>6374565</v>
+        <v>6374314</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2787,6 +2778,7 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2906,10 +2898,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128904088</v>
+        <v>128904443</v>
       </c>
       <c r="B23" t="n">
-        <v>79743</v>
+        <v>57717</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2917,26 +2909,35 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -2944,10 +2945,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>584195</v>
+        <v>584113</v>
       </c>
       <c r="R23" t="n">
-        <v>6374314</v>
+        <v>6374565</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2988,7 +2989,6 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3007,55 +3007,48 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128903851</v>
+        <v>128895716</v>
       </c>
       <c r="B24" t="n">
-        <v>91528</v>
+        <v>96232</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5442</v>
+        <v>2180</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Draggöl, Stora Ramm, Sm</t>
+          <t>Draggöl, Draggöl, Sm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>584167</v>
+        <v>584171</v>
       </c>
       <c r="R24" t="n">
-        <v>6374518</v>
+        <v>6374322</v>
       </c>
       <c r="S24" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3084,7 +3077,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3094,7 +3087,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3103,65 +3096,59 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128903521</v>
+        <v>128903851</v>
       </c>
       <c r="B25" t="n">
-        <v>58090</v>
+        <v>91528</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>103015</v>
+        <v>5442</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3169,10 +3156,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>584198</v>
+        <v>584167</v>
       </c>
       <c r="R25" t="n">
-        <v>6374339</v>
+        <v>6374518</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3223,6 +3210,7 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3241,10 +3229,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128895716</v>
+        <v>128903521</v>
       </c>
       <c r="B26" t="n">
-        <v>96232</v>
+        <v>58090</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3252,37 +3240,49 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2180</v>
+        <v>103015</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Draggöl, Draggöl, Sm</t>
+          <t>Draggöl, Stora Ramm, Sm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>584171</v>
+        <v>584198</v>
       </c>
       <c r="R26" t="n">
-        <v>6374322</v>
+        <v>6374339</v>
       </c>
       <c r="S26" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3311,7 +3311,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3336,22 +3336,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128904268</v>
+        <v>128904429</v>
       </c>
       <c r="B27" t="n">
-        <v>79743</v>
+        <v>91528</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3359,25 +3359,33 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6453</v>
+        <v>5442</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
@@ -3386,10 +3394,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>584121</v>
+        <v>584130</v>
       </c>
       <c r="R27" t="n">
-        <v>6374409</v>
+        <v>6374515</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3449,10 +3457,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128903578</v>
+        <v>128904268</v>
       </c>
       <c r="B28" t="n">
-        <v>92836</v>
+        <v>79743</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3460,44 +3468,40 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Draggöl, Stora Ramm, Sm</t>
+          <t>Ekelund, Sm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>584236</v>
+        <v>584121</v>
       </c>
       <c r="R28" t="n">
-        <v>6374327</v>
+        <v>6374409</v>
       </c>
       <c r="S28" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3524,19 +3528,9 @@
           <t>2025-10-04</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>10:30</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-10-04</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>15:00</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3552,19 +3546,19 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128903661</v>
+        <v>128903578</v>
       </c>
       <c r="B29" t="n">
         <v>92836</v>
@@ -3606,10 +3600,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>584164</v>
+        <v>584236</v>
       </c>
       <c r="R29" t="n">
-        <v>6374343</v>
+        <v>6374327</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3679,10 +3673,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128904111</v>
+        <v>128903661</v>
       </c>
       <c r="B30" t="n">
-        <v>57717</v>
+        <v>92836</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3690,49 +3684,44 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100049</v>
+        <v>5966</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>E, Sm</t>
+          <t>Draggöl, Stora Ramm, Sm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>584212</v>
+        <v>584164</v>
       </c>
       <c r="R30" t="n">
-        <v>6374329</v>
+        <v>6374343</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3759,29 +3748,40 @@
           <t>2025-10-04</t>
         </is>
       </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-10-04</t>
         </is>
       </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
@@ -3897,10 +3897,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128904429</v>
+        <v>128904111</v>
       </c>
       <c r="B32" t="n">
-        <v>91528</v>
+        <v>57717</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3908,21 +3908,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -3930,23 +3930,24 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Ekelund, Sm</t>
+          <t>E, Sm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>584130</v>
+        <v>584212</v>
       </c>
       <c r="R32" t="n">
-        <v>6374515</v>
+        <v>6374329</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3987,7 +3988,6 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -5110,10 +5110,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128897364</v>
+        <v>128897073</v>
       </c>
       <c r="B43" t="n">
-        <v>92836</v>
+        <v>79743</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5121,21 +5121,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5145,10 +5145,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>584139</v>
+        <v>584164</v>
       </c>
       <c r="R43" t="n">
-        <v>6374551</v>
+        <v>6374466</v>
       </c>
       <c r="S43" t="n">
         <v>2</v>
@@ -5180,7 +5180,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5190,7 +5190,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5217,10 +5217,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128897073</v>
+        <v>128897364</v>
       </c>
       <c r="B44" t="n">
-        <v>79743</v>
+        <v>92836</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5228,21 +5228,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5252,10 +5252,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>584164</v>
+        <v>584139</v>
       </c>
       <c r="R44" t="n">
-        <v>6374466</v>
+        <v>6374551</v>
       </c>
       <c r="S44" t="n">
         <v>2</v>
@@ -5287,7 +5287,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5297,7 +5297,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD44" t="b">

--- a/artfynd/A 45800-2025 artfynd.xlsx
+++ b/artfynd/A 45800-2025 artfynd.xlsx
@@ -2041,10 +2041,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128903544</v>
+        <v>128903951</v>
       </c>
       <c r="B15" t="n">
-        <v>79743</v>
+        <v>92836</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2052,24 +2052,28 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
@@ -2079,10 +2083,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>584191</v>
+        <v>584183</v>
       </c>
       <c r="R15" t="n">
-        <v>6374331</v>
+        <v>6374596</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2152,10 +2156,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128903951</v>
+        <v>128903544</v>
       </c>
       <c r="B16" t="n">
-        <v>92836</v>
+        <v>79743</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2163,28 +2167,24 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
@@ -2194,10 +2194,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>584183</v>
+        <v>584191</v>
       </c>
       <c r="R16" t="n">
-        <v>6374596</v>
+        <v>6374331</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2267,10 +2267,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128904192</v>
+        <v>128904395</v>
       </c>
       <c r="B17" t="n">
-        <v>79743</v>
+        <v>92836</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2278,25 +2278,33 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
@@ -2305,10 +2313,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>584149</v>
+        <v>584177</v>
       </c>
       <c r="R17" t="n">
-        <v>6374399</v>
+        <v>6374515</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2368,52 +2376,51 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128903715</v>
+        <v>128904192</v>
       </c>
       <c r="B18" t="n">
-        <v>96232</v>
+        <v>79743</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2180</v>
+        <v>6453</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Draggöl, Stora Ramm, Sm</t>
+          <t>Ekelund, Sm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>584142</v>
+        <v>584149</v>
       </c>
       <c r="R18" t="n">
-        <v>6374419</v>
+        <v>6374399</v>
       </c>
       <c r="S18" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2440,19 +2447,9 @@
           <t>2025-10-04</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>10:30</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-10-04</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>15:00</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2468,71 +2465,60 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128904395</v>
+        <v>128897118</v>
       </c>
       <c r="B19" t="n">
-        <v>92836</v>
+        <v>96232</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5966</v>
+        <v>2180</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Ekelund, Sm</t>
+          <t>Draggöl, Draggöl, Sm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>584177</v>
+        <v>584190</v>
       </c>
       <c r="R19" t="n">
-        <v>6374515</v>
+        <v>6374486</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2559,37 +2545,46 @@
           <t>2025-10-04</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-10-04</t>
         </is>
       </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Kristian  Norrby</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Kristian  Norrby</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128897118</v>
+        <v>128903715</v>
       </c>
       <c r="B20" t="n">
         <v>96232</v>
@@ -2618,19 +2613,23 @@
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Draggöl, Draggöl, Sm</t>
+          <t>Draggöl, Stora Ramm, Sm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>584190</v>
+        <v>584142</v>
       </c>
       <c r="R20" t="n">
-        <v>6374486</v>
+        <v>6374419</v>
       </c>
       <c r="S20" t="n">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2659,7 +2658,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2669,7 +2668,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2678,18 +2677,19 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Kristian  Norrby</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Kristian  Norrby</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -3348,10 +3348,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128904429</v>
+        <v>128904268</v>
       </c>
       <c r="B27" t="n">
-        <v>91528</v>
+        <v>79743</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3359,33 +3359,25 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5442</v>
+        <v>6453</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
@@ -3394,10 +3386,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>584130</v>
+        <v>584121</v>
       </c>
       <c r="R27" t="n">
-        <v>6374515</v>
+        <v>6374409</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3457,10 +3449,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128904268</v>
+        <v>128904111</v>
       </c>
       <c r="B28" t="n">
-        <v>79743</v>
+        <v>57717</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3468,37 +3460,46 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Ekelund, Sm</t>
+          <t>E, Sm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>584121</v>
+        <v>584212</v>
       </c>
       <c r="R28" t="n">
-        <v>6374409</v>
+        <v>6374329</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3539,7 +3540,6 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3897,10 +3897,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128904111</v>
+        <v>128904429</v>
       </c>
       <c r="B32" t="n">
-        <v>57717</v>
+        <v>91528</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3908,21 +3908,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -3930,24 +3930,23 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>E, Sm</t>
+          <t>Ekelund, Sm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>584212</v>
+        <v>584130</v>
       </c>
       <c r="R32" t="n">
-        <v>6374329</v>
+        <v>6374515</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3988,6 +3987,7 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -4787,59 +4787,48 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128904323</v>
+        <v>128897896</v>
       </c>
       <c r="B40" t="n">
-        <v>92836</v>
+        <v>96232</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5966</v>
+        <v>2180</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Ekelund, Sm</t>
+          <t>Draggöl, Draggöl, Sm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>584175</v>
+        <v>584067</v>
       </c>
       <c r="R40" t="n">
-        <v>6374451</v>
+        <v>6374669</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4866,78 +4855,98 @@
           <t>2025-10-04</t>
         </is>
       </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>13:31</t>
+        </is>
+      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-10-04</t>
         </is>
       </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>13:31</t>
+        </is>
+      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Kristian  Norrby</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Kristian  Norrby</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128897896</v>
+        <v>128904323</v>
       </c>
       <c r="B41" t="n">
-        <v>96232</v>
+        <v>92836</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>2180</v>
+        <v>5966</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Draggöl, Draggöl, Sm</t>
+          <t>Ekelund, Sm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>584067</v>
+        <v>584175</v>
       </c>
       <c r="R41" t="n">
-        <v>6374669</v>
+        <v>6374451</v>
       </c>
       <c r="S41" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4964,39 +4973,30 @@
           <t>2025-10-04</t>
         </is>
       </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>13:31</t>
-        </is>
-      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-10-04</t>
         </is>
       </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>13:31</t>
-        </is>
-      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Kristian  Norrby</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Kristian  Norrby</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
@@ -5324,10 +5324,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128903690</v>
+        <v>128903940</v>
       </c>
       <c r="B45" t="n">
-        <v>79743</v>
+        <v>92836</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5335,24 +5335,28 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
       <c r="N45" t="inlineStr"/>
@@ -5362,10 +5366,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>584120</v>
+        <v>584166</v>
       </c>
       <c r="R45" t="n">
-        <v>6374392</v>
+        <v>6374449</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -5435,10 +5439,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128903940</v>
+        <v>128903690</v>
       </c>
       <c r="B46" t="n">
-        <v>92836</v>
+        <v>79743</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5446,28 +5450,24 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
       <c r="N46" t="inlineStr"/>
@@ -5477,10 +5477,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>584166</v>
+        <v>584120</v>
       </c>
       <c r="R46" t="n">
-        <v>6374449</v>
+        <v>6374392</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>

--- a/artfynd/A 45800-2025 artfynd.xlsx
+++ b/artfynd/A 45800-2025 artfynd.xlsx
@@ -2044,7 +2044,7 @@
         <v>128903951</v>
       </c>
       <c r="B15" t="n">
-        <v>92836</v>
+        <v>92841</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2159,7 +2159,7 @@
         <v>128903544</v>
       </c>
       <c r="B16" t="n">
-        <v>79743</v>
+        <v>79648</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2267,10 +2267,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128904395</v>
+        <v>128904192</v>
       </c>
       <c r="B17" t="n">
-        <v>92836</v>
+        <v>79648</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2278,33 +2278,25 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
@@ -2313,10 +2305,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>584177</v>
+        <v>584149</v>
       </c>
       <c r="R17" t="n">
-        <v>6374515</v>
+        <v>6374399</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2376,51 +2368,52 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128904192</v>
+        <v>128903715</v>
       </c>
       <c r="B18" t="n">
-        <v>79743</v>
+        <v>96239</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6453</v>
+        <v>2180</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Ekelund, Sm</t>
+          <t>Draggöl, Stora Ramm, Sm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>584149</v>
+        <v>584142</v>
       </c>
       <c r="R18" t="n">
-        <v>6374399</v>
+        <v>6374419</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2447,9 +2440,19 @@
           <t>2025-10-04</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-10-04</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2465,12 +2468,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -2480,7 +2483,7 @@
         <v>128897118</v>
       </c>
       <c r="B19" t="n">
-        <v>96232</v>
+        <v>96239</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2584,52 +2587,59 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128903715</v>
+        <v>128904395</v>
       </c>
       <c r="B20" t="n">
-        <v>96232</v>
+        <v>92841</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2180</v>
+        <v>5966</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Draggöl, Stora Ramm, Sm</t>
+          <t>Ekelund, Sm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>584142</v>
+        <v>584177</v>
       </c>
       <c r="R20" t="n">
-        <v>6374419</v>
+        <v>6374515</v>
       </c>
       <c r="S20" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2656,19 +2666,9 @@
           <t>2025-10-04</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>10:30</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-10-04</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>15:00</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2684,12 +2684,12 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -2699,7 +2699,7 @@
         <v>128904088</v>
       </c>
       <c r="B21" t="n">
-        <v>79743</v>
+        <v>79648</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2800,7 +2800,7 @@
         <v>128904450</v>
       </c>
       <c r="B22" t="n">
-        <v>79743</v>
+        <v>79648</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2901,7 +2901,7 @@
         <v>128904443</v>
       </c>
       <c r="B23" t="n">
-        <v>57717</v>
+        <v>57720</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3007,48 +3007,55 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128895716</v>
+        <v>128903851</v>
       </c>
       <c r="B24" t="n">
-        <v>96232</v>
+        <v>91533</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2180</v>
+        <v>5442</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Draggöl, Draggöl, Sm</t>
+          <t>Draggöl, Stora Ramm, Sm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>584171</v>
+        <v>584167</v>
       </c>
       <c r="R24" t="n">
-        <v>6374322</v>
+        <v>6374518</v>
       </c>
       <c r="S24" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3077,7 +3084,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3087,7 +3094,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3096,59 +3103,65 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128903851</v>
+        <v>128903521</v>
       </c>
       <c r="B25" t="n">
-        <v>91528</v>
+        <v>58093</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5442</v>
+        <v>103015</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr"/>
+          <t>4</t>
+        </is>
+      </c>
       <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3156,10 +3169,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>584167</v>
+        <v>584198</v>
       </c>
       <c r="R25" t="n">
-        <v>6374518</v>
+        <v>6374339</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3210,7 +3223,6 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3229,10 +3241,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128903521</v>
+        <v>128895716</v>
       </c>
       <c r="B26" t="n">
-        <v>58090</v>
+        <v>96239</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3240,49 +3252,37 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>103015</v>
+        <v>2180</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr"/>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Draggöl, Stora Ramm, Sm</t>
+          <t>Draggöl, Draggöl, Sm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>584198</v>
+        <v>584171</v>
       </c>
       <c r="R26" t="n">
-        <v>6374339</v>
+        <v>6374322</v>
       </c>
       <c r="S26" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3311,7 +3311,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3336,12 +3336,12 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
@@ -3351,7 +3351,7 @@
         <v>128904268</v>
       </c>
       <c r="B27" t="n">
-        <v>79743</v>
+        <v>79648</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3452,7 +3452,7 @@
         <v>128904111</v>
       </c>
       <c r="B28" t="n">
-        <v>57717</v>
+        <v>57720</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3558,10 +3558,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128903578</v>
+        <v>128904408</v>
       </c>
       <c r="B29" t="n">
-        <v>92836</v>
+        <v>91533</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3569,44 +3569,48 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5966</v>
+        <v>5442</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Draggöl, Stora Ramm, Sm</t>
+          <t>Ekelund, Sm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>584236</v>
+        <v>584143</v>
       </c>
       <c r="R29" t="n">
-        <v>6374327</v>
+        <v>6374517</v>
       </c>
       <c r="S29" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3633,19 +3637,9 @@
           <t>2025-10-04</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>10:30</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-10-04</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>15:00</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3661,12 +3655,12 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
@@ -3676,7 +3670,7 @@
         <v>128903661</v>
       </c>
       <c r="B30" t="n">
-        <v>92836</v>
+        <v>92841</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3788,10 +3782,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128904408</v>
+        <v>128904429</v>
       </c>
       <c r="B31" t="n">
-        <v>91528</v>
+        <v>91533</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3818,7 +3812,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -3834,10 +3828,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>584143</v>
+        <v>584130</v>
       </c>
       <c r="R31" t="n">
-        <v>6374517</v>
+        <v>6374515</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3897,10 +3891,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128904429</v>
+        <v>128903578</v>
       </c>
       <c r="B32" t="n">
-        <v>91528</v>
+        <v>92841</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3908,48 +3902,44 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5442</v>
+        <v>5966</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Ekelund, Sm</t>
+          <t>Draggöl, Stora Ramm, Sm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>584130</v>
+        <v>584236</v>
       </c>
       <c r="R32" t="n">
-        <v>6374515</v>
+        <v>6374327</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3976,9 +3966,19 @@
           <t>2025-10-04</t>
         </is>
       </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-10-04</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3994,12 +3994,12 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
@@ -4009,7 +4009,7 @@
         <v>128903926</v>
       </c>
       <c r="B33" t="n">
-        <v>92836</v>
+        <v>92841</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4124,7 +4124,7 @@
         <v>128903960</v>
       </c>
       <c r="B34" t="n">
-        <v>92798</v>
+        <v>92803</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4239,7 +4239,7 @@
         <v>128904329</v>
       </c>
       <c r="B35" t="n">
-        <v>79743</v>
+        <v>79648</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4340,7 +4340,7 @@
         <v>128903654</v>
       </c>
       <c r="B36" t="n">
-        <v>92836</v>
+        <v>92841</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4455,7 +4455,7 @@
         <v>128903739</v>
       </c>
       <c r="B37" t="n">
-        <v>79743</v>
+        <v>79648</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4566,7 +4566,7 @@
         <v>128903593</v>
       </c>
       <c r="B38" t="n">
-        <v>92836</v>
+        <v>92841</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4681,7 +4681,7 @@
         <v>128904385</v>
       </c>
       <c r="B39" t="n">
-        <v>92836</v>
+        <v>92841</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4787,48 +4787,59 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128897896</v>
+        <v>128904323</v>
       </c>
       <c r="B40" t="n">
-        <v>96232</v>
+        <v>92841</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>2180</v>
+        <v>5966</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Draggöl, Draggöl, Sm</t>
+          <t>Ekelund, Sm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>584067</v>
+        <v>584175</v>
       </c>
       <c r="R40" t="n">
-        <v>6374669</v>
+        <v>6374451</v>
       </c>
       <c r="S40" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4855,98 +4866,78 @@
           <t>2025-10-04</t>
         </is>
       </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>13:31</t>
-        </is>
-      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-10-04</t>
         </is>
       </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>13:31</t>
-        </is>
-      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Kristian  Norrby</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Kristian  Norrby</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128904323</v>
+        <v>128897896</v>
       </c>
       <c r="B41" t="n">
-        <v>92836</v>
+        <v>96239</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5966</v>
+        <v>2180</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Ekelund, Sm</t>
+          <t>Draggöl, Draggöl, Sm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>584175</v>
+        <v>584067</v>
       </c>
       <c r="R41" t="n">
-        <v>6374451</v>
+        <v>6374669</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4973,30 +4964,39 @@
           <t>2025-10-04</t>
         </is>
       </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>13:31</t>
+        </is>
+      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-10-04</t>
         </is>
       </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>13:31</t>
+        </is>
+      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Kristian  Norrby</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Kristian  Norrby</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
@@ -5006,7 +5006,7 @@
         <v>128897155</v>
       </c>
       <c r="B42" t="n">
-        <v>96232</v>
+        <v>96239</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5110,10 +5110,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128897073</v>
+        <v>128897364</v>
       </c>
       <c r="B43" t="n">
-        <v>79743</v>
+        <v>92841</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5121,21 +5121,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5145,10 +5145,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>584164</v>
+        <v>584139</v>
       </c>
       <c r="R43" t="n">
-        <v>6374466</v>
+        <v>6374551</v>
       </c>
       <c r="S43" t="n">
         <v>2</v>
@@ -5180,7 +5180,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5190,7 +5190,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5217,10 +5217,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128897364</v>
+        <v>128897073</v>
       </c>
       <c r="B44" t="n">
-        <v>92836</v>
+        <v>79648</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5228,21 +5228,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5252,10 +5252,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>584139</v>
+        <v>584164</v>
       </c>
       <c r="R44" t="n">
-        <v>6374551</v>
+        <v>6374466</v>
       </c>
       <c r="S44" t="n">
         <v>2</v>
@@ -5287,7 +5287,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5297,7 +5297,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5327,7 +5327,7 @@
         <v>128903940</v>
       </c>
       <c r="B45" t="n">
-        <v>92836</v>
+        <v>92841</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5442,7 +5442,7 @@
         <v>128903690</v>
       </c>
       <c r="B46" t="n">
-        <v>79743</v>
+        <v>79648</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5553,7 +5553,7 @@
         <v>128903857</v>
       </c>
       <c r="B47" t="n">
-        <v>79743</v>
+        <v>79648</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5664,7 +5664,7 @@
         <v>128904459</v>
       </c>
       <c r="B48" t="n">
-        <v>79743</v>
+        <v>79648</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5765,7 +5765,7 @@
         <v>128903869</v>
       </c>
       <c r="B49" t="n">
-        <v>79743</v>
+        <v>79648</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5881,7 +5881,7 @@
         <v>128909203</v>
       </c>
       <c r="B50" t="n">
-        <v>79714</v>
+        <v>79619</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5992,7 +5992,7 @@
         <v>128908556</v>
       </c>
       <c r="B51" t="n">
-        <v>78881</v>
+        <v>78786</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6108,7 +6108,7 @@
         <v>128908500</v>
       </c>
       <c r="B52" t="n">
-        <v>92790</v>
+        <v>92795</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6219,7 +6219,7 @@
         <v>128904124</v>
       </c>
       <c r="B53" t="n">
-        <v>92824</v>
+        <v>92829</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>

--- a/artfynd/A 45800-2025 artfynd.xlsx
+++ b/artfynd/A 45800-2025 artfynd.xlsx
@@ -3007,10 +3007,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128903521</v>
+        <v>128895716</v>
       </c>
       <c r="B24" t="n">
-        <v>58093</v>
+        <v>96247</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3018,49 +3018,37 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>103015</v>
+        <v>2180</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr"/>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Draggöl, Stora Ramm, Sm</t>
+          <t>Draggöl, Draggöl, Sm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>584198</v>
+        <v>584171</v>
       </c>
       <c r="R24" t="n">
-        <v>6374339</v>
+        <v>6374322</v>
       </c>
       <c r="S24" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3089,7 +3077,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3099,7 +3087,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3114,60 +3102,67 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128895716</v>
+        <v>128903851</v>
       </c>
       <c r="B25" t="n">
-        <v>96247</v>
+        <v>91540</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2180</v>
+        <v>5442</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Draggöl, Draggöl, Sm</t>
+          <t>Draggöl, Stora Ramm, Sm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>584171</v>
+        <v>584167</v>
       </c>
       <c r="R25" t="n">
-        <v>6374322</v>
+        <v>6374518</v>
       </c>
       <c r="S25" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3196,7 +3191,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3206,7 +3201,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3215,59 +3210,65 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128903851</v>
+        <v>128903521</v>
       </c>
       <c r="B26" t="n">
-        <v>91540</v>
+        <v>58093</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5442</v>
+        <v>103015</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr"/>
+          <t>4</t>
+        </is>
+      </c>
       <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3275,10 +3276,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>584167</v>
+        <v>584198</v>
       </c>
       <c r="R26" t="n">
-        <v>6374518</v>
+        <v>6374339</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3329,7 +3330,6 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 45800-2025 artfynd.xlsx
+++ b/artfynd/A 45800-2025 artfynd.xlsx
@@ -2155,7 +2155,7 @@
         <v>128903951</v>
       </c>
       <c r="B16" t="n">
-        <v>92849</v>
+        <v>92854</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2368,10 +2368,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128897118</v>
+        <v>128903715</v>
       </c>
       <c r="B18" t="n">
-        <v>96247</v>
+        <v>96252</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2397,19 +2397,23 @@
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Draggöl, Draggöl, Sm</t>
+          <t>Draggöl, Stora Ramm, Sm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>584190</v>
+        <v>584142</v>
       </c>
       <c r="R18" t="n">
-        <v>6374486</v>
+        <v>6374419</v>
       </c>
       <c r="S18" t="n">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2438,7 +2442,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2448,7 +2452,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2457,70 +2461,78 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Kristian  Norrby</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kristian  Norrby</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128903715</v>
+        <v>128904395</v>
       </c>
       <c r="B19" t="n">
-        <v>96247</v>
+        <v>92854</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2180</v>
+        <v>5966</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Draggöl, Stora Ramm, Sm</t>
+          <t>Ekelund, Sm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>584142</v>
+        <v>584177</v>
       </c>
       <c r="R19" t="n">
-        <v>6374419</v>
+        <v>6374515</v>
       </c>
       <c r="S19" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2547,19 +2559,9 @@
           <t>2025-10-04</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>10:30</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-10-04</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>15:00</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2575,71 +2577,60 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128904395</v>
+        <v>128897118</v>
       </c>
       <c r="B20" t="n">
-        <v>92849</v>
+        <v>96252</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5966</v>
+        <v>2180</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Ekelund, Sm</t>
+          <t>Draggöl, Draggöl, Sm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>584177</v>
+        <v>584190</v>
       </c>
       <c r="R20" t="n">
-        <v>6374515</v>
+        <v>6374486</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2666,30 +2657,39 @@
           <t>2025-10-04</t>
         </is>
       </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-10-04</t>
         </is>
       </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Kristian  Norrby</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Kristian  Norrby</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -3010,7 +3010,7 @@
         <v>128895716</v>
       </c>
       <c r="B24" t="n">
-        <v>96247</v>
+        <v>96252</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3117,7 +3117,7 @@
         <v>128903851</v>
       </c>
       <c r="B25" t="n">
-        <v>91540</v>
+        <v>91543</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3351,7 +3351,7 @@
         <v>128903578</v>
       </c>
       <c r="B27" t="n">
-        <v>92849</v>
+        <v>92854</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3463,10 +3463,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128903661</v>
+        <v>128904408</v>
       </c>
       <c r="B28" t="n">
-        <v>92849</v>
+        <v>91543</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3474,44 +3474,48 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5966</v>
+        <v>5442</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Draggöl, Stora Ramm, Sm</t>
+          <t>Ekelund, Sm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>584164</v>
+        <v>584143</v>
       </c>
       <c r="R28" t="n">
-        <v>6374343</v>
+        <v>6374517</v>
       </c>
       <c r="S28" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3538,19 +3542,9 @@
           <t>2025-10-04</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>10:30</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-10-04</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>15:00</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3566,22 +3560,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128904111</v>
+        <v>128903661</v>
       </c>
       <c r="B29" t="n">
-        <v>57720</v>
+        <v>92854</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3589,49 +3583,44 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100049</v>
+        <v>5966</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>E, Sm</t>
+          <t>Draggöl, Stora Ramm, Sm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>584212</v>
+        <v>584164</v>
       </c>
       <c r="R29" t="n">
-        <v>6374329</v>
+        <v>6374343</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3658,39 +3647,50 @@
           <t>2025-10-04</t>
         </is>
       </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-10-04</t>
         </is>
       </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128904268</v>
+        <v>128904429</v>
       </c>
       <c r="B30" t="n">
-        <v>79653</v>
+        <v>91543</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3698,25 +3698,33 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6453</v>
+        <v>5442</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
@@ -3725,10 +3733,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>584121</v>
+        <v>584130</v>
       </c>
       <c r="R30" t="n">
-        <v>6374409</v>
+        <v>6374515</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3788,10 +3796,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128904408</v>
+        <v>128904268</v>
       </c>
       <c r="B31" t="n">
-        <v>91540</v>
+        <v>79653</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3799,33 +3807,25 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5442</v>
+        <v>6453</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
@@ -3834,10 +3834,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>584143</v>
+        <v>584121</v>
       </c>
       <c r="R31" t="n">
-        <v>6374517</v>
+        <v>6374409</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3897,10 +3897,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128904429</v>
+        <v>128904111</v>
       </c>
       <c r="B32" t="n">
-        <v>91540</v>
+        <v>57720</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3908,21 +3908,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -3930,23 +3930,24 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Ekelund, Sm</t>
+          <t>E, Sm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>584130</v>
+        <v>584212</v>
       </c>
       <c r="R32" t="n">
-        <v>6374515</v>
+        <v>6374329</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3987,7 +3988,6 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -4009,7 +4009,7 @@
         <v>128903926</v>
       </c>
       <c r="B33" t="n">
-        <v>92849</v>
+        <v>92854</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4124,7 +4124,7 @@
         <v>128903960</v>
       </c>
       <c r="B34" t="n">
-        <v>92811</v>
+        <v>92816</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4340,7 +4340,7 @@
         <v>128903654</v>
       </c>
       <c r="B36" t="n">
-        <v>92849</v>
+        <v>92854</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4566,7 +4566,7 @@
         <v>128903593</v>
       </c>
       <c r="B38" t="n">
-        <v>92849</v>
+        <v>92854</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4681,7 +4681,7 @@
         <v>128904385</v>
       </c>
       <c r="B39" t="n">
-        <v>92849</v>
+        <v>92854</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4790,7 +4790,7 @@
         <v>128897896</v>
       </c>
       <c r="B40" t="n">
-        <v>96247</v>
+        <v>96252</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4897,7 +4897,7 @@
         <v>128904323</v>
       </c>
       <c r="B41" t="n">
-        <v>92849</v>
+        <v>92854</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5006,7 +5006,7 @@
         <v>128897155</v>
       </c>
       <c r="B42" t="n">
-        <v>96247</v>
+        <v>96252</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5110,10 +5110,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128897073</v>
+        <v>128897364</v>
       </c>
       <c r="B43" t="n">
-        <v>79653</v>
+        <v>92854</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5121,21 +5121,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5145,10 +5145,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>584164</v>
+        <v>584139</v>
       </c>
       <c r="R43" t="n">
-        <v>6374466</v>
+        <v>6374551</v>
       </c>
       <c r="S43" t="n">
         <v>2</v>
@@ -5180,7 +5180,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5190,7 +5190,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5217,10 +5217,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128897364</v>
+        <v>128897073</v>
       </c>
       <c r="B44" t="n">
-        <v>92849</v>
+        <v>79653</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5228,21 +5228,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5252,10 +5252,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>584139</v>
+        <v>584164</v>
       </c>
       <c r="R44" t="n">
-        <v>6374551</v>
+        <v>6374466</v>
       </c>
       <c r="S44" t="n">
         <v>2</v>
@@ -5287,7 +5287,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5297,7 +5297,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5324,10 +5324,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128903690</v>
+        <v>128903940</v>
       </c>
       <c r="B45" t="n">
-        <v>79653</v>
+        <v>92854</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5335,24 +5335,28 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
       <c r="N45" t="inlineStr"/>
@@ -5362,10 +5366,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>584120</v>
+        <v>584166</v>
       </c>
       <c r="R45" t="n">
-        <v>6374392</v>
+        <v>6374449</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -5435,10 +5439,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128903940</v>
+        <v>128903690</v>
       </c>
       <c r="B46" t="n">
-        <v>92849</v>
+        <v>79653</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5446,28 +5450,24 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
       <c r="N46" t="inlineStr"/>
@@ -5477,10 +5477,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>584166</v>
+        <v>584120</v>
       </c>
       <c r="R46" t="n">
-        <v>6374449</v>
+        <v>6374392</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -6108,7 +6108,7 @@
         <v>128908500</v>
       </c>
       <c r="B52" t="n">
-        <v>92803</v>
+        <v>92808</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6219,7 +6219,7 @@
         <v>128904124</v>
       </c>
       <c r="B53" t="n">
-        <v>92837</v>
+        <v>92842</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>

--- a/artfynd/A 45800-2025 artfynd.xlsx
+++ b/artfynd/A 45800-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY53"/>
+  <dimension ref="A1:AY55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2044,7 +2044,7 @@
         <v>128903544</v>
       </c>
       <c r="B15" t="n">
-        <v>79653</v>
+        <v>79654</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2155,7 +2155,7 @@
         <v>128903951</v>
       </c>
       <c r="B16" t="n">
-        <v>92854</v>
+        <v>92857</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2267,51 +2267,52 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128904192</v>
+        <v>128903715</v>
       </c>
       <c r="B17" t="n">
-        <v>79653</v>
+        <v>96255</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6453</v>
+        <v>2180</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Ekelund, Sm</t>
+          <t>Draggöl, Stora Ramm, Sm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>584149</v>
+        <v>584142</v>
       </c>
       <c r="R17" t="n">
-        <v>6374399</v>
+        <v>6374419</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2338,9 +2339,19 @@
           <t>2025-10-04</t>
         </is>
       </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-10-04</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2356,64 +2367,71 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128903715</v>
+        <v>128904395</v>
       </c>
       <c r="B18" t="n">
-        <v>96252</v>
+        <v>92857</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2180</v>
+        <v>5966</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Draggöl, Stora Ramm, Sm</t>
+          <t>Ekelund, Sm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>584142</v>
+        <v>584177</v>
       </c>
       <c r="R18" t="n">
-        <v>6374419</v>
+        <v>6374515</v>
       </c>
       <c r="S18" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2440,19 +2458,9 @@
           <t>2025-10-04</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>10:30</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-10-04</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>15:00</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2468,22 +2476,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128904395</v>
+        <v>128904192</v>
       </c>
       <c r="B19" t="n">
-        <v>92854</v>
+        <v>79654</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2491,33 +2499,25 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
@@ -2526,10 +2526,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>584177</v>
+        <v>584149</v>
       </c>
       <c r="R19" t="n">
-        <v>6374515</v>
+        <v>6374399</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2592,7 +2592,7 @@
         <v>128897118</v>
       </c>
       <c r="B20" t="n">
-        <v>96252</v>
+        <v>96255</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2696,10 +2696,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128904088</v>
+        <v>128904443</v>
       </c>
       <c r="B21" t="n">
-        <v>79653</v>
+        <v>57720</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2707,26 +2707,35 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2734,10 +2743,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>584195</v>
+        <v>584113</v>
       </c>
       <c r="R21" t="n">
-        <v>6374314</v>
+        <v>6374565</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2778,7 +2787,6 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2797,10 +2805,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128904450</v>
+        <v>128904088</v>
       </c>
       <c r="B22" t="n">
-        <v>79653</v>
+        <v>79654</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2835,10 +2843,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>584145</v>
+        <v>584195</v>
       </c>
       <c r="R22" t="n">
-        <v>6374604</v>
+        <v>6374314</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2898,10 +2906,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128904443</v>
+        <v>128904450</v>
       </c>
       <c r="B23" t="n">
-        <v>57720</v>
+        <v>79654</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2909,35 +2917,26 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -2945,10 +2944,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>584113</v>
+        <v>584145</v>
       </c>
       <c r="R23" t="n">
-        <v>6374565</v>
+        <v>6374604</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2989,6 +2988,7 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3007,48 +3007,55 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128895716</v>
+        <v>128903851</v>
       </c>
       <c r="B24" t="n">
-        <v>96252</v>
+        <v>91546</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2180</v>
+        <v>5442</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Draggöl, Draggöl, Sm</t>
+          <t>Draggöl, Stora Ramm, Sm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>584171</v>
+        <v>584167</v>
       </c>
       <c r="R24" t="n">
-        <v>6374322</v>
+        <v>6374518</v>
       </c>
       <c r="S24" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3077,7 +3084,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3087,7 +3094,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3096,73 +3103,67 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128903851</v>
+        <v>128895716</v>
       </c>
       <c r="B25" t="n">
-        <v>91543</v>
+        <v>96255</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5442</v>
+        <v>2180</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Draggöl, Stora Ramm, Sm</t>
+          <t>Draggöl, Draggöl, Sm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>584167</v>
+        <v>584171</v>
       </c>
       <c r="R25" t="n">
-        <v>6374518</v>
+        <v>6374322</v>
       </c>
       <c r="S25" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3191,7 +3192,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3201,7 +3202,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3210,19 +3211,18 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
@@ -3348,10 +3348,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128903578</v>
+        <v>128904111</v>
       </c>
       <c r="B27" t="n">
-        <v>92854</v>
+        <v>57720</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3359,44 +3359,49 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5966</v>
+        <v>100049</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Draggöl, Stora Ramm, Sm</t>
+          <t>E, Sm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>584236</v>
+        <v>584212</v>
       </c>
       <c r="R27" t="n">
-        <v>6374327</v>
+        <v>6374329</v>
       </c>
       <c r="S27" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3423,40 +3428,29 @@
           <t>2025-10-04</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>10:30</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-10-04</t>
         </is>
       </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>15:00</t>
-        </is>
-      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
@@ -3466,7 +3460,7 @@
         <v>128904408</v>
       </c>
       <c r="B28" t="n">
-        <v>91543</v>
+        <v>91546</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3572,10 +3566,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128903661</v>
+        <v>128904429</v>
       </c>
       <c r="B29" t="n">
-        <v>92854</v>
+        <v>91546</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3583,44 +3577,48 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5966</v>
+        <v>5442</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Draggöl, Stora Ramm, Sm</t>
+          <t>Ekelund, Sm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>584164</v>
+        <v>584130</v>
       </c>
       <c r="R29" t="n">
-        <v>6374343</v>
+        <v>6374515</v>
       </c>
       <c r="S29" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3647,19 +3645,9 @@
           <t>2025-10-04</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>10:30</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-10-04</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>15:00</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3675,22 +3663,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128904429</v>
+        <v>128903578</v>
       </c>
       <c r="B30" t="n">
-        <v>91543</v>
+        <v>92857</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3698,48 +3686,44 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5442</v>
+        <v>5966</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Ekelund, Sm</t>
+          <t>Draggöl, Stora Ramm, Sm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>584130</v>
+        <v>584236</v>
       </c>
       <c r="R30" t="n">
-        <v>6374515</v>
+        <v>6374327</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3766,9 +3750,19 @@
           <t>2025-10-04</t>
         </is>
       </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-10-04</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3784,22 +3778,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128904268</v>
+        <v>128903661</v>
       </c>
       <c r="B31" t="n">
-        <v>79653</v>
+        <v>92857</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3807,40 +3801,44 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Ekelund, Sm</t>
+          <t>Draggöl, Stora Ramm, Sm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>584121</v>
+        <v>584164</v>
       </c>
       <c r="R31" t="n">
-        <v>6374409</v>
+        <v>6374343</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3867,9 +3865,19 @@
           <t>2025-10-04</t>
         </is>
       </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-10-04</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3885,22 +3893,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128904111</v>
+        <v>128904268</v>
       </c>
       <c r="B32" t="n">
-        <v>57720</v>
+        <v>79654</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3908,46 +3916,37 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>E, Sm</t>
+          <t>Ekelund, Sm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>584212</v>
+        <v>584121</v>
       </c>
       <c r="R32" t="n">
-        <v>6374329</v>
+        <v>6374409</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3988,6 +3987,7 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -4009,7 +4009,7 @@
         <v>128903926</v>
       </c>
       <c r="B33" t="n">
-        <v>92854</v>
+        <v>92857</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4124,7 +4124,7 @@
         <v>128903960</v>
       </c>
       <c r="B34" t="n">
-        <v>92816</v>
+        <v>92819</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4239,7 +4239,7 @@
         <v>128904329</v>
       </c>
       <c r="B35" t="n">
-        <v>79653</v>
+        <v>79654</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4340,7 +4340,7 @@
         <v>128903654</v>
       </c>
       <c r="B36" t="n">
-        <v>92854</v>
+        <v>92857</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4455,7 +4455,7 @@
         <v>128903739</v>
       </c>
       <c r="B37" t="n">
-        <v>79653</v>
+        <v>79654</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4566,7 +4566,7 @@
         <v>128903593</v>
       </c>
       <c r="B38" t="n">
-        <v>92854</v>
+        <v>92857</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4681,7 +4681,7 @@
         <v>128904385</v>
       </c>
       <c r="B39" t="n">
-        <v>92854</v>
+        <v>92857</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4787,48 +4787,59 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128897896</v>
+        <v>128904323</v>
       </c>
       <c r="B40" t="n">
-        <v>96252</v>
+        <v>92857</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>2180</v>
+        <v>5966</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Draggöl, Draggöl, Sm</t>
+          <t>Ekelund, Sm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>584067</v>
+        <v>584175</v>
       </c>
       <c r="R40" t="n">
-        <v>6374669</v>
+        <v>6374451</v>
       </c>
       <c r="S40" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4855,98 +4866,78 @@
           <t>2025-10-04</t>
         </is>
       </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>13:31</t>
-        </is>
-      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-10-04</t>
         </is>
       </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>13:31</t>
-        </is>
-      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Kristian  Norrby</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Kristian  Norrby</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128904323</v>
+        <v>128897896</v>
       </c>
       <c r="B41" t="n">
-        <v>92854</v>
+        <v>96255</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5966</v>
+        <v>2180</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Ekelund, Sm</t>
+          <t>Draggöl, Draggöl, Sm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>584175</v>
+        <v>584067</v>
       </c>
       <c r="R41" t="n">
-        <v>6374451</v>
+        <v>6374669</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4973,30 +4964,39 @@
           <t>2025-10-04</t>
         </is>
       </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>13:31</t>
+        </is>
+      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-10-04</t>
         </is>
       </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>13:31</t>
+        </is>
+      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Kristian  Norrby</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Kristian  Norrby</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
@@ -5006,7 +5006,7 @@
         <v>128897155</v>
       </c>
       <c r="B42" t="n">
-        <v>96252</v>
+        <v>96255</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5113,7 +5113,7 @@
         <v>128897364</v>
       </c>
       <c r="B43" t="n">
-        <v>92854</v>
+        <v>92857</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5220,7 +5220,7 @@
         <v>128897073</v>
       </c>
       <c r="B44" t="n">
-        <v>79653</v>
+        <v>79654</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5327,7 +5327,7 @@
         <v>128903940</v>
       </c>
       <c r="B45" t="n">
-        <v>92854</v>
+        <v>92857</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5442,7 +5442,7 @@
         <v>128903690</v>
       </c>
       <c r="B46" t="n">
-        <v>79653</v>
+        <v>79654</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5553,7 +5553,7 @@
         <v>128903857</v>
       </c>
       <c r="B47" t="n">
-        <v>79653</v>
+        <v>79654</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5664,7 +5664,7 @@
         <v>128904459</v>
       </c>
       <c r="B48" t="n">
-        <v>79653</v>
+        <v>79654</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5765,7 +5765,7 @@
         <v>128903869</v>
       </c>
       <c r="B49" t="n">
-        <v>79653</v>
+        <v>79654</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5881,7 +5881,7 @@
         <v>128909203</v>
       </c>
       <c r="B50" t="n">
-        <v>79624</v>
+        <v>79625</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5992,7 +5992,7 @@
         <v>128908556</v>
       </c>
       <c r="B51" t="n">
-        <v>78791</v>
+        <v>78792</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6108,7 +6108,7 @@
         <v>128908500</v>
       </c>
       <c r="B52" t="n">
-        <v>92808</v>
+        <v>92811</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6219,7 +6219,7 @@
         <v>128904124</v>
       </c>
       <c r="B53" t="n">
-        <v>92842</v>
+        <v>92845</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6318,6 +6318,216 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>129193511</v>
+      </c>
+      <c r="B54" t="n">
+        <v>91546</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Boda, Sm</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>584177</v>
+      </c>
+      <c r="R54" t="n">
+        <v>6374328</v>
+      </c>
+      <c r="S54" t="n">
+        <v>1</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Oskarshamn</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Misterhult</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2025-10-05</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2025-10-05</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF54" t="inlineStr"/>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Gunilla Rosendahl</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Gunilla Rosendahl</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>129193484</v>
+      </c>
+      <c r="B55" t="n">
+        <v>92819</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Boda, Sm</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>584189</v>
+      </c>
+      <c r="R55" t="n">
+        <v>6374573</v>
+      </c>
+      <c r="S55" t="n">
+        <v>1</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Oskarshamn</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Misterhult</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2025-10-05</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2025-10-05</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF55" t="inlineStr"/>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Gunilla Rosendahl</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Gunilla Rosendahl</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 45800-2025 artfynd.xlsx
+++ b/artfynd/A 45800-2025 artfynd.xlsx
@@ -2041,10 +2041,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128903544</v>
+        <v>128903951</v>
       </c>
       <c r="B15" t="n">
-        <v>79654</v>
+        <v>92857</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2052,24 +2052,28 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
@@ -2079,10 +2083,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>584191</v>
+        <v>584183</v>
       </c>
       <c r="R15" t="n">
-        <v>6374331</v>
+        <v>6374596</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2152,10 +2156,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128903951</v>
+        <v>128903544</v>
       </c>
       <c r="B16" t="n">
-        <v>92857</v>
+        <v>79654</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2163,28 +2167,24 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
@@ -2194,10 +2194,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>584183</v>
+        <v>584191</v>
       </c>
       <c r="R16" t="n">
-        <v>6374596</v>
+        <v>6374331</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2267,52 +2267,51 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128903715</v>
+        <v>128904192</v>
       </c>
       <c r="B17" t="n">
-        <v>96255</v>
+        <v>79654</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2180</v>
+        <v>6453</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Draggöl, Stora Ramm, Sm</t>
+          <t>Ekelund, Sm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>584142</v>
+        <v>584149</v>
       </c>
       <c r="R17" t="n">
-        <v>6374419</v>
+        <v>6374399</v>
       </c>
       <c r="S17" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2339,19 +2338,9 @@
           <t>2025-10-04</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>10:30</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-10-04</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>15:00</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2367,71 +2356,60 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128904395</v>
+        <v>128897118</v>
       </c>
       <c r="B18" t="n">
-        <v>92857</v>
+        <v>96255</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5966</v>
+        <v>2180</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Ekelund, Sm</t>
+          <t>Draggöl, Draggöl, Sm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>584177</v>
+        <v>584190</v>
       </c>
       <c r="R18" t="n">
-        <v>6374515</v>
+        <v>6374486</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2458,81 +2436,91 @@
           <t>2025-10-04</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-10-04</t>
         </is>
       </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Kristian  Norrby</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Kristian  Norrby</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128904192</v>
+        <v>128903715</v>
       </c>
       <c r="B19" t="n">
-        <v>79654</v>
+        <v>96255</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6453</v>
+        <v>2180</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Ekelund, Sm</t>
+          <t>Draggöl, Stora Ramm, Sm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>584149</v>
+        <v>584142</v>
       </c>
       <c r="R19" t="n">
-        <v>6374399</v>
+        <v>6374419</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2559,9 +2547,19 @@
           <t>2025-10-04</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-10-04</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2577,60 +2575,71 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128897118</v>
+        <v>128904395</v>
       </c>
       <c r="B20" t="n">
-        <v>96255</v>
+        <v>92857</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2180</v>
+        <v>5966</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Draggöl, Draggöl, Sm</t>
+          <t>Ekelund, Sm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>584190</v>
+        <v>584177</v>
       </c>
       <c r="R20" t="n">
-        <v>6374486</v>
+        <v>6374515</v>
       </c>
       <c r="S20" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2657,39 +2666,30 @@
           <t>2025-10-04</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>13:05</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-10-04</t>
         </is>
       </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>13:05</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Kristian  Norrby</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Kristian  Norrby</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -3007,41 +3007,46 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128903851</v>
+        <v>128903521</v>
       </c>
       <c r="B24" t="n">
-        <v>91546</v>
+        <v>58093</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5442</v>
+        <v>103015</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr"/>
+          <t>4</t>
+        </is>
+      </c>
       <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3049,10 +3054,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>584167</v>
+        <v>584198</v>
       </c>
       <c r="R24" t="n">
-        <v>6374518</v>
+        <v>6374339</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3103,7 +3108,6 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3122,48 +3126,55 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128895716</v>
+        <v>128903851</v>
       </c>
       <c r="B25" t="n">
-        <v>96255</v>
+        <v>91546</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2180</v>
+        <v>5442</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Draggöl, Draggöl, Sm</t>
+          <t>Draggöl, Stora Ramm, Sm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>584171</v>
+        <v>584167</v>
       </c>
       <c r="R25" t="n">
-        <v>6374322</v>
+        <v>6374518</v>
       </c>
       <c r="S25" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3192,7 +3203,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3202,7 +3213,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3211,28 +3222,29 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128903521</v>
+        <v>128895716</v>
       </c>
       <c r="B26" t="n">
-        <v>58093</v>
+        <v>96255</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3240,49 +3252,37 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>103015</v>
+        <v>2180</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr"/>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Draggöl, Stora Ramm, Sm</t>
+          <t>Draggöl, Draggöl, Sm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>584198</v>
+        <v>584171</v>
       </c>
       <c r="R26" t="n">
-        <v>6374339</v>
+        <v>6374322</v>
       </c>
       <c r="S26" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3311,7 +3311,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3336,12 +3336,12 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
@@ -3457,10 +3457,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128904408</v>
+        <v>128903578</v>
       </c>
       <c r="B28" t="n">
-        <v>91546</v>
+        <v>92857</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3468,48 +3468,44 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5442</v>
+        <v>5966</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Ekelund, Sm</t>
+          <t>Draggöl, Stora Ramm, Sm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>584143</v>
+        <v>584236</v>
       </c>
       <c r="R28" t="n">
-        <v>6374517</v>
+        <v>6374327</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3536,9 +3532,19 @@
           <t>2025-10-04</t>
         </is>
       </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-10-04</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3554,19 +3560,19 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128904429</v>
+        <v>128904408</v>
       </c>
       <c r="B29" t="n">
         <v>91546</v>
@@ -3596,7 +3602,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -3612,10 +3618,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>584130</v>
+        <v>584143</v>
       </c>
       <c r="R29" t="n">
-        <v>6374515</v>
+        <v>6374517</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3675,7 +3681,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128903578</v>
+        <v>128903661</v>
       </c>
       <c r="B30" t="n">
         <v>92857</v>
@@ -3717,10 +3723,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>584236</v>
+        <v>584164</v>
       </c>
       <c r="R30" t="n">
-        <v>6374327</v>
+        <v>6374343</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3790,10 +3796,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128903661</v>
+        <v>128904429</v>
       </c>
       <c r="B31" t="n">
-        <v>92857</v>
+        <v>91546</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3801,44 +3807,48 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5966</v>
+        <v>5442</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Draggöl, Stora Ramm, Sm</t>
+          <t>Ekelund, Sm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>584164</v>
+        <v>584130</v>
       </c>
       <c r="R31" t="n">
-        <v>6374343</v>
+        <v>6374515</v>
       </c>
       <c r="S31" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3865,19 +3875,9 @@
           <t>2025-10-04</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>10:30</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-10-04</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>15:00</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3893,12 +3893,12 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>

--- a/artfynd/A 45800-2025 artfynd.xlsx
+++ b/artfynd/A 45800-2025 artfynd.xlsx
@@ -2267,51 +2267,52 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128904192</v>
+        <v>128903715</v>
       </c>
       <c r="B17" t="n">
-        <v>79654</v>
+        <v>96255</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6453</v>
+        <v>2180</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Ekelund, Sm</t>
+          <t>Draggöl, Stora Ramm, Sm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>584149</v>
+        <v>584142</v>
       </c>
       <c r="R17" t="n">
-        <v>6374399</v>
+        <v>6374419</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2338,9 +2339,19 @@
           <t>2025-10-04</t>
         </is>
       </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-10-04</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2356,60 +2367,71 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128897118</v>
+        <v>128904395</v>
       </c>
       <c r="B18" t="n">
-        <v>96255</v>
+        <v>92857</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2180</v>
+        <v>5966</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Draggöl, Draggöl, Sm</t>
+          <t>Ekelund, Sm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>584190</v>
+        <v>584177</v>
       </c>
       <c r="R18" t="n">
-        <v>6374486</v>
+        <v>6374515</v>
       </c>
       <c r="S18" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2436,91 +2458,81 @@
           <t>2025-10-04</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>13:05</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-10-04</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>13:05</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Kristian  Norrby</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kristian  Norrby</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128903715</v>
+        <v>128904192</v>
       </c>
       <c r="B19" t="n">
-        <v>96255</v>
+        <v>79654</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2180</v>
+        <v>6453</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Draggöl, Stora Ramm, Sm</t>
+          <t>Ekelund, Sm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>584142</v>
+        <v>584149</v>
       </c>
       <c r="R19" t="n">
-        <v>6374419</v>
+        <v>6374399</v>
       </c>
       <c r="S19" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2547,19 +2559,9 @@
           <t>2025-10-04</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>10:30</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-10-04</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>15:00</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2575,71 +2577,60 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128904395</v>
+        <v>128897118</v>
       </c>
       <c r="B20" t="n">
-        <v>92857</v>
+        <v>96255</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5966</v>
+        <v>2180</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Ekelund, Sm</t>
+          <t>Draggöl, Draggöl, Sm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>584177</v>
+        <v>584190</v>
       </c>
       <c r="R20" t="n">
-        <v>6374515</v>
+        <v>6374486</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2666,40 +2657,49 @@
           <t>2025-10-04</t>
         </is>
       </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-10-04</t>
         </is>
       </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Kristian  Norrby</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Kristian  Norrby</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128904443</v>
+        <v>128904088</v>
       </c>
       <c r="B21" t="n">
-        <v>57720</v>
+        <v>79654</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2707,35 +2707,26 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2743,10 +2734,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>584113</v>
+        <v>584195</v>
       </c>
       <c r="R21" t="n">
-        <v>6374565</v>
+        <v>6374314</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2787,6 +2778,7 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2805,7 +2797,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128904088</v>
+        <v>128904450</v>
       </c>
       <c r="B22" t="n">
         <v>79654</v>
@@ -2843,10 +2835,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>584195</v>
+        <v>584145</v>
       </c>
       <c r="R22" t="n">
-        <v>6374314</v>
+        <v>6374604</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2906,10 +2898,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128904450</v>
+        <v>128904443</v>
       </c>
       <c r="B23" t="n">
-        <v>79654</v>
+        <v>57720</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2917,26 +2909,35 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -2944,10 +2945,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>584145</v>
+        <v>584113</v>
       </c>
       <c r="R23" t="n">
-        <v>6374604</v>
+        <v>6374565</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2988,7 +2989,6 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3348,10 +3348,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128904111</v>
+        <v>128904268</v>
       </c>
       <c r="B27" t="n">
-        <v>57720</v>
+        <v>79654</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3359,46 +3359,37 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>E, Sm</t>
+          <t>Ekelund, Sm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>584212</v>
+        <v>584121</v>
       </c>
       <c r="R27" t="n">
-        <v>6374329</v>
+        <v>6374409</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3439,6 +3430,7 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3457,10 +3449,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128903578</v>
+        <v>128904111</v>
       </c>
       <c r="B28" t="n">
-        <v>92857</v>
+        <v>57720</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3468,44 +3460,49 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5966</v>
+        <v>100049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Draggöl, Stora Ramm, Sm</t>
+          <t>E, Sm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>584236</v>
+        <v>584212</v>
       </c>
       <c r="R28" t="n">
-        <v>6374327</v>
+        <v>6374329</v>
       </c>
       <c r="S28" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3532,50 +3529,39 @@
           <t>2025-10-04</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>10:30</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-10-04</t>
         </is>
       </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>15:00</t>
-        </is>
-      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128904408</v>
+        <v>128903578</v>
       </c>
       <c r="B29" t="n">
-        <v>91546</v>
+        <v>92857</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3583,48 +3569,44 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5442</v>
+        <v>5966</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Ekelund, Sm</t>
+          <t>Draggöl, Stora Ramm, Sm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>584143</v>
+        <v>584236</v>
       </c>
       <c r="R29" t="n">
-        <v>6374517</v>
+        <v>6374327</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3651,9 +3633,19 @@
           <t>2025-10-04</t>
         </is>
       </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-10-04</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3669,22 +3661,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128903661</v>
+        <v>128904408</v>
       </c>
       <c r="B30" t="n">
-        <v>92857</v>
+        <v>91546</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3692,44 +3684,48 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5966</v>
+        <v>5442</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Draggöl, Stora Ramm, Sm</t>
+          <t>Ekelund, Sm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>584164</v>
+        <v>584143</v>
       </c>
       <c r="R30" t="n">
-        <v>6374343</v>
+        <v>6374517</v>
       </c>
       <c r="S30" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3756,19 +3752,9 @@
           <t>2025-10-04</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>10:30</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-10-04</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>15:00</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3784,22 +3770,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128904429</v>
+        <v>128903661</v>
       </c>
       <c r="B31" t="n">
-        <v>91546</v>
+        <v>92857</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3807,48 +3793,44 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5442</v>
+        <v>5966</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Ekelund, Sm</t>
+          <t>Draggöl, Stora Ramm, Sm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>584130</v>
+        <v>584164</v>
       </c>
       <c r="R31" t="n">
-        <v>6374515</v>
+        <v>6374343</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3875,9 +3857,19 @@
           <t>2025-10-04</t>
         </is>
       </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-10-04</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3893,22 +3885,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128904268</v>
+        <v>128904429</v>
       </c>
       <c r="B32" t="n">
-        <v>79654</v>
+        <v>91546</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3916,25 +3908,33 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6453</v>
+        <v>5442</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
@@ -3943,10 +3943,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>584121</v>
+        <v>584130</v>
       </c>
       <c r="R32" t="n">
-        <v>6374409</v>
+        <v>6374515</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>

--- a/artfynd/A 45800-2025 artfynd.xlsx
+++ b/artfynd/A 45800-2025 artfynd.xlsx
@@ -2041,10 +2041,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128903951</v>
+        <v>128903544</v>
       </c>
       <c r="B15" t="n">
-        <v>92857</v>
+        <v>79654</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2052,28 +2052,24 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
@@ -2083,10 +2079,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>584183</v>
+        <v>584191</v>
       </c>
       <c r="R15" t="n">
-        <v>6374596</v>
+        <v>6374331</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2156,10 +2152,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128903544</v>
+        <v>128903951</v>
       </c>
       <c r="B16" t="n">
-        <v>79654</v>
+        <v>92857</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2167,24 +2163,28 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
@@ -2194,10 +2194,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>584191</v>
+        <v>584183</v>
       </c>
       <c r="R16" t="n">
-        <v>6374331</v>
+        <v>6374596</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2267,7 +2267,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128903715</v>
+        <v>128897118</v>
       </c>
       <c r="B17" t="n">
         <v>96255</v>
@@ -2296,23 +2296,19 @@
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Draggöl, Stora Ramm, Sm</t>
+          <t>Draggöl, Draggöl, Sm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>584142</v>
+        <v>584190</v>
       </c>
       <c r="R17" t="n">
-        <v>6374419</v>
+        <v>6374486</v>
       </c>
       <c r="S17" t="n">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2341,7 +2337,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2351,7 +2347,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2360,78 +2356,70 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Kristian  Norrby</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Kristian  Norrby</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128904395</v>
+        <v>128903715</v>
       </c>
       <c r="B18" t="n">
-        <v>92857</v>
+        <v>96255</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5966</v>
+        <v>2180</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Ekelund, Sm</t>
+          <t>Draggöl, Stora Ramm, Sm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>584177</v>
+        <v>584142</v>
       </c>
       <c r="R18" t="n">
-        <v>6374515</v>
+        <v>6374419</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2458,9 +2446,19 @@
           <t>2025-10-04</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-10-04</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2476,12 +2474,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -2589,48 +2587,59 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128897118</v>
+        <v>128904395</v>
       </c>
       <c r="B20" t="n">
-        <v>96255</v>
+        <v>92857</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2180</v>
+        <v>5966</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Draggöl, Draggöl, Sm</t>
+          <t>Ekelund, Sm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>584190</v>
+        <v>584177</v>
       </c>
       <c r="R20" t="n">
-        <v>6374486</v>
+        <v>6374515</v>
       </c>
       <c r="S20" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2657,46 +2666,37 @@
           <t>2025-10-04</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>13:05</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-10-04</t>
         </is>
       </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>13:05</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Kristian  Norrby</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Kristian  Norrby</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128904088</v>
+        <v>128904450</v>
       </c>
       <c r="B21" t="n">
         <v>79654</v>
@@ -2734,10 +2734,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>584195</v>
+        <v>584145</v>
       </c>
       <c r="R21" t="n">
-        <v>6374314</v>
+        <v>6374604</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2797,7 +2797,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128904450</v>
+        <v>128904088</v>
       </c>
       <c r="B22" t="n">
         <v>79654</v>
@@ -2835,10 +2835,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>584145</v>
+        <v>584195</v>
       </c>
       <c r="R22" t="n">
-        <v>6374604</v>
+        <v>6374314</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3449,10 +3449,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128904111</v>
+        <v>128903578</v>
       </c>
       <c r="B28" t="n">
-        <v>57720</v>
+        <v>92857</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3460,49 +3460,44 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100049</v>
+        <v>5966</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>E, Sm</t>
+          <t>Draggöl, Stora Ramm, Sm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>584212</v>
+        <v>584236</v>
       </c>
       <c r="R28" t="n">
-        <v>6374329</v>
+        <v>6374327</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3529,36 +3524,47 @@
           <t>2025-10-04</t>
         </is>
       </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-10-04</t>
         </is>
       </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128903578</v>
+        <v>128903661</v>
       </c>
       <c r="B29" t="n">
         <v>92857</v>
@@ -3600,10 +3606,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>584236</v>
+        <v>584164</v>
       </c>
       <c r="R29" t="n">
-        <v>6374327</v>
+        <v>6374343</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3782,10 +3788,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128903661</v>
+        <v>128904429</v>
       </c>
       <c r="B31" t="n">
-        <v>92857</v>
+        <v>91546</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3793,44 +3799,48 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5966</v>
+        <v>5442</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Draggöl, Stora Ramm, Sm</t>
+          <t>Ekelund, Sm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>584164</v>
+        <v>584130</v>
       </c>
       <c r="R31" t="n">
-        <v>6374343</v>
+        <v>6374515</v>
       </c>
       <c r="S31" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3857,19 +3867,9 @@
           <t>2025-10-04</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>10:30</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-10-04</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>15:00</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3885,22 +3885,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128904429</v>
+        <v>128904111</v>
       </c>
       <c r="B32" t="n">
-        <v>91546</v>
+        <v>57720</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3908,21 +3908,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -3930,23 +3930,24 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Ekelund, Sm</t>
+          <t>E, Sm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>584130</v>
+        <v>584212</v>
       </c>
       <c r="R32" t="n">
-        <v>6374515</v>
+        <v>6374329</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3987,7 +3988,6 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -4787,59 +4787,48 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128904323</v>
+        <v>128897896</v>
       </c>
       <c r="B40" t="n">
-        <v>92857</v>
+        <v>96255</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5966</v>
+        <v>2180</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Ekelund, Sm</t>
+          <t>Draggöl, Draggöl, Sm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>584175</v>
+        <v>584067</v>
       </c>
       <c r="R40" t="n">
-        <v>6374451</v>
+        <v>6374669</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4866,78 +4855,98 @@
           <t>2025-10-04</t>
         </is>
       </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>13:31</t>
+        </is>
+      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-10-04</t>
         </is>
       </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>13:31</t>
+        </is>
+      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Kristian  Norrby</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Kristian  Norrby</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128897896</v>
+        <v>128904323</v>
       </c>
       <c r="B41" t="n">
-        <v>96255</v>
+        <v>92857</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>2180</v>
+        <v>5966</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Draggöl, Draggöl, Sm</t>
+          <t>Ekelund, Sm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>584067</v>
+        <v>584175</v>
       </c>
       <c r="R41" t="n">
-        <v>6374669</v>
+        <v>6374451</v>
       </c>
       <c r="S41" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4964,39 +4973,30 @@
           <t>2025-10-04</t>
         </is>
       </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>13:31</t>
-        </is>
-      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-10-04</t>
         </is>
       </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>13:31</t>
-        </is>
-      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Kristian  Norrby</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Kristian  Norrby</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
@@ -5324,10 +5324,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128903940</v>
+        <v>128903690</v>
       </c>
       <c r="B45" t="n">
-        <v>92857</v>
+        <v>79654</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5335,28 +5335,24 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
       <c r="N45" t="inlineStr"/>
@@ -5366,10 +5362,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>584166</v>
+        <v>584120</v>
       </c>
       <c r="R45" t="n">
-        <v>6374449</v>
+        <v>6374392</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -5439,10 +5435,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128903690</v>
+        <v>128903940</v>
       </c>
       <c r="B46" t="n">
-        <v>79654</v>
+        <v>92857</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5450,24 +5446,28 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
       <c r="N46" t="inlineStr"/>
@@ -5477,10 +5477,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>584120</v>
+        <v>584166</v>
       </c>
       <c r="R46" t="n">
-        <v>6374392</v>
+        <v>6374449</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>

--- a/artfynd/A 45800-2025 artfynd.xlsx
+++ b/artfynd/A 45800-2025 artfynd.xlsx
@@ -2041,10 +2041,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128903544</v>
+        <v>128903951</v>
       </c>
       <c r="B15" t="n">
-        <v>79654</v>
+        <v>92864</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2052,24 +2052,28 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
@@ -2079,10 +2083,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>584191</v>
+        <v>584183</v>
       </c>
       <c r="R15" t="n">
-        <v>6374331</v>
+        <v>6374596</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2152,10 +2156,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128903951</v>
+        <v>128903544</v>
       </c>
       <c r="B16" t="n">
-        <v>92857</v>
+        <v>79658</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2163,28 +2167,24 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
@@ -2194,10 +2194,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>584183</v>
+        <v>584191</v>
       </c>
       <c r="R16" t="n">
-        <v>6374596</v>
+        <v>6374331</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2267,10 +2267,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128897118</v>
+        <v>128903715</v>
       </c>
       <c r="B17" t="n">
-        <v>96255</v>
+        <v>96265</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2296,19 +2296,23 @@
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Draggöl, Draggöl, Sm</t>
+          <t>Draggöl, Stora Ramm, Sm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>584190</v>
+        <v>584142</v>
       </c>
       <c r="R17" t="n">
-        <v>6374486</v>
+        <v>6374419</v>
       </c>
       <c r="S17" t="n">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2337,7 +2341,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2347,7 +2351,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2356,70 +2360,78 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kristian  Norrby</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kristian  Norrby</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128903715</v>
+        <v>128904395</v>
       </c>
       <c r="B18" t="n">
-        <v>96255</v>
+        <v>92864</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2180</v>
+        <v>5966</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Draggöl, Stora Ramm, Sm</t>
+          <t>Ekelund, Sm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>584142</v>
+        <v>584177</v>
       </c>
       <c r="R18" t="n">
-        <v>6374419</v>
+        <v>6374515</v>
       </c>
       <c r="S18" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2446,19 +2458,9 @@
           <t>2025-10-04</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>10:30</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-10-04</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>15:00</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2474,12 +2476,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -2489,7 +2491,7 @@
         <v>128904192</v>
       </c>
       <c r="B19" t="n">
-        <v>79654</v>
+        <v>79658</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2587,59 +2589,48 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128904395</v>
+        <v>128897118</v>
       </c>
       <c r="B20" t="n">
-        <v>92857</v>
+        <v>96265</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5966</v>
+        <v>2180</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Ekelund, Sm</t>
+          <t>Draggöl, Draggöl, Sm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>584177</v>
+        <v>584190</v>
       </c>
       <c r="R20" t="n">
-        <v>6374515</v>
+        <v>6374486</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2666,40 +2657,49 @@
           <t>2025-10-04</t>
         </is>
       </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-10-04</t>
         </is>
       </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Kristian  Norrby</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Kristian  Norrby</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128904450</v>
+        <v>128904088</v>
       </c>
       <c r="B21" t="n">
-        <v>79654</v>
+        <v>79658</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2734,10 +2734,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>584145</v>
+        <v>584195</v>
       </c>
       <c r="R21" t="n">
-        <v>6374604</v>
+        <v>6374314</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2797,10 +2797,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128904088</v>
+        <v>128904450</v>
       </c>
       <c r="B22" t="n">
-        <v>79654</v>
+        <v>79658</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2835,10 +2835,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>584195</v>
+        <v>584145</v>
       </c>
       <c r="R22" t="n">
-        <v>6374314</v>
+        <v>6374604</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2901,7 +2901,7 @@
         <v>128904443</v>
       </c>
       <c r="B23" t="n">
-        <v>57720</v>
+        <v>57722</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3010,7 +3010,7 @@
         <v>128903521</v>
       </c>
       <c r="B24" t="n">
-        <v>58093</v>
+        <v>58095</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3126,55 +3126,48 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128903851</v>
+        <v>128895716</v>
       </c>
       <c r="B25" t="n">
-        <v>91546</v>
+        <v>96265</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5442</v>
+        <v>2180</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Draggöl, Stora Ramm, Sm</t>
+          <t>Draggöl, Draggöl, Sm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>584167</v>
+        <v>584171</v>
       </c>
       <c r="R25" t="n">
-        <v>6374518</v>
+        <v>6374322</v>
       </c>
       <c r="S25" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3203,7 +3196,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3213,7 +3206,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3222,67 +3215,73 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128895716</v>
+        <v>128903851</v>
       </c>
       <c r="B26" t="n">
-        <v>96255</v>
+        <v>91553</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2180</v>
+        <v>5442</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Draggöl, Draggöl, Sm</t>
+          <t>Draggöl, Stora Ramm, Sm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>584171</v>
+        <v>584167</v>
       </c>
       <c r="R26" t="n">
-        <v>6374322</v>
+        <v>6374518</v>
       </c>
       <c r="S26" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3311,7 +3310,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3321,7 +3320,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3330,28 +3329,29 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128904268</v>
+        <v>128904111</v>
       </c>
       <c r="B27" t="n">
-        <v>79654</v>
+        <v>57722</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3359,37 +3359,46 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Ekelund, Sm</t>
+          <t>E, Sm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>584121</v>
+        <v>584212</v>
       </c>
       <c r="R27" t="n">
-        <v>6374409</v>
+        <v>6374329</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3430,7 +3439,6 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3449,10 +3457,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128903578</v>
+        <v>128904408</v>
       </c>
       <c r="B28" t="n">
-        <v>92857</v>
+        <v>91553</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3460,44 +3468,48 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5966</v>
+        <v>5442</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Draggöl, Stora Ramm, Sm</t>
+          <t>Ekelund, Sm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>584236</v>
+        <v>584143</v>
       </c>
       <c r="R28" t="n">
-        <v>6374327</v>
+        <v>6374517</v>
       </c>
       <c r="S28" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3524,19 +3536,9 @@
           <t>2025-10-04</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>10:30</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-10-04</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>15:00</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3552,22 +3554,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128903661</v>
+        <v>128904429</v>
       </c>
       <c r="B29" t="n">
-        <v>92857</v>
+        <v>91553</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3575,44 +3577,48 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5966</v>
+        <v>5442</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Draggöl, Stora Ramm, Sm</t>
+          <t>Ekelund, Sm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>584164</v>
+        <v>584130</v>
       </c>
       <c r="R29" t="n">
-        <v>6374343</v>
+        <v>6374515</v>
       </c>
       <c r="S29" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3639,19 +3645,9 @@
           <t>2025-10-04</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>10:30</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-10-04</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>15:00</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3667,22 +3663,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128904408</v>
+        <v>128904268</v>
       </c>
       <c r="B30" t="n">
-        <v>91546</v>
+        <v>79658</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3690,33 +3686,25 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5442</v>
+        <v>6453</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
@@ -3725,10 +3713,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>584143</v>
+        <v>584121</v>
       </c>
       <c r="R30" t="n">
-        <v>6374517</v>
+        <v>6374409</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3788,10 +3776,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128904429</v>
+        <v>128903578</v>
       </c>
       <c r="B31" t="n">
-        <v>91546</v>
+        <v>92864</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3799,48 +3787,44 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5442</v>
+        <v>5966</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Ekelund, Sm</t>
+          <t>Draggöl, Stora Ramm, Sm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>584130</v>
+        <v>584236</v>
       </c>
       <c r="R31" t="n">
-        <v>6374515</v>
+        <v>6374327</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3867,9 +3851,19 @@
           <t>2025-10-04</t>
         </is>
       </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-10-04</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3885,22 +3879,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128904111</v>
+        <v>128903661</v>
       </c>
       <c r="B32" t="n">
-        <v>57720</v>
+        <v>92864</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3908,49 +3902,44 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100049</v>
+        <v>5966</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>E, Sm</t>
+          <t>Draggöl, Stora Ramm, Sm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>584212</v>
+        <v>584164</v>
       </c>
       <c r="R32" t="n">
-        <v>6374329</v>
+        <v>6374343</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3977,29 +3966,40 @@
           <t>2025-10-04</t>
         </is>
       </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-10-04</t>
         </is>
       </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
@@ -4009,7 +4009,7 @@
         <v>128903926</v>
       </c>
       <c r="B33" t="n">
-        <v>92857</v>
+        <v>92864</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4124,7 +4124,7 @@
         <v>128903960</v>
       </c>
       <c r="B34" t="n">
-        <v>92819</v>
+        <v>92826</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4239,7 +4239,7 @@
         <v>128904329</v>
       </c>
       <c r="B35" t="n">
-        <v>79654</v>
+        <v>79658</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4340,7 +4340,7 @@
         <v>128903654</v>
       </c>
       <c r="B36" t="n">
-        <v>92857</v>
+        <v>92864</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4455,7 +4455,7 @@
         <v>128903739</v>
       </c>
       <c r="B37" t="n">
-        <v>79654</v>
+        <v>79658</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4566,7 +4566,7 @@
         <v>128903593</v>
       </c>
       <c r="B38" t="n">
-        <v>92857</v>
+        <v>92864</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4681,7 +4681,7 @@
         <v>128904385</v>
       </c>
       <c r="B39" t="n">
-        <v>92857</v>
+        <v>92864</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4787,48 +4787,59 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128897896</v>
+        <v>128904323</v>
       </c>
       <c r="B40" t="n">
-        <v>96255</v>
+        <v>92864</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>2180</v>
+        <v>5966</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Draggöl, Draggöl, Sm</t>
+          <t>Ekelund, Sm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>584067</v>
+        <v>584175</v>
       </c>
       <c r="R40" t="n">
-        <v>6374669</v>
+        <v>6374451</v>
       </c>
       <c r="S40" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4855,98 +4866,78 @@
           <t>2025-10-04</t>
         </is>
       </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>13:31</t>
-        </is>
-      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-10-04</t>
         </is>
       </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>13:31</t>
-        </is>
-      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Kristian  Norrby</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Kristian  Norrby</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128904323</v>
+        <v>128897896</v>
       </c>
       <c r="B41" t="n">
-        <v>92857</v>
+        <v>96265</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5966</v>
+        <v>2180</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Ekelund, Sm</t>
+          <t>Draggöl, Draggöl, Sm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>584175</v>
+        <v>584067</v>
       </c>
       <c r="R41" t="n">
-        <v>6374451</v>
+        <v>6374669</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4973,30 +4964,39 @@
           <t>2025-10-04</t>
         </is>
       </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>13:31</t>
+        </is>
+      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-10-04</t>
         </is>
       </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>13:31</t>
+        </is>
+      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Kristian  Norrby</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Kristian  Norrby</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
@@ -5006,7 +5006,7 @@
         <v>128897155</v>
       </c>
       <c r="B42" t="n">
-        <v>96255</v>
+        <v>96265</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5113,7 +5113,7 @@
         <v>128897364</v>
       </c>
       <c r="B43" t="n">
-        <v>92857</v>
+        <v>92864</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5220,7 +5220,7 @@
         <v>128897073</v>
       </c>
       <c r="B44" t="n">
-        <v>79654</v>
+        <v>79658</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5324,10 +5324,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128903690</v>
+        <v>128903940</v>
       </c>
       <c r="B45" t="n">
-        <v>79654</v>
+        <v>92864</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5335,24 +5335,28 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
       <c r="N45" t="inlineStr"/>
@@ -5362,10 +5366,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>584120</v>
+        <v>584166</v>
       </c>
       <c r="R45" t="n">
-        <v>6374392</v>
+        <v>6374449</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -5435,10 +5439,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128903940</v>
+        <v>128903690</v>
       </c>
       <c r="B46" t="n">
-        <v>92857</v>
+        <v>79658</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5446,28 +5450,24 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
       <c r="N46" t="inlineStr"/>
@@ -5477,10 +5477,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>584166</v>
+        <v>584120</v>
       </c>
       <c r="R46" t="n">
-        <v>6374449</v>
+        <v>6374392</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -5553,7 +5553,7 @@
         <v>128903857</v>
       </c>
       <c r="B47" t="n">
-        <v>79654</v>
+        <v>79658</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5664,7 +5664,7 @@
         <v>128904459</v>
       </c>
       <c r="B48" t="n">
-        <v>79654</v>
+        <v>79658</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5765,7 +5765,7 @@
         <v>128903869</v>
       </c>
       <c r="B49" t="n">
-        <v>79654</v>
+        <v>79658</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5881,7 +5881,7 @@
         <v>128909203</v>
       </c>
       <c r="B50" t="n">
-        <v>79625</v>
+        <v>79629</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5992,7 +5992,7 @@
         <v>128908556</v>
       </c>
       <c r="B51" t="n">
-        <v>78792</v>
+        <v>78796</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6108,7 +6108,7 @@
         <v>128908500</v>
       </c>
       <c r="B52" t="n">
-        <v>92811</v>
+        <v>92818</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6219,7 +6219,7 @@
         <v>128904124</v>
       </c>
       <c r="B53" t="n">
-        <v>92845</v>
+        <v>92852</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6324,7 +6324,7 @@
         <v>129193511</v>
       </c>
       <c r="B54" t="n">
-        <v>91546</v>
+        <v>91553</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6429,7 +6429,7 @@
         <v>129193484</v>
       </c>
       <c r="B55" t="n">
-        <v>92819</v>
+        <v>92826</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>

--- a/artfynd/A 45800-2025 artfynd.xlsx
+++ b/artfynd/A 45800-2025 artfynd.xlsx
@@ -3007,10 +3007,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128903521</v>
+        <v>128895716</v>
       </c>
       <c r="B24" t="n">
-        <v>58095</v>
+        <v>96265</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3018,49 +3018,37 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>103015</v>
+        <v>2180</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr"/>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Draggöl, Stora Ramm, Sm</t>
+          <t>Draggöl, Draggöl, Sm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>584198</v>
+        <v>584171</v>
       </c>
       <c r="R24" t="n">
-        <v>6374339</v>
+        <v>6374322</v>
       </c>
       <c r="S24" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3089,7 +3077,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3099,7 +3087,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3114,60 +3102,67 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128895716</v>
+        <v>128903851</v>
       </c>
       <c r="B25" t="n">
-        <v>96265</v>
+        <v>91553</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2180</v>
+        <v>5442</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Draggöl, Draggöl, Sm</t>
+          <t>Draggöl, Stora Ramm, Sm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>584171</v>
+        <v>584167</v>
       </c>
       <c r="R25" t="n">
-        <v>6374322</v>
+        <v>6374518</v>
       </c>
       <c r="S25" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3196,7 +3191,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3206,7 +3201,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3215,59 +3210,65 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128903851</v>
+        <v>128903521</v>
       </c>
       <c r="B26" t="n">
-        <v>91553</v>
+        <v>58095</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5442</v>
+        <v>103015</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr"/>
+          <t>4</t>
+        </is>
+      </c>
       <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3275,10 +3276,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>584167</v>
+        <v>584198</v>
       </c>
       <c r="R26" t="n">
-        <v>6374518</v>
+        <v>6374339</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3329,7 +3330,6 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 45800-2025 artfynd.xlsx
+++ b/artfynd/A 45800-2025 artfynd.xlsx
@@ -2044,7 +2044,7 @@
         <v>128903951</v>
       </c>
       <c r="B15" t="n">
-        <v>92864</v>
+        <v>92871</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2267,10 +2267,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128903715</v>
+        <v>128897118</v>
       </c>
       <c r="B17" t="n">
-        <v>96265</v>
+        <v>96272</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2296,23 +2296,19 @@
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Draggöl, Stora Ramm, Sm</t>
+          <t>Draggöl, Draggöl, Sm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>584142</v>
+        <v>584190</v>
       </c>
       <c r="R17" t="n">
-        <v>6374419</v>
+        <v>6374486</v>
       </c>
       <c r="S17" t="n">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2341,7 +2337,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2351,7 +2347,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2360,78 +2356,70 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Kristian  Norrby</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Kristian  Norrby</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128904395</v>
+        <v>128903715</v>
       </c>
       <c r="B18" t="n">
-        <v>92864</v>
+        <v>96272</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5966</v>
+        <v>2180</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Ekelund, Sm</t>
+          <t>Draggöl, Stora Ramm, Sm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>584177</v>
+        <v>584142</v>
       </c>
       <c r="R18" t="n">
-        <v>6374515</v>
+        <v>6374419</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2458,9 +2446,19 @@
           <t>2025-10-04</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-10-04</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2476,22 +2474,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128904192</v>
+        <v>128904395</v>
       </c>
       <c r="B19" t="n">
-        <v>79658</v>
+        <v>92871</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2499,25 +2497,33 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
@@ -2526,10 +2532,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>584149</v>
+        <v>584177</v>
       </c>
       <c r="R19" t="n">
-        <v>6374399</v>
+        <v>6374515</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2589,48 +2595,51 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128897118</v>
+        <v>128904192</v>
       </c>
       <c r="B20" t="n">
-        <v>96265</v>
+        <v>79658</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2180</v>
+        <v>6453</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Draggöl, Draggöl, Sm</t>
+          <t>Ekelund, Sm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>584190</v>
+        <v>584149</v>
       </c>
       <c r="R20" t="n">
-        <v>6374486</v>
+        <v>6374399</v>
       </c>
       <c r="S20" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2657,39 +2666,30 @@
           <t>2025-10-04</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>13:05</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-10-04</t>
         </is>
       </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>13:05</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Kristian  Norrby</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Kristian  Norrby</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -3010,7 +3010,7 @@
         <v>128895716</v>
       </c>
       <c r="B24" t="n">
-        <v>96265</v>
+        <v>96272</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3117,7 +3117,7 @@
         <v>128903851</v>
       </c>
       <c r="B25" t="n">
-        <v>91553</v>
+        <v>91560</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3348,10 +3348,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128904111</v>
+        <v>128903578</v>
       </c>
       <c r="B27" t="n">
-        <v>57722</v>
+        <v>92871</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3359,49 +3359,44 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100049</v>
+        <v>5966</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>E, Sm</t>
+          <t>Draggöl, Stora Ramm, Sm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>584212</v>
+        <v>584236</v>
       </c>
       <c r="R27" t="n">
-        <v>6374329</v>
+        <v>6374327</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3428,29 +3423,40 @@
           <t>2025-10-04</t>
         </is>
       </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-10-04</t>
         </is>
       </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
@@ -3460,7 +3466,7 @@
         <v>128904408</v>
       </c>
       <c r="B28" t="n">
-        <v>91553</v>
+        <v>91560</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3566,10 +3572,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128904429</v>
+        <v>128903661</v>
       </c>
       <c r="B29" t="n">
-        <v>91553</v>
+        <v>92871</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3577,48 +3583,44 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5442</v>
+        <v>5966</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Ekelund, Sm</t>
+          <t>Draggöl, Stora Ramm, Sm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>584130</v>
+        <v>584164</v>
       </c>
       <c r="R29" t="n">
-        <v>6374515</v>
+        <v>6374343</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3645,9 +3647,19 @@
           <t>2025-10-04</t>
         </is>
       </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-10-04</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3663,22 +3675,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128904268</v>
+        <v>128904429</v>
       </c>
       <c r="B30" t="n">
-        <v>79658</v>
+        <v>91560</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3686,25 +3698,33 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6453</v>
+        <v>5442</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
@@ -3713,10 +3733,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>584121</v>
+        <v>584130</v>
       </c>
       <c r="R30" t="n">
-        <v>6374409</v>
+        <v>6374515</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3776,10 +3796,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128903578</v>
+        <v>128904268</v>
       </c>
       <c r="B31" t="n">
-        <v>92864</v>
+        <v>79658</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3787,44 +3807,40 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Draggöl, Stora Ramm, Sm</t>
+          <t>Ekelund, Sm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>584236</v>
+        <v>584121</v>
       </c>
       <c r="R31" t="n">
-        <v>6374327</v>
+        <v>6374409</v>
       </c>
       <c r="S31" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3851,19 +3867,9 @@
           <t>2025-10-04</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>10:30</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-10-04</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>15:00</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3879,22 +3885,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128903661</v>
+        <v>128904111</v>
       </c>
       <c r="B32" t="n">
-        <v>92864</v>
+        <v>57722</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3902,44 +3908,49 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5966</v>
+        <v>100049</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Draggöl, Stora Ramm, Sm</t>
+          <t>E, Sm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>584164</v>
+        <v>584212</v>
       </c>
       <c r="R32" t="n">
-        <v>6374343</v>
+        <v>6374329</v>
       </c>
       <c r="S32" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3966,40 +3977,29 @@
           <t>2025-10-04</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>10:30</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-10-04</t>
         </is>
       </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>15:00</t>
-        </is>
-      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
@@ -4009,7 +4009,7 @@
         <v>128903926</v>
       </c>
       <c r="B33" t="n">
-        <v>92864</v>
+        <v>92871</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4124,7 +4124,7 @@
         <v>128903960</v>
       </c>
       <c r="B34" t="n">
-        <v>92826</v>
+        <v>92833</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4340,7 +4340,7 @@
         <v>128903654</v>
       </c>
       <c r="B36" t="n">
-        <v>92864</v>
+        <v>92871</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4566,7 +4566,7 @@
         <v>128903593</v>
       </c>
       <c r="B38" t="n">
-        <v>92864</v>
+        <v>92871</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4681,7 +4681,7 @@
         <v>128904385</v>
       </c>
       <c r="B39" t="n">
-        <v>92864</v>
+        <v>92871</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4787,59 +4787,48 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128904323</v>
+        <v>128897896</v>
       </c>
       <c r="B40" t="n">
-        <v>92864</v>
+        <v>96272</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5966</v>
+        <v>2180</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Ekelund, Sm</t>
+          <t>Draggöl, Draggöl, Sm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>584175</v>
+        <v>584067</v>
       </c>
       <c r="R40" t="n">
-        <v>6374451</v>
+        <v>6374669</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4866,78 +4855,98 @@
           <t>2025-10-04</t>
         </is>
       </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>13:31</t>
+        </is>
+      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-10-04</t>
         </is>
       </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>13:31</t>
+        </is>
+      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Kristian  Norrby</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Kristian  Norrby</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128897896</v>
+        <v>128904323</v>
       </c>
       <c r="B41" t="n">
-        <v>96265</v>
+        <v>92871</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>2180</v>
+        <v>5966</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Draggöl, Draggöl, Sm</t>
+          <t>Ekelund, Sm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>584067</v>
+        <v>584175</v>
       </c>
       <c r="R41" t="n">
-        <v>6374669</v>
+        <v>6374451</v>
       </c>
       <c r="S41" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4964,39 +4973,30 @@
           <t>2025-10-04</t>
         </is>
       </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>13:31</t>
-        </is>
-      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-10-04</t>
         </is>
       </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>13:31</t>
-        </is>
-      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Kristian  Norrby</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Kristian  Norrby</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
@@ -5006,7 +5006,7 @@
         <v>128897155</v>
       </c>
       <c r="B42" t="n">
-        <v>96265</v>
+        <v>96272</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5113,7 +5113,7 @@
         <v>128897364</v>
       </c>
       <c r="B43" t="n">
-        <v>92864</v>
+        <v>92871</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5327,7 +5327,7 @@
         <v>128903940</v>
       </c>
       <c r="B45" t="n">
-        <v>92864</v>
+        <v>92871</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6108,7 +6108,7 @@
         <v>128908500</v>
       </c>
       <c r="B52" t="n">
-        <v>92818</v>
+        <v>92825</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6219,7 +6219,7 @@
         <v>128904124</v>
       </c>
       <c r="B53" t="n">
-        <v>92852</v>
+        <v>92859</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6324,7 +6324,7 @@
         <v>129193511</v>
       </c>
       <c r="B54" t="n">
-        <v>91553</v>
+        <v>91560</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6429,7 +6429,7 @@
         <v>129193484</v>
       </c>
       <c r="B55" t="n">
-        <v>92826</v>
+        <v>92833</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>

--- a/artfynd/A 45800-2025 artfynd.xlsx
+++ b/artfynd/A 45800-2025 artfynd.xlsx
@@ -2041,10 +2041,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128903951</v>
+        <v>128903544</v>
       </c>
       <c r="B15" t="n">
-        <v>92871</v>
+        <v>79660</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2052,28 +2052,24 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
@@ -2083,10 +2079,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>584183</v>
+        <v>584191</v>
       </c>
       <c r="R15" t="n">
-        <v>6374596</v>
+        <v>6374331</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2156,10 +2152,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128903544</v>
+        <v>128903951</v>
       </c>
       <c r="B16" t="n">
-        <v>79658</v>
+        <v>92873</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2167,24 +2163,28 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
@@ -2194,10 +2194,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>584191</v>
+        <v>584183</v>
       </c>
       <c r="R16" t="n">
-        <v>6374331</v>
+        <v>6374596</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2270,7 +2270,7 @@
         <v>128897118</v>
       </c>
       <c r="B17" t="n">
-        <v>96272</v>
+        <v>96274</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2374,52 +2374,59 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128903715</v>
+        <v>128904395</v>
       </c>
       <c r="B18" t="n">
-        <v>96272</v>
+        <v>92873</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2180</v>
+        <v>5966</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Draggöl, Stora Ramm, Sm</t>
+          <t>Ekelund, Sm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>584142</v>
+        <v>584177</v>
       </c>
       <c r="R18" t="n">
-        <v>6374419</v>
+        <v>6374515</v>
       </c>
       <c r="S18" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2446,19 +2453,9 @@
           <t>2025-10-04</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>10:30</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-10-04</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>15:00</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2474,71 +2471,64 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128904395</v>
+        <v>128903715</v>
       </c>
       <c r="B19" t="n">
-        <v>92871</v>
+        <v>96274</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5966</v>
+        <v>2180</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Ekelund, Sm</t>
+          <t>Draggöl, Stora Ramm, Sm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>584177</v>
+        <v>584142</v>
       </c>
       <c r="R19" t="n">
-        <v>6374515</v>
+        <v>6374419</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2565,9 +2555,19 @@
           <t>2025-10-04</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-10-04</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2583,12 +2583,12 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
@@ -2598,7 +2598,7 @@
         <v>128904192</v>
       </c>
       <c r="B20" t="n">
-        <v>79658</v>
+        <v>79660</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2696,10 +2696,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128904088</v>
+        <v>128904443</v>
       </c>
       <c r="B21" t="n">
-        <v>79658</v>
+        <v>57724</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2707,26 +2707,35 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2734,10 +2743,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>584195</v>
+        <v>584113</v>
       </c>
       <c r="R21" t="n">
-        <v>6374314</v>
+        <v>6374565</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2778,7 +2787,6 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2797,10 +2805,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128904450</v>
+        <v>128904088</v>
       </c>
       <c r="B22" t="n">
-        <v>79658</v>
+        <v>79660</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2835,10 +2843,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>584145</v>
+        <v>584195</v>
       </c>
       <c r="R22" t="n">
-        <v>6374604</v>
+        <v>6374314</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2898,10 +2906,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128904443</v>
+        <v>128904450</v>
       </c>
       <c r="B23" t="n">
-        <v>57722</v>
+        <v>79660</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2909,35 +2917,26 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -2945,10 +2944,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>584113</v>
+        <v>584145</v>
       </c>
       <c r="R23" t="n">
-        <v>6374565</v>
+        <v>6374604</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2989,6 +2988,7 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3010,7 +3010,7 @@
         <v>128895716</v>
       </c>
       <c r="B24" t="n">
-        <v>96272</v>
+        <v>96274</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3117,7 +3117,7 @@
         <v>128903851</v>
       </c>
       <c r="B25" t="n">
-        <v>91560</v>
+        <v>91562</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3232,7 +3232,7 @@
         <v>128903521</v>
       </c>
       <c r="B26" t="n">
-        <v>58095</v>
+        <v>58097</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3351,7 +3351,7 @@
         <v>128903578</v>
       </c>
       <c r="B27" t="n">
-        <v>92871</v>
+        <v>92873</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3463,10 +3463,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128904408</v>
+        <v>128903661</v>
       </c>
       <c r="B28" t="n">
-        <v>91560</v>
+        <v>92873</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3474,48 +3474,44 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5442</v>
+        <v>5966</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Ekelund, Sm</t>
+          <t>Draggöl, Stora Ramm, Sm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>584143</v>
+        <v>584164</v>
       </c>
       <c r="R28" t="n">
-        <v>6374517</v>
+        <v>6374343</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3542,9 +3538,19 @@
           <t>2025-10-04</t>
         </is>
       </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-10-04</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3560,22 +3566,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128903661</v>
+        <v>128904268</v>
       </c>
       <c r="B29" t="n">
-        <v>92871</v>
+        <v>79660</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3583,44 +3589,40 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Draggöl, Stora Ramm, Sm</t>
+          <t>Ekelund, Sm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>584164</v>
+        <v>584121</v>
       </c>
       <c r="R29" t="n">
-        <v>6374343</v>
+        <v>6374409</v>
       </c>
       <c r="S29" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3647,19 +3649,9 @@
           <t>2025-10-04</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>10:30</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-10-04</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>15:00</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3675,22 +3667,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128904429</v>
+        <v>128904111</v>
       </c>
       <c r="B30" t="n">
-        <v>91560</v>
+        <v>57724</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3698,21 +3690,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -3720,23 +3712,24 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Ekelund, Sm</t>
+          <t>E, Sm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>584130</v>
+        <v>584212</v>
       </c>
       <c r="R30" t="n">
-        <v>6374515</v>
+        <v>6374329</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3777,7 +3770,6 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3796,10 +3788,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128904268</v>
+        <v>128904408</v>
       </c>
       <c r="B31" t="n">
-        <v>79658</v>
+        <v>91562</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3807,25 +3799,33 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6453</v>
+        <v>5442</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
@@ -3834,10 +3834,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>584121</v>
+        <v>584143</v>
       </c>
       <c r="R31" t="n">
-        <v>6374409</v>
+        <v>6374517</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3897,10 +3897,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128904111</v>
+        <v>128904429</v>
       </c>
       <c r="B32" t="n">
-        <v>57722</v>
+        <v>91562</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3908,21 +3908,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -3930,24 +3930,23 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>E, Sm</t>
+          <t>Ekelund, Sm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>584212</v>
+        <v>584130</v>
       </c>
       <c r="R32" t="n">
-        <v>6374329</v>
+        <v>6374515</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3988,6 +3987,7 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -4009,7 +4009,7 @@
         <v>128903926</v>
       </c>
       <c r="B33" t="n">
-        <v>92871</v>
+        <v>92873</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4124,7 +4124,7 @@
         <v>128903960</v>
       </c>
       <c r="B34" t="n">
-        <v>92833</v>
+        <v>92835</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4239,7 +4239,7 @@
         <v>128904329</v>
       </c>
       <c r="B35" t="n">
-        <v>79658</v>
+        <v>79660</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4340,7 +4340,7 @@
         <v>128903654</v>
       </c>
       <c r="B36" t="n">
-        <v>92871</v>
+        <v>92873</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4455,7 +4455,7 @@
         <v>128903739</v>
       </c>
       <c r="B37" t="n">
-        <v>79658</v>
+        <v>79660</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4566,7 +4566,7 @@
         <v>128903593</v>
       </c>
       <c r="B38" t="n">
-        <v>92871</v>
+        <v>92873</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4681,7 +4681,7 @@
         <v>128904385</v>
       </c>
       <c r="B39" t="n">
-        <v>92871</v>
+        <v>92873</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4790,7 +4790,7 @@
         <v>128897896</v>
       </c>
       <c r="B40" t="n">
-        <v>96272</v>
+        <v>96274</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4897,7 +4897,7 @@
         <v>128904323</v>
       </c>
       <c r="B41" t="n">
-        <v>92871</v>
+        <v>92873</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5006,7 +5006,7 @@
         <v>128897155</v>
       </c>
       <c r="B42" t="n">
-        <v>96272</v>
+        <v>96274</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5113,7 +5113,7 @@
         <v>128897364</v>
       </c>
       <c r="B43" t="n">
-        <v>92871</v>
+        <v>92873</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5220,7 +5220,7 @@
         <v>128897073</v>
       </c>
       <c r="B44" t="n">
-        <v>79658</v>
+        <v>79660</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5327,7 +5327,7 @@
         <v>128903940</v>
       </c>
       <c r="B45" t="n">
-        <v>92871</v>
+        <v>92873</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5442,7 +5442,7 @@
         <v>128903690</v>
       </c>
       <c r="B46" t="n">
-        <v>79658</v>
+        <v>79660</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5553,7 +5553,7 @@
         <v>128903857</v>
       </c>
       <c r="B47" t="n">
-        <v>79658</v>
+        <v>79660</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5664,7 +5664,7 @@
         <v>128904459</v>
       </c>
       <c r="B48" t="n">
-        <v>79658</v>
+        <v>79660</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5765,7 +5765,7 @@
         <v>128903869</v>
       </c>
       <c r="B49" t="n">
-        <v>79658</v>
+        <v>79660</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5881,7 +5881,7 @@
         <v>128909203</v>
       </c>
       <c r="B50" t="n">
-        <v>79629</v>
+        <v>79631</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5992,7 +5992,7 @@
         <v>128908556</v>
       </c>
       <c r="B51" t="n">
-        <v>78796</v>
+        <v>78798</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6108,7 +6108,7 @@
         <v>128908500</v>
       </c>
       <c r="B52" t="n">
-        <v>92825</v>
+        <v>92827</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6219,7 +6219,7 @@
         <v>128904124</v>
       </c>
       <c r="B53" t="n">
-        <v>92859</v>
+        <v>92861</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6324,7 +6324,7 @@
         <v>129193511</v>
       </c>
       <c r="B54" t="n">
-        <v>91560</v>
+        <v>91562</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6429,7 +6429,7 @@
         <v>129193484</v>
       </c>
       <c r="B55" t="n">
-        <v>92833</v>
+        <v>92835</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>

--- a/artfynd/A 45800-2025 artfynd.xlsx
+++ b/artfynd/A 45800-2025 artfynd.xlsx
@@ -2041,10 +2041,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128903544</v>
+        <v>128903951</v>
       </c>
       <c r="B15" t="n">
-        <v>79660</v>
+        <v>92873</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2052,24 +2052,28 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
@@ -2079,10 +2083,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>584191</v>
+        <v>584183</v>
       </c>
       <c r="R15" t="n">
-        <v>6374331</v>
+        <v>6374596</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2152,10 +2156,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128903951</v>
+        <v>128903544</v>
       </c>
       <c r="B16" t="n">
-        <v>92873</v>
+        <v>79660</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2163,28 +2167,24 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
@@ -2194,10 +2194,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>584183</v>
+        <v>584191</v>
       </c>
       <c r="R16" t="n">
-        <v>6374596</v>
+        <v>6374331</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2267,7 +2267,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128897118</v>
+        <v>128903715</v>
       </c>
       <c r="B17" t="n">
         <v>96274</v>
@@ -2296,19 +2296,23 @@
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Draggöl, Draggöl, Sm</t>
+          <t>Draggöl, Stora Ramm, Sm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>584190</v>
+        <v>584142</v>
       </c>
       <c r="R17" t="n">
-        <v>6374486</v>
+        <v>6374419</v>
       </c>
       <c r="S17" t="n">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2337,7 +2341,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2347,7 +2351,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2356,18 +2360,19 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kristian  Norrby</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kristian  Norrby</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
@@ -2483,7 +2488,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128903715</v>
+        <v>128897118</v>
       </c>
       <c r="B19" t="n">
         <v>96274</v>
@@ -2512,23 +2517,19 @@
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Draggöl, Stora Ramm, Sm</t>
+          <t>Draggöl, Draggöl, Sm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>584142</v>
+        <v>584190</v>
       </c>
       <c r="R19" t="n">
-        <v>6374419</v>
+        <v>6374486</v>
       </c>
       <c r="S19" t="n">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2557,7 +2558,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2567,7 +2568,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2576,19 +2577,18 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Kristian  Norrby</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Kristian  Norrby</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
@@ -2696,10 +2696,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128904443</v>
+        <v>128904088</v>
       </c>
       <c r="B21" t="n">
-        <v>57724</v>
+        <v>79660</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2707,35 +2707,26 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2743,10 +2734,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>584113</v>
+        <v>584195</v>
       </c>
       <c r="R21" t="n">
-        <v>6374565</v>
+        <v>6374314</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2787,6 +2778,7 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2805,7 +2797,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128904088</v>
+        <v>128904450</v>
       </c>
       <c r="B22" t="n">
         <v>79660</v>
@@ -2843,10 +2835,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>584195</v>
+        <v>584145</v>
       </c>
       <c r="R22" t="n">
-        <v>6374314</v>
+        <v>6374604</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2906,10 +2898,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128904450</v>
+        <v>128904443</v>
       </c>
       <c r="B23" t="n">
-        <v>79660</v>
+        <v>57724</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2917,26 +2909,35 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -2944,10 +2945,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>584145</v>
+        <v>584113</v>
       </c>
       <c r="R23" t="n">
-        <v>6374604</v>
+        <v>6374565</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2988,7 +2989,6 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3114,41 +3114,46 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128903851</v>
+        <v>128903521</v>
       </c>
       <c r="B25" t="n">
-        <v>91562</v>
+        <v>58097</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5442</v>
+        <v>103015</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr"/>
+          <t>4</t>
+        </is>
+      </c>
       <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3156,10 +3161,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>584167</v>
+        <v>584198</v>
       </c>
       <c r="R25" t="n">
-        <v>6374518</v>
+        <v>6374339</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3210,7 +3215,6 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3229,46 +3233,41 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128903521</v>
+        <v>128903851</v>
       </c>
       <c r="B26" t="n">
-        <v>58097</v>
+        <v>91562</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>103015</v>
+        <v>5442</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3276,10 +3275,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>584198</v>
+        <v>584167</v>
       </c>
       <c r="R26" t="n">
-        <v>6374339</v>
+        <v>6374518</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3330,6 +3329,7 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3348,10 +3348,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128903578</v>
+        <v>128904268</v>
       </c>
       <c r="B27" t="n">
-        <v>92873</v>
+        <v>79660</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3359,44 +3359,40 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Draggöl, Stora Ramm, Sm</t>
+          <t>Ekelund, Sm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>584236</v>
+        <v>584121</v>
       </c>
       <c r="R27" t="n">
-        <v>6374327</v>
+        <v>6374409</v>
       </c>
       <c r="S27" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3423,19 +3419,9 @@
           <t>2025-10-04</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>10:30</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-10-04</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>15:00</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3451,22 +3437,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128903661</v>
+        <v>128904111</v>
       </c>
       <c r="B28" t="n">
-        <v>92873</v>
+        <v>57724</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3474,44 +3460,49 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5966</v>
+        <v>100049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Draggöl, Stora Ramm, Sm</t>
+          <t>E, Sm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>584164</v>
+        <v>584212</v>
       </c>
       <c r="R28" t="n">
-        <v>6374343</v>
+        <v>6374329</v>
       </c>
       <c r="S28" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3538,50 +3529,39 @@
           <t>2025-10-04</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>10:30</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-10-04</t>
         </is>
       </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>15:00</t>
-        </is>
-      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128904268</v>
+        <v>128903578</v>
       </c>
       <c r="B29" t="n">
-        <v>79660</v>
+        <v>92873</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3589,40 +3569,44 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Ekelund, Sm</t>
+          <t>Draggöl, Stora Ramm, Sm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>584121</v>
+        <v>584236</v>
       </c>
       <c r="R29" t="n">
-        <v>6374409</v>
+        <v>6374327</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3649,9 +3633,19 @@
           <t>2025-10-04</t>
         </is>
       </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-10-04</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3667,22 +3661,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128904111</v>
+        <v>128903661</v>
       </c>
       <c r="B30" t="n">
-        <v>57724</v>
+        <v>92873</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3690,49 +3684,44 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100049</v>
+        <v>5966</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>E, Sm</t>
+          <t>Draggöl, Stora Ramm, Sm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>584212</v>
+        <v>584164</v>
       </c>
       <c r="R30" t="n">
-        <v>6374329</v>
+        <v>6374343</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3759,29 +3748,40 @@
           <t>2025-10-04</t>
         </is>
       </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-10-04</t>
         </is>
       </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
@@ -5110,10 +5110,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128897364</v>
+        <v>128897073</v>
       </c>
       <c r="B43" t="n">
-        <v>92873</v>
+        <v>79660</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5121,21 +5121,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5145,10 +5145,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>584139</v>
+        <v>584164</v>
       </c>
       <c r="R43" t="n">
-        <v>6374551</v>
+        <v>6374466</v>
       </c>
       <c r="S43" t="n">
         <v>2</v>
@@ -5180,7 +5180,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5190,7 +5190,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5217,10 +5217,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128897073</v>
+        <v>128897364</v>
       </c>
       <c r="B44" t="n">
-        <v>79660</v>
+        <v>92873</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5228,21 +5228,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5252,10 +5252,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>584164</v>
+        <v>584139</v>
       </c>
       <c r="R44" t="n">
-        <v>6374466</v>
+        <v>6374551</v>
       </c>
       <c r="S44" t="n">
         <v>2</v>
@@ -5287,7 +5287,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5297,7 +5297,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5324,10 +5324,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128903940</v>
+        <v>128903690</v>
       </c>
       <c r="B45" t="n">
-        <v>92873</v>
+        <v>79660</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5335,28 +5335,24 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
       <c r="N45" t="inlineStr"/>
@@ -5366,10 +5362,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>584166</v>
+        <v>584120</v>
       </c>
       <c r="R45" t="n">
-        <v>6374449</v>
+        <v>6374392</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -5439,10 +5435,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128903690</v>
+        <v>128903940</v>
       </c>
       <c r="B46" t="n">
-        <v>79660</v>
+        <v>92873</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5450,24 +5446,28 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
       <c r="N46" t="inlineStr"/>
@@ -5477,10 +5477,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>584120</v>
+        <v>584166</v>
       </c>
       <c r="R46" t="n">
-        <v>6374392</v>
+        <v>6374449</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>

--- a/artfynd/A 45800-2025 artfynd.xlsx
+++ b/artfynd/A 45800-2025 artfynd.xlsx
@@ -2267,52 +2267,51 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128903715</v>
+        <v>128904192</v>
       </c>
       <c r="B17" t="n">
-        <v>96274</v>
+        <v>79660</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2180</v>
+        <v>6453</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Draggöl, Stora Ramm, Sm</t>
+          <t>Ekelund, Sm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>584142</v>
+        <v>584149</v>
       </c>
       <c r="R17" t="n">
-        <v>6374419</v>
+        <v>6374399</v>
       </c>
       <c r="S17" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2339,19 +2338,9 @@
           <t>2025-10-04</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>10:30</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-10-04</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>15:00</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2367,71 +2356,64 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128904395</v>
+        <v>128903715</v>
       </c>
       <c r="B18" t="n">
-        <v>92873</v>
+        <v>96274</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5966</v>
+        <v>2180</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Ekelund, Sm</t>
+          <t>Draggöl, Stora Ramm, Sm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>584177</v>
+        <v>584142</v>
       </c>
       <c r="R18" t="n">
-        <v>6374515</v>
+        <v>6374419</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2458,9 +2440,19 @@
           <t>2025-10-04</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-10-04</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2476,60 +2468,71 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128897118</v>
+        <v>128904395</v>
       </c>
       <c r="B19" t="n">
-        <v>96274</v>
+        <v>92873</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2180</v>
+        <v>5966</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Draggöl, Draggöl, Sm</t>
+          <t>Ekelund, Sm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>584190</v>
+        <v>584177</v>
       </c>
       <c r="R19" t="n">
-        <v>6374486</v>
+        <v>6374515</v>
       </c>
       <c r="S19" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2556,90 +2559,78 @@
           <t>2025-10-04</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>13:05</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-10-04</t>
         </is>
       </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>13:05</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Kristian  Norrby</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Kristian  Norrby</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128904192</v>
+        <v>128897118</v>
       </c>
       <c r="B20" t="n">
-        <v>79660</v>
+        <v>96274</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6453</v>
+        <v>2180</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Ekelund, Sm</t>
+          <t>Draggöl, Draggöl, Sm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>584149</v>
+        <v>584190</v>
       </c>
       <c r="R20" t="n">
-        <v>6374399</v>
+        <v>6374486</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2666,30 +2657,39 @@
           <t>2025-10-04</t>
         </is>
       </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-10-04</t>
         </is>
       </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Kristian  Norrby</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Kristian  Norrby</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -5324,10 +5324,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128903690</v>
+        <v>128903940</v>
       </c>
       <c r="B45" t="n">
-        <v>79660</v>
+        <v>92873</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5335,24 +5335,28 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
       <c r="N45" t="inlineStr"/>
@@ -5362,10 +5366,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>584120</v>
+        <v>584166</v>
       </c>
       <c r="R45" t="n">
-        <v>6374392</v>
+        <v>6374449</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -5435,10 +5439,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128903940</v>
+        <v>128903690</v>
       </c>
       <c r="B46" t="n">
-        <v>92873</v>
+        <v>79660</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5446,28 +5450,24 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
       <c r="N46" t="inlineStr"/>
@@ -5477,10 +5477,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>584166</v>
+        <v>584120</v>
       </c>
       <c r="R46" t="n">
-        <v>6374449</v>
+        <v>6374392</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>

--- a/artfynd/A 45800-2025 artfynd.xlsx
+++ b/artfynd/A 45800-2025 artfynd.xlsx
@@ -2044,7 +2044,7 @@
         <v>128903951</v>
       </c>
       <c r="B15" t="n">
-        <v>92873</v>
+        <v>92859</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2267,51 +2267,48 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128904192</v>
+        <v>128897118</v>
       </c>
       <c r="B17" t="n">
-        <v>79660</v>
+        <v>96300</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6453</v>
+        <v>2180</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Ekelund, Sm</t>
+          <t>Draggöl, Draggöl, Sm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>584149</v>
+        <v>584190</v>
       </c>
       <c r="R17" t="n">
-        <v>6374399</v>
+        <v>6374486</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2338,82 +2335,98 @@
           <t>2025-10-04</t>
         </is>
       </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-10-04</t>
         </is>
       </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Kristian  Norrby</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Kristian  Norrby</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128903715</v>
+        <v>128904395</v>
       </c>
       <c r="B18" t="n">
-        <v>96274</v>
+        <v>92859</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2180</v>
+        <v>5966</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Draggöl, Stora Ramm, Sm</t>
+          <t>Ekelund, Sm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>584142</v>
+        <v>584177</v>
       </c>
       <c r="R18" t="n">
-        <v>6374419</v>
+        <v>6374515</v>
       </c>
       <c r="S18" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2440,19 +2453,9 @@
           <t>2025-10-04</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>10:30</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-10-04</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>15:00</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2468,71 +2471,64 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128904395</v>
+        <v>128903715</v>
       </c>
       <c r="B19" t="n">
-        <v>92873</v>
+        <v>96300</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5966</v>
+        <v>2180</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Ekelund, Sm</t>
+          <t>Draggöl, Stora Ramm, Sm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>584177</v>
+        <v>584142</v>
       </c>
       <c r="R19" t="n">
-        <v>6374515</v>
+        <v>6374419</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2559,9 +2555,19 @@
           <t>2025-10-04</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-10-04</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2577,60 +2583,63 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128897118</v>
+        <v>128904192</v>
       </c>
       <c r="B20" t="n">
-        <v>96274</v>
+        <v>79660</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2180</v>
+        <v>6453</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Draggöl, Draggöl, Sm</t>
+          <t>Ekelund, Sm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>584190</v>
+        <v>584149</v>
       </c>
       <c r="R20" t="n">
-        <v>6374486</v>
+        <v>6374399</v>
       </c>
       <c r="S20" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2657,39 +2666,30 @@
           <t>2025-10-04</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>13:05</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-10-04</t>
         </is>
       </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>13:05</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Kristian  Norrby</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Kristian  Norrby</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -3010,7 +3010,7 @@
         <v>128895716</v>
       </c>
       <c r="B24" t="n">
-        <v>96274</v>
+        <v>96300</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3114,46 +3114,41 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128903521</v>
+        <v>128903851</v>
       </c>
       <c r="B25" t="n">
-        <v>58097</v>
+        <v>91560</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>103015</v>
+        <v>5442</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3161,10 +3156,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>584198</v>
+        <v>584167</v>
       </c>
       <c r="R25" t="n">
-        <v>6374339</v>
+        <v>6374518</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3215,6 +3210,7 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3233,41 +3229,46 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128903851</v>
+        <v>128903521</v>
       </c>
       <c r="B26" t="n">
-        <v>91562</v>
+        <v>58097</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5442</v>
+        <v>103015</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr"/>
+          <t>4</t>
+        </is>
+      </c>
       <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3275,10 +3276,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>584167</v>
+        <v>584198</v>
       </c>
       <c r="R26" t="n">
-        <v>6374518</v>
+        <v>6374339</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3329,7 +3330,6 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3348,10 +3348,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128904268</v>
+        <v>128904408</v>
       </c>
       <c r="B27" t="n">
-        <v>79660</v>
+        <v>91560</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3359,25 +3359,33 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6453</v>
+        <v>5442</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
@@ -3386,10 +3394,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>584121</v>
+        <v>584143</v>
       </c>
       <c r="R27" t="n">
-        <v>6374409</v>
+        <v>6374517</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3449,10 +3457,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128904111</v>
+        <v>128904429</v>
       </c>
       <c r="B28" t="n">
-        <v>57724</v>
+        <v>91560</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3460,21 +3468,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -3482,24 +3490,23 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>E, Sm</t>
+          <t>Ekelund, Sm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>584212</v>
+        <v>584130</v>
       </c>
       <c r="R28" t="n">
-        <v>6374329</v>
+        <v>6374515</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3540,6 +3547,7 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3561,7 +3569,7 @@
         <v>128903578</v>
       </c>
       <c r="B29" t="n">
-        <v>92873</v>
+        <v>92859</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3676,7 +3684,7 @@
         <v>128903661</v>
       </c>
       <c r="B30" t="n">
-        <v>92873</v>
+        <v>92859</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3788,10 +3796,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128904408</v>
+        <v>128904268</v>
       </c>
       <c r="B31" t="n">
-        <v>91562</v>
+        <v>79660</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3799,33 +3807,25 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5442</v>
+        <v>6453</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
@@ -3834,10 +3834,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>584143</v>
+        <v>584121</v>
       </c>
       <c r="R31" t="n">
-        <v>6374517</v>
+        <v>6374409</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3897,10 +3897,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128904429</v>
+        <v>128904111</v>
       </c>
       <c r="B32" t="n">
-        <v>91562</v>
+        <v>57724</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3908,21 +3908,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -3930,23 +3930,24 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Ekelund, Sm</t>
+          <t>E, Sm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>584130</v>
+        <v>584212</v>
       </c>
       <c r="R32" t="n">
-        <v>6374515</v>
+        <v>6374329</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3987,7 +3988,6 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -4009,7 +4009,7 @@
         <v>128903926</v>
       </c>
       <c r="B33" t="n">
-        <v>92873</v>
+        <v>92859</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4124,7 +4124,7 @@
         <v>128903960</v>
       </c>
       <c r="B34" t="n">
-        <v>92835</v>
+        <v>92821</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4340,7 +4340,7 @@
         <v>128903654</v>
       </c>
       <c r="B36" t="n">
-        <v>92873</v>
+        <v>92859</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4566,7 +4566,7 @@
         <v>128903593</v>
       </c>
       <c r="B38" t="n">
-        <v>92873</v>
+        <v>92859</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4681,7 +4681,7 @@
         <v>128904385</v>
       </c>
       <c r="B39" t="n">
-        <v>92873</v>
+        <v>92859</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4790,7 +4790,7 @@
         <v>128897896</v>
       </c>
       <c r="B40" t="n">
-        <v>96274</v>
+        <v>96300</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4897,7 +4897,7 @@
         <v>128904323</v>
       </c>
       <c r="B41" t="n">
-        <v>92873</v>
+        <v>92859</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5006,7 +5006,7 @@
         <v>128897155</v>
       </c>
       <c r="B42" t="n">
-        <v>96274</v>
+        <v>96300</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5110,10 +5110,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128897073</v>
+        <v>128897364</v>
       </c>
       <c r="B43" t="n">
-        <v>79660</v>
+        <v>92859</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5121,21 +5121,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5145,10 +5145,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>584164</v>
+        <v>584139</v>
       </c>
       <c r="R43" t="n">
-        <v>6374466</v>
+        <v>6374551</v>
       </c>
       <c r="S43" t="n">
         <v>2</v>
@@ -5180,7 +5180,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5190,7 +5190,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5217,10 +5217,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128897364</v>
+        <v>128897073</v>
       </c>
       <c r="B44" t="n">
-        <v>92873</v>
+        <v>79660</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5228,21 +5228,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5252,10 +5252,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>584139</v>
+        <v>584164</v>
       </c>
       <c r="R44" t="n">
-        <v>6374551</v>
+        <v>6374466</v>
       </c>
       <c r="S44" t="n">
         <v>2</v>
@@ -5287,7 +5287,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5297,7 +5297,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5327,7 +5327,7 @@
         <v>128903940</v>
       </c>
       <c r="B45" t="n">
-        <v>92873</v>
+        <v>92859</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6108,7 +6108,7 @@
         <v>128908500</v>
       </c>
       <c r="B52" t="n">
-        <v>92827</v>
+        <v>92813</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6219,7 +6219,7 @@
         <v>128904124</v>
       </c>
       <c r="B53" t="n">
-        <v>92861</v>
+        <v>92847</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6324,7 +6324,7 @@
         <v>129193511</v>
       </c>
       <c r="B54" t="n">
-        <v>91562</v>
+        <v>91560</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6429,7 +6429,7 @@
         <v>129193484</v>
       </c>
       <c r="B55" t="n">
-        <v>92835</v>
+        <v>92821</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>

--- a/artfynd/A 45800-2025 artfynd.xlsx
+++ b/artfynd/A 45800-2025 artfynd.xlsx
@@ -2044,7 +2044,7 @@
         <v>128903951</v>
       </c>
       <c r="B15" t="n">
-        <v>92859</v>
+        <v>92860</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2267,10 +2267,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128897118</v>
+        <v>128903715</v>
       </c>
       <c r="B17" t="n">
-        <v>96300</v>
+        <v>96301</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2296,19 +2296,23 @@
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Draggöl, Draggöl, Sm</t>
+          <t>Draggöl, Stora Ramm, Sm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>584190</v>
+        <v>584142</v>
       </c>
       <c r="R17" t="n">
-        <v>6374486</v>
+        <v>6374419</v>
       </c>
       <c r="S17" t="n">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2337,7 +2341,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2347,7 +2351,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2356,77 +2360,67 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kristian  Norrby</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kristian  Norrby</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128904395</v>
+        <v>128897118</v>
       </c>
       <c r="B18" t="n">
-        <v>92859</v>
+        <v>96301</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5966</v>
+        <v>2180</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Ekelund, Sm</t>
+          <t>Draggöl, Draggöl, Sm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>584177</v>
+        <v>584190</v>
       </c>
       <c r="R18" t="n">
-        <v>6374515</v>
+        <v>6374486</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2453,82 +2447,98 @@
           <t>2025-10-04</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-10-04</t>
         </is>
       </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Kristian  Norrby</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Kristian  Norrby</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128903715</v>
+        <v>128904395</v>
       </c>
       <c r="B19" t="n">
-        <v>96300</v>
+        <v>92860</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2180</v>
+        <v>5966</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Draggöl, Stora Ramm, Sm</t>
+          <t>Ekelund, Sm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>584142</v>
+        <v>584177</v>
       </c>
       <c r="R19" t="n">
-        <v>6374419</v>
+        <v>6374515</v>
       </c>
       <c r="S19" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2555,19 +2565,9 @@
           <t>2025-10-04</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>10:30</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-10-04</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>15:00</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2583,12 +2583,12 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
@@ -2696,10 +2696,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128904088</v>
+        <v>128904443</v>
       </c>
       <c r="B21" t="n">
-        <v>79660</v>
+        <v>57724</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2707,26 +2707,35 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2734,10 +2743,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>584195</v>
+        <v>584113</v>
       </c>
       <c r="R21" t="n">
-        <v>6374314</v>
+        <v>6374565</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2778,7 +2787,6 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2797,7 +2805,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128904450</v>
+        <v>128904088</v>
       </c>
       <c r="B22" t="n">
         <v>79660</v>
@@ -2835,10 +2843,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>584145</v>
+        <v>584195</v>
       </c>
       <c r="R22" t="n">
-        <v>6374604</v>
+        <v>6374314</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2898,10 +2906,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128904443</v>
+        <v>128904450</v>
       </c>
       <c r="B23" t="n">
-        <v>57724</v>
+        <v>79660</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2909,35 +2917,26 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -2945,10 +2944,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>584113</v>
+        <v>584145</v>
       </c>
       <c r="R23" t="n">
-        <v>6374565</v>
+        <v>6374604</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2989,6 +2988,7 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3007,48 +3007,55 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128895716</v>
+        <v>128903851</v>
       </c>
       <c r="B24" t="n">
-        <v>96300</v>
+        <v>91561</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2180</v>
+        <v>5442</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Draggöl, Draggöl, Sm</t>
+          <t>Draggöl, Stora Ramm, Sm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>584171</v>
+        <v>584167</v>
       </c>
       <c r="R24" t="n">
-        <v>6374322</v>
+        <v>6374518</v>
       </c>
       <c r="S24" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3077,7 +3084,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3087,7 +3094,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3096,59 +3103,65 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128903851</v>
+        <v>128903521</v>
       </c>
       <c r="B25" t="n">
-        <v>91560</v>
+        <v>58097</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5442</v>
+        <v>103015</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr"/>
+          <t>4</t>
+        </is>
+      </c>
       <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3156,10 +3169,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>584167</v>
+        <v>584198</v>
       </c>
       <c r="R25" t="n">
-        <v>6374518</v>
+        <v>6374339</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3210,7 +3223,6 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3229,10 +3241,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128903521</v>
+        <v>128895716</v>
       </c>
       <c r="B26" t="n">
-        <v>58097</v>
+        <v>96301</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3240,49 +3252,37 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>103015</v>
+        <v>2180</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr"/>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Draggöl, Stora Ramm, Sm</t>
+          <t>Draggöl, Draggöl, Sm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>584198</v>
+        <v>584171</v>
       </c>
       <c r="R26" t="n">
-        <v>6374339</v>
+        <v>6374322</v>
       </c>
       <c r="S26" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3311,7 +3311,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3336,22 +3336,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128904408</v>
+        <v>128903578</v>
       </c>
       <c r="B27" t="n">
-        <v>91560</v>
+        <v>92860</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3359,48 +3359,44 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5442</v>
+        <v>5966</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Ekelund, Sm</t>
+          <t>Draggöl, Stora Ramm, Sm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>584143</v>
+        <v>584236</v>
       </c>
       <c r="R27" t="n">
-        <v>6374517</v>
+        <v>6374327</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3427,9 +3423,19 @@
           <t>2025-10-04</t>
         </is>
       </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-10-04</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3445,22 +3451,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128904429</v>
+        <v>128903661</v>
       </c>
       <c r="B28" t="n">
-        <v>91560</v>
+        <v>92860</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3468,48 +3474,44 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5442</v>
+        <v>5966</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Ekelund, Sm</t>
+          <t>Draggöl, Stora Ramm, Sm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>584130</v>
+        <v>584164</v>
       </c>
       <c r="R28" t="n">
-        <v>6374515</v>
+        <v>6374343</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3536,9 +3538,19 @@
           <t>2025-10-04</t>
         </is>
       </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-10-04</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3554,22 +3566,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128903578</v>
+        <v>128904111</v>
       </c>
       <c r="B29" t="n">
-        <v>92859</v>
+        <v>57724</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3577,44 +3589,49 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5966</v>
+        <v>100049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Draggöl, Stora Ramm, Sm</t>
+          <t>E, Sm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>584236</v>
+        <v>584212</v>
       </c>
       <c r="R29" t="n">
-        <v>6374327</v>
+        <v>6374329</v>
       </c>
       <c r="S29" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3641,50 +3658,39 @@
           <t>2025-10-04</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>10:30</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-10-04</t>
         </is>
       </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>15:00</t>
-        </is>
-      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128903661</v>
+        <v>128904408</v>
       </c>
       <c r="B30" t="n">
-        <v>92859</v>
+        <v>91561</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3692,44 +3698,48 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5966</v>
+        <v>5442</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Draggöl, Stora Ramm, Sm</t>
+          <t>Ekelund, Sm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>584164</v>
+        <v>584143</v>
       </c>
       <c r="R30" t="n">
-        <v>6374343</v>
+        <v>6374517</v>
       </c>
       <c r="S30" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3756,19 +3766,9 @@
           <t>2025-10-04</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>10:30</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-10-04</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>15:00</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3784,22 +3784,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128904268</v>
+        <v>128904429</v>
       </c>
       <c r="B31" t="n">
-        <v>79660</v>
+        <v>91561</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3807,25 +3807,33 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6453</v>
+        <v>5442</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
@@ -3834,10 +3842,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>584121</v>
+        <v>584130</v>
       </c>
       <c r="R31" t="n">
-        <v>6374409</v>
+        <v>6374515</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3897,10 +3905,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128904111</v>
+        <v>128904268</v>
       </c>
       <c r="B32" t="n">
-        <v>57724</v>
+        <v>79660</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3908,46 +3916,37 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>E, Sm</t>
+          <t>Ekelund, Sm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>584212</v>
+        <v>584121</v>
       </c>
       <c r="R32" t="n">
-        <v>6374329</v>
+        <v>6374409</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3988,6 +3987,7 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -4009,7 +4009,7 @@
         <v>128903926</v>
       </c>
       <c r="B33" t="n">
-        <v>92859</v>
+        <v>92860</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4124,7 +4124,7 @@
         <v>128903960</v>
       </c>
       <c r="B34" t="n">
-        <v>92821</v>
+        <v>92822</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4340,7 +4340,7 @@
         <v>128903654</v>
       </c>
       <c r="B36" t="n">
-        <v>92859</v>
+        <v>92860</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4566,7 +4566,7 @@
         <v>128903593</v>
       </c>
       <c r="B38" t="n">
-        <v>92859</v>
+        <v>92860</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4681,7 +4681,7 @@
         <v>128904385</v>
       </c>
       <c r="B39" t="n">
-        <v>92859</v>
+        <v>92860</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4787,48 +4787,59 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128897896</v>
+        <v>128904323</v>
       </c>
       <c r="B40" t="n">
-        <v>96300</v>
+        <v>92860</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>2180</v>
+        <v>5966</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Draggöl, Draggöl, Sm</t>
+          <t>Ekelund, Sm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>584067</v>
+        <v>584175</v>
       </c>
       <c r="R40" t="n">
-        <v>6374669</v>
+        <v>6374451</v>
       </c>
       <c r="S40" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4855,98 +4866,78 @@
           <t>2025-10-04</t>
         </is>
       </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>13:31</t>
-        </is>
-      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-10-04</t>
         </is>
       </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>13:31</t>
-        </is>
-      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Kristian  Norrby</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Kristian  Norrby</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128904323</v>
+        <v>128897896</v>
       </c>
       <c r="B41" t="n">
-        <v>92859</v>
+        <v>96301</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5966</v>
+        <v>2180</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Ekelund, Sm</t>
+          <t>Draggöl, Draggöl, Sm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>584175</v>
+        <v>584067</v>
       </c>
       <c r="R41" t="n">
-        <v>6374451</v>
+        <v>6374669</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4973,30 +4964,39 @@
           <t>2025-10-04</t>
         </is>
       </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>13:31</t>
+        </is>
+      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-10-04</t>
         </is>
       </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>13:31</t>
+        </is>
+      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Kristian  Norrby</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Kristian  Norrby</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
@@ -5006,7 +5006,7 @@
         <v>128897155</v>
       </c>
       <c r="B42" t="n">
-        <v>96300</v>
+        <v>96301</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5110,10 +5110,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128897364</v>
+        <v>128897073</v>
       </c>
       <c r="B43" t="n">
-        <v>92859</v>
+        <v>79660</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5121,21 +5121,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5145,10 +5145,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>584139</v>
+        <v>584164</v>
       </c>
       <c r="R43" t="n">
-        <v>6374551</v>
+        <v>6374466</v>
       </c>
       <c r="S43" t="n">
         <v>2</v>
@@ -5180,7 +5180,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5190,7 +5190,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5217,10 +5217,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128897073</v>
+        <v>128897364</v>
       </c>
       <c r="B44" t="n">
-        <v>79660</v>
+        <v>92860</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5228,21 +5228,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5252,10 +5252,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>584164</v>
+        <v>584139</v>
       </c>
       <c r="R44" t="n">
-        <v>6374466</v>
+        <v>6374551</v>
       </c>
       <c r="S44" t="n">
         <v>2</v>
@@ -5287,7 +5287,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5297,7 +5297,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5324,10 +5324,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128903940</v>
+        <v>128903690</v>
       </c>
       <c r="B45" t="n">
-        <v>92859</v>
+        <v>79660</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5335,28 +5335,24 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
       <c r="N45" t="inlineStr"/>
@@ -5366,10 +5362,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>584166</v>
+        <v>584120</v>
       </c>
       <c r="R45" t="n">
-        <v>6374449</v>
+        <v>6374392</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -5439,10 +5435,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128903690</v>
+        <v>128903940</v>
       </c>
       <c r="B46" t="n">
-        <v>79660</v>
+        <v>92860</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5450,24 +5446,28 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
       <c r="N46" t="inlineStr"/>
@@ -5477,10 +5477,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>584120</v>
+        <v>584166</v>
       </c>
       <c r="R46" t="n">
-        <v>6374392</v>
+        <v>6374449</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -6108,7 +6108,7 @@
         <v>128908500</v>
       </c>
       <c r="B52" t="n">
-        <v>92813</v>
+        <v>92814</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6219,7 +6219,7 @@
         <v>128904124</v>
       </c>
       <c r="B53" t="n">
-        <v>92847</v>
+        <v>92848</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6324,7 +6324,7 @@
         <v>129193511</v>
       </c>
       <c r="B54" t="n">
-        <v>91560</v>
+        <v>91561</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6429,7 +6429,7 @@
         <v>129193484</v>
       </c>
       <c r="B55" t="n">
-        <v>92821</v>
+        <v>92822</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>

--- a/artfynd/A 45800-2025 artfynd.xlsx
+++ b/artfynd/A 45800-2025 artfynd.xlsx
@@ -2041,10 +2041,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128903951</v>
+        <v>128903544</v>
       </c>
       <c r="B15" t="n">
-        <v>92860</v>
+        <v>79660</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2052,28 +2052,24 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
@@ -2083,10 +2079,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>584183</v>
+        <v>584191</v>
       </c>
       <c r="R15" t="n">
-        <v>6374596</v>
+        <v>6374331</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2156,10 +2152,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128903544</v>
+        <v>128903951</v>
       </c>
       <c r="B16" t="n">
-        <v>79660</v>
+        <v>92860</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2167,24 +2163,28 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
@@ -2194,10 +2194,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>584191</v>
+        <v>584183</v>
       </c>
       <c r="R16" t="n">
-        <v>6374331</v>
+        <v>6374596</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2270,7 +2270,7 @@
         <v>128903715</v>
       </c>
       <c r="B17" t="n">
-        <v>96301</v>
+        <v>96302</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2379,48 +2379,51 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128897118</v>
+        <v>128904192</v>
       </c>
       <c r="B18" t="n">
-        <v>96301</v>
+        <v>79660</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2180</v>
+        <v>6453</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Draggöl, Draggöl, Sm</t>
+          <t>Ekelund, Sm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>584190</v>
+        <v>584149</v>
       </c>
       <c r="R18" t="n">
-        <v>6374486</v>
+        <v>6374399</v>
       </c>
       <c r="S18" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2447,39 +2450,30 @@
           <t>2025-10-04</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>13:05</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-10-04</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>13:05</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Kristian  Norrby</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kristian  Norrby</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -2595,51 +2589,48 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128904192</v>
+        <v>128897118</v>
       </c>
       <c r="B20" t="n">
-        <v>79660</v>
+        <v>96302</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6453</v>
+        <v>2180</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Ekelund, Sm</t>
+          <t>Draggöl, Draggöl, Sm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>584149</v>
+        <v>584190</v>
       </c>
       <c r="R20" t="n">
-        <v>6374399</v>
+        <v>6374486</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2666,30 +2657,39 @@
           <t>2025-10-04</t>
         </is>
       </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-10-04</t>
         </is>
       </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Kristian  Norrby</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Kristian  Norrby</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -3244,7 +3244,7 @@
         <v>128895716</v>
       </c>
       <c r="B26" t="n">
-        <v>96301</v>
+        <v>96302</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3348,10 +3348,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128903578</v>
+        <v>128904268</v>
       </c>
       <c r="B27" t="n">
-        <v>92860</v>
+        <v>79660</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3359,44 +3359,40 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Draggöl, Stora Ramm, Sm</t>
+          <t>Ekelund, Sm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>584236</v>
+        <v>584121</v>
       </c>
       <c r="R27" t="n">
-        <v>6374327</v>
+        <v>6374409</v>
       </c>
       <c r="S27" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3423,19 +3419,9 @@
           <t>2025-10-04</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>10:30</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-10-04</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>15:00</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3451,19 +3437,19 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128903661</v>
+        <v>128903578</v>
       </c>
       <c r="B28" t="n">
         <v>92860</v>
@@ -3505,10 +3491,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>584164</v>
+        <v>584236</v>
       </c>
       <c r="R28" t="n">
-        <v>6374343</v>
+        <v>6374327</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3578,10 +3564,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128904111</v>
+        <v>128903661</v>
       </c>
       <c r="B29" t="n">
-        <v>57724</v>
+        <v>92860</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3589,49 +3575,44 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100049</v>
+        <v>5966</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>E, Sm</t>
+          <t>Draggöl, Stora Ramm, Sm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>584212</v>
+        <v>584164</v>
       </c>
       <c r="R29" t="n">
-        <v>6374329</v>
+        <v>6374343</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3658,36 +3639,47 @@
           <t>2025-10-04</t>
         </is>
       </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-10-04</t>
         </is>
       </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128904408</v>
+        <v>128904429</v>
       </c>
       <c r="B30" t="n">
         <v>91561</v>
@@ -3717,7 +3709,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -3733,10 +3725,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>584143</v>
+        <v>584130</v>
       </c>
       <c r="R30" t="n">
-        <v>6374517</v>
+        <v>6374515</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3796,7 +3788,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128904429</v>
+        <v>128904408</v>
       </c>
       <c r="B31" t="n">
         <v>91561</v>
@@ -3826,7 +3818,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -3842,10 +3834,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>584130</v>
+        <v>584143</v>
       </c>
       <c r="R31" t="n">
-        <v>6374515</v>
+        <v>6374517</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3905,10 +3897,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128904268</v>
+        <v>128904111</v>
       </c>
       <c r="B32" t="n">
-        <v>79660</v>
+        <v>57724</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3916,37 +3908,46 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Ekelund, Sm</t>
+          <t>E, Sm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>584121</v>
+        <v>584212</v>
       </c>
       <c r="R32" t="n">
-        <v>6374409</v>
+        <v>6374329</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3987,7 +3988,6 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -4899,7 +4899,7 @@
         <v>128897896</v>
       </c>
       <c r="B41" t="n">
-        <v>96301</v>
+        <v>96302</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5006,7 +5006,7 @@
         <v>128897155</v>
       </c>
       <c r="B42" t="n">
-        <v>96301</v>
+        <v>96302</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>

--- a/artfynd/A 45800-2025 artfynd.xlsx
+++ b/artfynd/A 45800-2025 artfynd.xlsx
@@ -2041,10 +2041,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128903544</v>
+        <v>128903951</v>
       </c>
       <c r="B15" t="n">
-        <v>79660</v>
+        <v>92863</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2052,24 +2052,28 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
@@ -2079,10 +2083,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>584191</v>
+        <v>584183</v>
       </c>
       <c r="R15" t="n">
-        <v>6374331</v>
+        <v>6374596</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2152,10 +2156,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128903951</v>
+        <v>128903544</v>
       </c>
       <c r="B16" t="n">
-        <v>92860</v>
+        <v>79662</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2163,28 +2167,24 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
@@ -2194,10 +2194,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>584183</v>
+        <v>584191</v>
       </c>
       <c r="R16" t="n">
-        <v>6374596</v>
+        <v>6374331</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2267,10 +2267,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128903715</v>
+        <v>128897118</v>
       </c>
       <c r="B17" t="n">
-        <v>96302</v>
+        <v>96306</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2296,23 +2296,19 @@
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Draggöl, Stora Ramm, Sm</t>
+          <t>Draggöl, Draggöl, Sm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>584142</v>
+        <v>584190</v>
       </c>
       <c r="R17" t="n">
-        <v>6374419</v>
+        <v>6374486</v>
       </c>
       <c r="S17" t="n">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2341,7 +2337,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2351,7 +2347,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2360,70 +2356,70 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Kristian  Norrby</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Kristian  Norrby</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128904192</v>
+        <v>128903715</v>
       </c>
       <c r="B18" t="n">
-        <v>79660</v>
+        <v>96306</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6453</v>
+        <v>2180</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Ekelund, Sm</t>
+          <t>Draggöl, Stora Ramm, Sm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>584149</v>
+        <v>584142</v>
       </c>
       <c r="R18" t="n">
-        <v>6374399</v>
+        <v>6374419</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2450,9 +2446,19 @@
           <t>2025-10-04</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-10-04</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2468,12 +2474,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -2483,7 +2489,7 @@
         <v>128904395</v>
       </c>
       <c r="B19" t="n">
-        <v>92860</v>
+        <v>92863</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2589,48 +2595,51 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128897118</v>
+        <v>128904192</v>
       </c>
       <c r="B20" t="n">
-        <v>96302</v>
+        <v>79662</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2180</v>
+        <v>6453</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Draggöl, Draggöl, Sm</t>
+          <t>Ekelund, Sm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>584190</v>
+        <v>584149</v>
       </c>
       <c r="R20" t="n">
-        <v>6374486</v>
+        <v>6374399</v>
       </c>
       <c r="S20" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2657,49 +2666,40 @@
           <t>2025-10-04</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>13:05</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-10-04</t>
         </is>
       </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>13:05</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Kristian  Norrby</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Kristian  Norrby</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128904443</v>
+        <v>128904450</v>
       </c>
       <c r="B21" t="n">
-        <v>57724</v>
+        <v>79662</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2707,35 +2707,26 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2743,10 +2734,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>584113</v>
+        <v>584145</v>
       </c>
       <c r="R21" t="n">
-        <v>6374565</v>
+        <v>6374604</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2787,6 +2778,7 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2808,7 +2800,7 @@
         <v>128904088</v>
       </c>
       <c r="B22" t="n">
-        <v>79660</v>
+        <v>79662</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2906,10 +2898,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128904450</v>
+        <v>128904443</v>
       </c>
       <c r="B23" t="n">
-        <v>79660</v>
+        <v>57724</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2917,26 +2909,35 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -2944,10 +2945,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>584145</v>
+        <v>584113</v>
       </c>
       <c r="R23" t="n">
-        <v>6374604</v>
+        <v>6374565</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2988,7 +2989,6 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3007,55 +3007,48 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128903851</v>
+        <v>128895716</v>
       </c>
       <c r="B24" t="n">
-        <v>91561</v>
+        <v>96306</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5442</v>
+        <v>2180</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Draggöl, Stora Ramm, Sm</t>
+          <t>Draggöl, Draggöl, Sm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>584167</v>
+        <v>584171</v>
       </c>
       <c r="R24" t="n">
-        <v>6374518</v>
+        <v>6374322</v>
       </c>
       <c r="S24" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3084,7 +3077,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3094,7 +3087,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3103,65 +3096,59 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128903521</v>
+        <v>128903851</v>
       </c>
       <c r="B25" t="n">
-        <v>58097</v>
+        <v>91564</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>103015</v>
+        <v>5442</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3169,10 +3156,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>584198</v>
+        <v>584167</v>
       </c>
       <c r="R25" t="n">
-        <v>6374339</v>
+        <v>6374518</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3223,6 +3210,7 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3241,10 +3229,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128895716</v>
+        <v>128903521</v>
       </c>
       <c r="B26" t="n">
-        <v>96302</v>
+        <v>58097</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3252,37 +3240,49 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2180</v>
+        <v>103015</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Draggöl, Draggöl, Sm</t>
+          <t>Draggöl, Stora Ramm, Sm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>584171</v>
+        <v>584198</v>
       </c>
       <c r="R26" t="n">
-        <v>6374322</v>
+        <v>6374339</v>
       </c>
       <c r="S26" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3311,7 +3311,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3336,22 +3336,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128904268</v>
+        <v>128904408</v>
       </c>
       <c r="B27" t="n">
-        <v>79660</v>
+        <v>91564</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3359,25 +3359,33 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6453</v>
+        <v>5442</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
@@ -3386,10 +3394,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>584121</v>
+        <v>584143</v>
       </c>
       <c r="R27" t="n">
-        <v>6374409</v>
+        <v>6374517</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3449,10 +3457,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128903578</v>
+        <v>128904429</v>
       </c>
       <c r="B28" t="n">
-        <v>92860</v>
+        <v>91564</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3460,44 +3468,48 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5966</v>
+        <v>5442</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Draggöl, Stora Ramm, Sm</t>
+          <t>Ekelund, Sm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>584236</v>
+        <v>584130</v>
       </c>
       <c r="R28" t="n">
-        <v>6374327</v>
+        <v>6374515</v>
       </c>
       <c r="S28" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3524,19 +3536,9 @@
           <t>2025-10-04</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>10:30</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-10-04</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>15:00</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3552,22 +3554,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128903661</v>
+        <v>128903578</v>
       </c>
       <c r="B29" t="n">
-        <v>92860</v>
+        <v>92863</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3606,10 +3608,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>584164</v>
+        <v>584236</v>
       </c>
       <c r="R29" t="n">
-        <v>6374343</v>
+        <v>6374327</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3679,10 +3681,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128904429</v>
+        <v>128903661</v>
       </c>
       <c r="B30" t="n">
-        <v>91561</v>
+        <v>92863</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3690,48 +3692,44 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5442</v>
+        <v>5966</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Ekelund, Sm</t>
+          <t>Draggöl, Stora Ramm, Sm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>584130</v>
+        <v>584164</v>
       </c>
       <c r="R30" t="n">
-        <v>6374515</v>
+        <v>6374343</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3758,9 +3756,19 @@
           <t>2025-10-04</t>
         </is>
       </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-10-04</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3776,22 +3784,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128904408</v>
+        <v>128904111</v>
       </c>
       <c r="B31" t="n">
-        <v>91561</v>
+        <v>57724</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3799,45 +3807,46 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>bålar</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Ekelund, Sm</t>
+          <t>E, Sm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>584143</v>
+        <v>584212</v>
       </c>
       <c r="R31" t="n">
-        <v>6374517</v>
+        <v>6374329</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3878,7 +3887,6 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -3897,10 +3905,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128904111</v>
+        <v>128904268</v>
       </c>
       <c r="B32" t="n">
-        <v>57724</v>
+        <v>79662</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3908,46 +3916,37 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>E, Sm</t>
+          <t>Ekelund, Sm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>584212</v>
+        <v>584121</v>
       </c>
       <c r="R32" t="n">
-        <v>6374329</v>
+        <v>6374409</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3988,6 +3987,7 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -4009,7 +4009,7 @@
         <v>128903926</v>
       </c>
       <c r="B33" t="n">
-        <v>92860</v>
+        <v>92863</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4124,7 +4124,7 @@
         <v>128903960</v>
       </c>
       <c r="B34" t="n">
-        <v>92822</v>
+        <v>92825</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4239,7 +4239,7 @@
         <v>128904329</v>
       </c>
       <c r="B35" t="n">
-        <v>79660</v>
+        <v>79662</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4340,7 +4340,7 @@
         <v>128903654</v>
       </c>
       <c r="B36" t="n">
-        <v>92860</v>
+        <v>92863</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4455,7 +4455,7 @@
         <v>128903739</v>
       </c>
       <c r="B37" t="n">
-        <v>79660</v>
+        <v>79662</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4566,7 +4566,7 @@
         <v>128903593</v>
       </c>
       <c r="B38" t="n">
-        <v>92860</v>
+        <v>92863</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4681,7 +4681,7 @@
         <v>128904385</v>
       </c>
       <c r="B39" t="n">
-        <v>92860</v>
+        <v>92863</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4787,59 +4787,48 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128904323</v>
+        <v>128897896</v>
       </c>
       <c r="B40" t="n">
-        <v>92860</v>
+        <v>96306</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5966</v>
+        <v>2180</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Ekelund, Sm</t>
+          <t>Draggöl, Draggöl, Sm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>584175</v>
+        <v>584067</v>
       </c>
       <c r="R40" t="n">
-        <v>6374451</v>
+        <v>6374669</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4866,78 +4855,98 @@
           <t>2025-10-04</t>
         </is>
       </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>13:31</t>
+        </is>
+      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-10-04</t>
         </is>
       </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>13:31</t>
+        </is>
+      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Kristian  Norrby</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Kristian  Norrby</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128897896</v>
+        <v>128904323</v>
       </c>
       <c r="B41" t="n">
-        <v>96302</v>
+        <v>92863</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>2180</v>
+        <v>5966</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Draggöl, Draggöl, Sm</t>
+          <t>Ekelund, Sm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>584067</v>
+        <v>584175</v>
       </c>
       <c r="R41" t="n">
-        <v>6374669</v>
+        <v>6374451</v>
       </c>
       <c r="S41" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4964,39 +4973,30 @@
           <t>2025-10-04</t>
         </is>
       </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>13:31</t>
-        </is>
-      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-10-04</t>
         </is>
       </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>13:31</t>
-        </is>
-      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Kristian  Norrby</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Kristian  Norrby</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
@@ -5006,7 +5006,7 @@
         <v>128897155</v>
       </c>
       <c r="B42" t="n">
-        <v>96302</v>
+        <v>96306</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5113,7 +5113,7 @@
         <v>128897073</v>
       </c>
       <c r="B43" t="n">
-        <v>79660</v>
+        <v>79662</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5220,7 +5220,7 @@
         <v>128897364</v>
       </c>
       <c r="B44" t="n">
-        <v>92860</v>
+        <v>92863</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5324,10 +5324,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128903690</v>
+        <v>128903940</v>
       </c>
       <c r="B45" t="n">
-        <v>79660</v>
+        <v>92863</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5335,24 +5335,28 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
       <c r="N45" t="inlineStr"/>
@@ -5362,10 +5366,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>584120</v>
+        <v>584166</v>
       </c>
       <c r="R45" t="n">
-        <v>6374392</v>
+        <v>6374449</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -5435,10 +5439,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128903940</v>
+        <v>128903690</v>
       </c>
       <c r="B46" t="n">
-        <v>92860</v>
+        <v>79662</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5446,28 +5450,24 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
       <c r="N46" t="inlineStr"/>
@@ -5477,10 +5477,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>584166</v>
+        <v>584120</v>
       </c>
       <c r="R46" t="n">
-        <v>6374449</v>
+        <v>6374392</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -5553,7 +5553,7 @@
         <v>128903857</v>
       </c>
       <c r="B47" t="n">
-        <v>79660</v>
+        <v>79662</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5664,7 +5664,7 @@
         <v>128904459</v>
       </c>
       <c r="B48" t="n">
-        <v>79660</v>
+        <v>79662</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5765,7 +5765,7 @@
         <v>128903869</v>
       </c>
       <c r="B49" t="n">
-        <v>79660</v>
+        <v>79662</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5881,7 +5881,7 @@
         <v>128909203</v>
       </c>
       <c r="B50" t="n">
-        <v>79631</v>
+        <v>79633</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5992,7 +5992,7 @@
         <v>128908556</v>
       </c>
       <c r="B51" t="n">
-        <v>78798</v>
+        <v>78800</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6108,7 +6108,7 @@
         <v>128908500</v>
       </c>
       <c r="B52" t="n">
-        <v>92814</v>
+        <v>92817</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6219,7 +6219,7 @@
         <v>128904124</v>
       </c>
       <c r="B53" t="n">
-        <v>92848</v>
+        <v>92851</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6324,7 +6324,7 @@
         <v>129193511</v>
       </c>
       <c r="B54" t="n">
-        <v>91561</v>
+        <v>91564</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6429,7 +6429,7 @@
         <v>129193484</v>
       </c>
       <c r="B55" t="n">
-        <v>92822</v>
+        <v>92825</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>

--- a/artfynd/A 45800-2025 artfynd.xlsx
+++ b/artfynd/A 45800-2025 artfynd.xlsx
@@ -2696,10 +2696,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128904450</v>
+        <v>128904443</v>
       </c>
       <c r="B21" t="n">
-        <v>79662</v>
+        <v>57724</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2707,26 +2707,35 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2734,10 +2743,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>584145</v>
+        <v>584113</v>
       </c>
       <c r="R21" t="n">
-        <v>6374604</v>
+        <v>6374565</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2778,7 +2787,6 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2797,7 +2805,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128904088</v>
+        <v>128904450</v>
       </c>
       <c r="B22" t="n">
         <v>79662</v>
@@ -2835,10 +2843,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>584195</v>
+        <v>584145</v>
       </c>
       <c r="R22" t="n">
-        <v>6374314</v>
+        <v>6374604</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2898,10 +2906,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128904443</v>
+        <v>128904088</v>
       </c>
       <c r="B23" t="n">
-        <v>57724</v>
+        <v>79662</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2909,35 +2917,26 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -2945,10 +2944,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>584113</v>
+        <v>584195</v>
       </c>
       <c r="R23" t="n">
-        <v>6374565</v>
+        <v>6374314</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2989,6 +2988,7 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3348,10 +3348,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128904408</v>
+        <v>128903578</v>
       </c>
       <c r="B27" t="n">
-        <v>91564</v>
+        <v>92863</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3359,48 +3359,44 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5442</v>
+        <v>5966</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Ekelund, Sm</t>
+          <t>Draggöl, Stora Ramm, Sm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>584143</v>
+        <v>584236</v>
       </c>
       <c r="R27" t="n">
-        <v>6374517</v>
+        <v>6374327</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3427,9 +3423,19 @@
           <t>2025-10-04</t>
         </is>
       </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-10-04</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3445,22 +3451,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128904429</v>
+        <v>128903661</v>
       </c>
       <c r="B28" t="n">
-        <v>91564</v>
+        <v>92863</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3468,48 +3474,44 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5442</v>
+        <v>5966</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Ekelund, Sm</t>
+          <t>Draggöl, Stora Ramm, Sm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>584130</v>
+        <v>584164</v>
       </c>
       <c r="R28" t="n">
-        <v>6374515</v>
+        <v>6374343</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3536,9 +3538,19 @@
           <t>2025-10-04</t>
         </is>
       </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-10-04</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3554,22 +3566,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128903578</v>
+        <v>128904111</v>
       </c>
       <c r="B29" t="n">
-        <v>92863</v>
+        <v>57724</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3577,44 +3589,49 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5966</v>
+        <v>100049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Draggöl, Stora Ramm, Sm</t>
+          <t>E, Sm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>584236</v>
+        <v>584212</v>
       </c>
       <c r="R29" t="n">
-        <v>6374327</v>
+        <v>6374329</v>
       </c>
       <c r="S29" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3641,50 +3658,39 @@
           <t>2025-10-04</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>10:30</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-10-04</t>
         </is>
       </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>15:00</t>
-        </is>
-      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128903661</v>
+        <v>128904268</v>
       </c>
       <c r="B30" t="n">
-        <v>92863</v>
+        <v>79662</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3692,44 +3698,40 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Draggöl, Stora Ramm, Sm</t>
+          <t>Ekelund, Sm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>584164</v>
+        <v>584121</v>
       </c>
       <c r="R30" t="n">
-        <v>6374343</v>
+        <v>6374409</v>
       </c>
       <c r="S30" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3756,19 +3758,9 @@
           <t>2025-10-04</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>10:30</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-10-04</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>15:00</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3784,22 +3776,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128904111</v>
+        <v>128904408</v>
       </c>
       <c r="B31" t="n">
-        <v>57724</v>
+        <v>91564</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3807,46 +3799,45 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>E, Sm</t>
+          <t>Ekelund, Sm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>584212</v>
+        <v>584143</v>
       </c>
       <c r="R31" t="n">
-        <v>6374329</v>
+        <v>6374517</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3887,6 +3878,7 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -3905,10 +3897,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128904268</v>
+        <v>128904429</v>
       </c>
       <c r="B32" t="n">
-        <v>79662</v>
+        <v>91564</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3916,25 +3908,33 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6453</v>
+        <v>5442</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
@@ -3943,10 +3943,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>584121</v>
+        <v>584130</v>
       </c>
       <c r="R32" t="n">
-        <v>6374409</v>
+        <v>6374515</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -5110,10 +5110,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128897073</v>
+        <v>128897364</v>
       </c>
       <c r="B43" t="n">
-        <v>79662</v>
+        <v>92863</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5121,21 +5121,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5145,10 +5145,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>584164</v>
+        <v>584139</v>
       </c>
       <c r="R43" t="n">
-        <v>6374466</v>
+        <v>6374551</v>
       </c>
       <c r="S43" t="n">
         <v>2</v>
@@ -5180,7 +5180,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5190,7 +5190,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5217,10 +5217,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128897364</v>
+        <v>128897073</v>
       </c>
       <c r="B44" t="n">
-        <v>92863</v>
+        <v>79662</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5228,21 +5228,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5252,10 +5252,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>584139</v>
+        <v>584164</v>
       </c>
       <c r="R44" t="n">
-        <v>6374551</v>
+        <v>6374466</v>
       </c>
       <c r="S44" t="n">
         <v>2</v>
@@ -5287,7 +5287,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5297,7 +5297,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AD44" t="b">

--- a/artfynd/A 45800-2025 artfynd.xlsx
+++ b/artfynd/A 45800-2025 artfynd.xlsx
@@ -2044,7 +2044,7 @@
         <v>128903951</v>
       </c>
       <c r="B15" t="n">
-        <v>92863</v>
+        <v>92865</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2159,7 +2159,7 @@
         <v>128903544</v>
       </c>
       <c r="B16" t="n">
-        <v>79662</v>
+        <v>79663</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2267,48 +2267,59 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128897118</v>
+        <v>128904395</v>
       </c>
       <c r="B17" t="n">
-        <v>96306</v>
+        <v>92865</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2180</v>
+        <v>5966</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Draggöl, Draggöl, Sm</t>
+          <t>Ekelund, Sm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>584190</v>
+        <v>584177</v>
       </c>
       <c r="R17" t="n">
-        <v>6374486</v>
+        <v>6374515</v>
       </c>
       <c r="S17" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2335,91 +2346,81 @@
           <t>2025-10-04</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>13:05</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-10-04</t>
         </is>
       </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>13:05</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kristian  Norrby</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kristian  Norrby</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128903715</v>
+        <v>128904192</v>
       </c>
       <c r="B18" t="n">
-        <v>96306</v>
+        <v>79663</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2180</v>
+        <v>6453</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Draggöl, Stora Ramm, Sm</t>
+          <t>Ekelund, Sm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>584142</v>
+        <v>584149</v>
       </c>
       <c r="R18" t="n">
-        <v>6374419</v>
+        <v>6374399</v>
       </c>
       <c r="S18" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2446,19 +2447,9 @@
           <t>2025-10-04</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>10:30</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-10-04</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>15:00</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2474,71 +2465,60 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128904395</v>
+        <v>128897118</v>
       </c>
       <c r="B19" t="n">
-        <v>92863</v>
+        <v>96308</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5966</v>
+        <v>2180</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Ekelund, Sm</t>
+          <t>Draggöl, Draggöl, Sm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>584177</v>
+        <v>584190</v>
       </c>
       <c r="R19" t="n">
-        <v>6374515</v>
+        <v>6374486</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2565,81 +2545,91 @@
           <t>2025-10-04</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-10-04</t>
         </is>
       </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Kristian  Norrby</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Kristian  Norrby</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128904192</v>
+        <v>128903715</v>
       </c>
       <c r="B20" t="n">
-        <v>79662</v>
+        <v>96308</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6453</v>
+        <v>2180</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Ekelund, Sm</t>
+          <t>Draggöl, Stora Ramm, Sm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>584149</v>
+        <v>584142</v>
       </c>
       <c r="R20" t="n">
-        <v>6374399</v>
+        <v>6374419</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2666,9 +2656,19 @@
           <t>2025-10-04</t>
         </is>
       </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-10-04</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2684,22 +2684,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128904443</v>
+        <v>128904088</v>
       </c>
       <c r="B21" t="n">
-        <v>57724</v>
+        <v>79663</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2707,35 +2707,26 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2743,10 +2734,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>584113</v>
+        <v>584195</v>
       </c>
       <c r="R21" t="n">
-        <v>6374565</v>
+        <v>6374314</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2787,6 +2778,7 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2808,7 +2800,7 @@
         <v>128904450</v>
       </c>
       <c r="B22" t="n">
-        <v>79662</v>
+        <v>79663</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2906,10 +2898,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128904088</v>
+        <v>128904443</v>
       </c>
       <c r="B23" t="n">
-        <v>79662</v>
+        <v>57724</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2917,26 +2909,35 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -2944,10 +2945,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>584195</v>
+        <v>584113</v>
       </c>
       <c r="R23" t="n">
-        <v>6374314</v>
+        <v>6374565</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2988,7 +2989,6 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3007,48 +3007,55 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128895716</v>
+        <v>128903851</v>
       </c>
       <c r="B24" t="n">
-        <v>96306</v>
+        <v>91566</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2180</v>
+        <v>5442</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Draggöl, Draggöl, Sm</t>
+          <t>Draggöl, Stora Ramm, Sm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>584171</v>
+        <v>584167</v>
       </c>
       <c r="R24" t="n">
-        <v>6374322</v>
+        <v>6374518</v>
       </c>
       <c r="S24" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3077,7 +3084,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3087,7 +3094,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3096,59 +3103,65 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128903851</v>
+        <v>128903521</v>
       </c>
       <c r="B25" t="n">
-        <v>91564</v>
+        <v>58097</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5442</v>
+        <v>103015</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr"/>
+          <t>4</t>
+        </is>
+      </c>
       <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3156,10 +3169,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>584167</v>
+        <v>584198</v>
       </c>
       <c r="R25" t="n">
-        <v>6374518</v>
+        <v>6374339</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3210,7 +3223,6 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3229,10 +3241,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128903521</v>
+        <v>128895716</v>
       </c>
       <c r="B26" t="n">
-        <v>58097</v>
+        <v>96308</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3240,49 +3252,37 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>103015</v>
+        <v>2180</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr"/>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Draggöl, Stora Ramm, Sm</t>
+          <t>Draggöl, Draggöl, Sm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>584198</v>
+        <v>584171</v>
       </c>
       <c r="R26" t="n">
-        <v>6374339</v>
+        <v>6374322</v>
       </c>
       <c r="S26" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3311,7 +3311,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3336,22 +3336,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128903578</v>
+        <v>128904408</v>
       </c>
       <c r="B27" t="n">
-        <v>92863</v>
+        <v>91566</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3359,44 +3359,48 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5966</v>
+        <v>5442</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Draggöl, Stora Ramm, Sm</t>
+          <t>Ekelund, Sm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>584236</v>
+        <v>584143</v>
       </c>
       <c r="R27" t="n">
-        <v>6374327</v>
+        <v>6374517</v>
       </c>
       <c r="S27" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3423,19 +3427,9 @@
           <t>2025-10-04</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>10:30</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-10-04</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>15:00</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3451,22 +3445,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128903661</v>
+        <v>128904429</v>
       </c>
       <c r="B28" t="n">
-        <v>92863</v>
+        <v>91566</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3474,44 +3468,48 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5966</v>
+        <v>5442</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Draggöl, Stora Ramm, Sm</t>
+          <t>Ekelund, Sm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>584164</v>
+        <v>584130</v>
       </c>
       <c r="R28" t="n">
-        <v>6374343</v>
+        <v>6374515</v>
       </c>
       <c r="S28" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3538,19 +3536,9 @@
           <t>2025-10-04</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>10:30</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-10-04</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>15:00</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3566,22 +3554,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128904111</v>
+        <v>128903578</v>
       </c>
       <c r="B29" t="n">
-        <v>57724</v>
+        <v>92865</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3589,49 +3577,44 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100049</v>
+        <v>5966</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>E, Sm</t>
+          <t>Draggöl, Stora Ramm, Sm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>584212</v>
+        <v>584236</v>
       </c>
       <c r="R29" t="n">
-        <v>6374329</v>
+        <v>6374327</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3658,39 +3641,50 @@
           <t>2025-10-04</t>
         </is>
       </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-10-04</t>
         </is>
       </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128904268</v>
+        <v>128903661</v>
       </c>
       <c r="B30" t="n">
-        <v>79662</v>
+        <v>92865</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3698,40 +3692,44 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Ekelund, Sm</t>
+          <t>Draggöl, Stora Ramm, Sm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>584121</v>
+        <v>584164</v>
       </c>
       <c r="R30" t="n">
-        <v>6374409</v>
+        <v>6374343</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3758,9 +3756,19 @@
           <t>2025-10-04</t>
         </is>
       </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-10-04</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3776,22 +3784,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128904408</v>
+        <v>128904111</v>
       </c>
       <c r="B31" t="n">
-        <v>91564</v>
+        <v>57724</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3799,45 +3807,46 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>bålar</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Ekelund, Sm</t>
+          <t>E, Sm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>584143</v>
+        <v>584212</v>
       </c>
       <c r="R31" t="n">
-        <v>6374517</v>
+        <v>6374329</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3878,7 +3887,6 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -3897,10 +3905,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128904429</v>
+        <v>128904268</v>
       </c>
       <c r="B32" t="n">
-        <v>91564</v>
+        <v>79663</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3908,33 +3916,25 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5442</v>
+        <v>6453</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
@@ -3943,10 +3943,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>584130</v>
+        <v>584121</v>
       </c>
       <c r="R32" t="n">
-        <v>6374515</v>
+        <v>6374409</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4009,7 +4009,7 @@
         <v>128903926</v>
       </c>
       <c r="B33" t="n">
-        <v>92863</v>
+        <v>92865</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4124,7 +4124,7 @@
         <v>128903960</v>
       </c>
       <c r="B34" t="n">
-        <v>92825</v>
+        <v>92827</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4239,7 +4239,7 @@
         <v>128904329</v>
       </c>
       <c r="B35" t="n">
-        <v>79662</v>
+        <v>79663</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4340,7 +4340,7 @@
         <v>128903654</v>
       </c>
       <c r="B36" t="n">
-        <v>92863</v>
+        <v>92865</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4455,7 +4455,7 @@
         <v>128903739</v>
       </c>
       <c r="B37" t="n">
-        <v>79662</v>
+        <v>79663</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4566,7 +4566,7 @@
         <v>128903593</v>
       </c>
       <c r="B38" t="n">
-        <v>92863</v>
+        <v>92865</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4681,7 +4681,7 @@
         <v>128904385</v>
       </c>
       <c r="B39" t="n">
-        <v>92863</v>
+        <v>92865</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4787,48 +4787,59 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128897896</v>
+        <v>128904323</v>
       </c>
       <c r="B40" t="n">
-        <v>96306</v>
+        <v>92865</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>2180</v>
+        <v>5966</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Draggöl, Draggöl, Sm</t>
+          <t>Ekelund, Sm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>584067</v>
+        <v>584175</v>
       </c>
       <c r="R40" t="n">
-        <v>6374669</v>
+        <v>6374451</v>
       </c>
       <c r="S40" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4855,98 +4866,78 @@
           <t>2025-10-04</t>
         </is>
       </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>13:31</t>
-        </is>
-      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-10-04</t>
         </is>
       </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>13:31</t>
-        </is>
-      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Kristian  Norrby</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Kristian  Norrby</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128904323</v>
+        <v>128897896</v>
       </c>
       <c r="B41" t="n">
-        <v>92863</v>
+        <v>96308</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5966</v>
+        <v>2180</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Ekelund, Sm</t>
+          <t>Draggöl, Draggöl, Sm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>584175</v>
+        <v>584067</v>
       </c>
       <c r="R41" t="n">
-        <v>6374451</v>
+        <v>6374669</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4973,30 +4964,39 @@
           <t>2025-10-04</t>
         </is>
       </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>13:31</t>
+        </is>
+      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-10-04</t>
         </is>
       </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>13:31</t>
+        </is>
+      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Kristian  Norrby</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Kristian  Norrby</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
@@ -5006,7 +5006,7 @@
         <v>128897155</v>
       </c>
       <c r="B42" t="n">
-        <v>96306</v>
+        <v>96308</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5110,10 +5110,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128897364</v>
+        <v>128897073</v>
       </c>
       <c r="B43" t="n">
-        <v>92863</v>
+        <v>79663</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5121,21 +5121,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5145,10 +5145,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>584139</v>
+        <v>584164</v>
       </c>
       <c r="R43" t="n">
-        <v>6374551</v>
+        <v>6374466</v>
       </c>
       <c r="S43" t="n">
         <v>2</v>
@@ -5180,7 +5180,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5190,7 +5190,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5217,10 +5217,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128897073</v>
+        <v>128897364</v>
       </c>
       <c r="B44" t="n">
-        <v>79662</v>
+        <v>92865</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5228,21 +5228,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5252,10 +5252,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>584164</v>
+        <v>584139</v>
       </c>
       <c r="R44" t="n">
-        <v>6374466</v>
+        <v>6374551</v>
       </c>
       <c r="S44" t="n">
         <v>2</v>
@@ -5287,7 +5287,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5297,7 +5297,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5327,7 +5327,7 @@
         <v>128903940</v>
       </c>
       <c r="B45" t="n">
-        <v>92863</v>
+        <v>92865</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5442,7 +5442,7 @@
         <v>128903690</v>
       </c>
       <c r="B46" t="n">
-        <v>79662</v>
+        <v>79663</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5553,7 +5553,7 @@
         <v>128903857</v>
       </c>
       <c r="B47" t="n">
-        <v>79662</v>
+        <v>79663</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5664,7 +5664,7 @@
         <v>128904459</v>
       </c>
       <c r="B48" t="n">
-        <v>79662</v>
+        <v>79663</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5765,7 +5765,7 @@
         <v>128903869</v>
       </c>
       <c r="B49" t="n">
-        <v>79662</v>
+        <v>79663</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5881,7 +5881,7 @@
         <v>128909203</v>
       </c>
       <c r="B50" t="n">
-        <v>79633</v>
+        <v>79634</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5992,7 +5992,7 @@
         <v>128908556</v>
       </c>
       <c r="B51" t="n">
-        <v>78800</v>
+        <v>78801</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6108,7 +6108,7 @@
         <v>128908500</v>
       </c>
       <c r="B52" t="n">
-        <v>92817</v>
+        <v>92819</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6219,7 +6219,7 @@
         <v>128904124</v>
       </c>
       <c r="B53" t="n">
-        <v>92851</v>
+        <v>92853</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6324,7 +6324,7 @@
         <v>129193511</v>
       </c>
       <c r="B54" t="n">
-        <v>91564</v>
+        <v>91566</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6429,7 +6429,7 @@
         <v>129193484</v>
       </c>
       <c r="B55" t="n">
-        <v>92825</v>
+        <v>92827</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>

--- a/artfynd/A 45800-2025 artfynd.xlsx
+++ b/artfynd/A 45800-2025 artfynd.xlsx
@@ -6108,7 +6108,7 @@
         <v>128908500</v>
       </c>
       <c r="B52" t="n">
-        <v>92819</v>
+        <v>92823</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6219,7 +6219,7 @@
         <v>128904124</v>
       </c>
       <c r="B53" t="n">
-        <v>92853</v>
+        <v>92857</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6324,7 +6324,7 @@
         <v>129193511</v>
       </c>
       <c r="B54" t="n">
-        <v>91566</v>
+        <v>91570</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6429,7 +6429,7 @@
         <v>129193484</v>
       </c>
       <c r="B55" t="n">
-        <v>92827</v>
+        <v>92831</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>

--- a/artfynd/A 45800-2025 artfynd.xlsx
+++ b/artfynd/A 45800-2025 artfynd.xlsx
@@ -6219,7 +6219,7 @@
         <v>128904124</v>
       </c>
       <c r="B53" t="n">
-        <v>92857</v>
+        <v>92858</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6324,7 +6324,7 @@
         <v>129193511</v>
       </c>
       <c r="B54" t="n">
-        <v>91570</v>
+        <v>91571</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6429,7 +6429,7 @@
         <v>129193484</v>
       </c>
       <c r="B55" t="n">
-        <v>92831</v>
+        <v>92832</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>

--- a/artfynd/A 45800-2025 artfynd.xlsx
+++ b/artfynd/A 45800-2025 artfynd.xlsx
@@ -6324,7 +6324,7 @@
         <v>129193511</v>
       </c>
       <c r="B54" t="n">
-        <v>91571</v>
+        <v>91574</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6429,7 +6429,7 @@
         <v>129193484</v>
       </c>
       <c r="B55" t="n">
-        <v>92832</v>
+        <v>92835</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>

--- a/artfynd/A 45800-2025 artfynd.xlsx
+++ b/artfynd/A 45800-2025 artfynd.xlsx
@@ -6324,7 +6324,7 @@
         <v>129193511</v>
       </c>
       <c r="B54" t="n">
-        <v>91574</v>
+        <v>91602</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6429,7 +6429,7 @@
         <v>129193484</v>
       </c>
       <c r="B55" t="n">
-        <v>92835</v>
+        <v>92863</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>

--- a/artfynd/A 45800-2025 artfynd.xlsx
+++ b/artfynd/A 45800-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY55"/>
+  <dimension ref="A1:AY57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6529,6 +6529,200 @@
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>132053729</v>
+      </c>
+      <c r="B56" t="n">
+        <v>92074</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>1618</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Hängticka</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Postia ceriflua</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(Berk. &amp; M.A.Curtis) Jülich</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Söder om Stora Ramm, Sm</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>584258</v>
+      </c>
+      <c r="R56" t="n">
+        <v>6374389</v>
+      </c>
+      <c r="S56" t="n">
+        <v>25</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Oskarshamn</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Misterhult</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2026-03-22</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>132053824</v>
+      </c>
+      <c r="B57" t="n">
+        <v>78934</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>353</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Söder om Stora Ramm, Sm</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>584243</v>
+      </c>
+      <c r="R57" t="n">
+        <v>6374320</v>
+      </c>
+      <c r="S57" t="n">
+        <v>25</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Oskarshamn</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Misterhult</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2026-03-22</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 45800-2025 artfynd.xlsx
+++ b/artfynd/A 45800-2025 artfynd.xlsx
@@ -6534,7 +6534,7 @@
         <v>132053729</v>
       </c>
       <c r="B56" t="n">
-        <v>92074</v>
+        <v>92075</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6631,7 +6631,7 @@
         <v>132053824</v>
       </c>
       <c r="B57" t="n">
-        <v>78934</v>
+        <v>78935</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>

--- a/artfynd/A 45800-2025 artfynd.xlsx
+++ b/artfynd/A 45800-2025 artfynd.xlsx
@@ -6534,7 +6534,7 @@
         <v>132053729</v>
       </c>
       <c r="B56" t="n">
-        <v>92075</v>
+        <v>92080</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6631,7 +6631,7 @@
         <v>132053824</v>
       </c>
       <c r="B57" t="n">
-        <v>78935</v>
+        <v>78940</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>

--- a/artfynd/A 45800-2025 artfynd.xlsx
+++ b/artfynd/A 45800-2025 artfynd.xlsx
@@ -6534,7 +6534,7 @@
         <v>132053729</v>
       </c>
       <c r="B56" t="n">
-        <v>92080</v>
+        <v>92082</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6631,7 +6631,7 @@
         <v>132053824</v>
       </c>
       <c r="B57" t="n">
-        <v>78940</v>
+        <v>78942</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>

--- a/artfynd/A 45800-2025 artfynd.xlsx
+++ b/artfynd/A 45800-2025 artfynd.xlsx
@@ -6534,7 +6534,7 @@
         <v>132053729</v>
       </c>
       <c r="B56" t="n">
-        <v>92082</v>
+        <v>92118</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6631,7 +6631,7 @@
         <v>132053824</v>
       </c>
       <c r="B57" t="n">
-        <v>78942</v>
+        <v>78976</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>

--- a/artfynd/A 45800-2025 artfynd.xlsx
+++ b/artfynd/A 45800-2025 artfynd.xlsx
@@ -6534,7 +6534,7 @@
         <v>132053729</v>
       </c>
       <c r="B56" t="n">
-        <v>92123</v>
+        <v>92126</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6631,7 +6631,7 @@
         <v>132053824</v>
       </c>
       <c r="B57" t="n">
-        <v>78981</v>
+        <v>78983</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>

--- a/artfynd/A 45800-2025 artfynd.xlsx
+++ b/artfynd/A 45800-2025 artfynd.xlsx
@@ -6534,7 +6534,7 @@
         <v>132053729</v>
       </c>
       <c r="B56" t="n">
-        <v>92126</v>
+        <v>92132</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6631,7 +6631,7 @@
         <v>132053824</v>
       </c>
       <c r="B57" t="n">
-        <v>78983</v>
+        <v>78985</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>

--- a/artfynd/A 45800-2025 artfynd.xlsx
+++ b/artfynd/A 45800-2025 artfynd.xlsx
@@ -6534,7 +6534,7 @@
         <v>132053729</v>
       </c>
       <c r="B56" t="n">
-        <v>92132</v>
+        <v>92142</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6631,7 +6631,7 @@
         <v>132053824</v>
       </c>
       <c r="B57" t="n">
-        <v>78985</v>
+        <v>78993</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>

--- a/artfynd/A 45800-2025 artfynd.xlsx
+++ b/artfynd/A 45800-2025 artfynd.xlsx
@@ -6534,7 +6534,7 @@
         <v>132053729</v>
       </c>
       <c r="B56" t="n">
-        <v>92142</v>
+        <v>92143</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>

--- a/artfynd/A 45800-2025 artfynd.xlsx
+++ b/artfynd/A 45800-2025 artfynd.xlsx
@@ -6534,7 +6534,7 @@
         <v>132053729</v>
       </c>
       <c r="B56" t="n">
-        <v>92143</v>
+        <v>92144</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6631,7 +6631,7 @@
         <v>132053824</v>
       </c>
       <c r="B57" t="n">
-        <v>78993</v>
+        <v>78994</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
